--- a/input/R_DMDT1 1.xlsx
+++ b/input/R_DMDT1 1.xlsx
@@ -25,10 +25,10 @@
     <t>001</t>
   </si>
   <si>
-    <t>Kh¸ch lÎ</t>
-  </si>
-  <si>
-    <t>Ph¶i thu cña kh¸ch hµng</t>
+    <t>Khách lẻ</t>
+  </si>
+  <si>
+    <t>Phải thu của khách hàng</t>
   </si>
   <si>
     <t/>
@@ -43,10 +43,10 @@
     <t>189</t>
   </si>
   <si>
-    <t>C«ng ty TNHH 189</t>
-  </si>
-  <si>
-    <t>27 Tr­êng Chinh, KiÕn An, HP</t>
+    <t>Công ty TNHH 189</t>
+  </si>
+  <si>
+    <t>27 Trường Chinh, Kiến An, HP</t>
   </si>
   <si>
     <t>0200134794</t>
@@ -55,10 +55,10 @@
     <t>190</t>
   </si>
   <si>
-    <t>C«ng ty TNHH èng thÐp 190</t>
-  </si>
-  <si>
-    <t>Km91, Hïng V­¬ng, Hång Bµng, HP</t>
+    <t>Công ty TNHH ống thép 190</t>
+  </si>
+  <si>
+    <t>Km91, Hùng Vương, Hồng Bàng, HP</t>
   </si>
   <si>
     <t>0200414657</t>
@@ -70,7 +70,7 @@
     <t>AARTI STEELS LIMITED</t>
   </si>
   <si>
-    <t>G.T Road, Ludhiana, Miller G¹n, India</t>
+    <t>G.T Road, Ludhiana, Miller Gạn, India</t>
   </si>
   <si>
     <t>ABDUL</t>
@@ -112,10 +112,10 @@
     <t>ADUONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH An D­¬ng</t>
-  </si>
-  <si>
-    <t>53 TrÇn Kh¸nh D­ - Ng« QuyÒn - H¶i Phßng</t>
+    <t>Công ty TNHH An Dương</t>
+  </si>
+  <si>
+    <t>53 Trần Khánh Dư - Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0200439933</t>
@@ -145,16 +145,16 @@
     <t>AMITY SM</t>
   </si>
   <si>
-    <t>C¤NG TY TNHH AMITY SM</t>
+    <t>CÔNG TY TNHH AMITY SM</t>
   </si>
   <si>
     <t>AMY</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn t¶i ¸ Mü</t>
-  </si>
-  <si>
-    <t>47-49 Hoµng Sa, P §a Kao, QuËn 1, HCM</t>
+    <t>Công ty TNHH Vận tải á Mỹ</t>
+  </si>
+  <si>
+    <t>47-49 Hoàng Sa, P Đa Kao, Quận 1, HCM</t>
   </si>
   <si>
     <t>0303654724</t>
@@ -172,10 +172,10 @@
     <t>ANBINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH MTV VËn T¶i An B×nh</t>
-  </si>
-  <si>
-    <t>Khu 1 BÝch Kh«i - TT Minh T©n - Kinh M«n - H¶i D­¬ng</t>
+    <t>Công ty TNHH MTV Vận Tải An Bình</t>
+  </si>
+  <si>
+    <t>Khu 1 Bích Khôi - TT Minh Tân - Kinh Môn - Hải Dương</t>
   </si>
   <si>
     <t>0800992240</t>
@@ -184,10 +184,10 @@
     <t>ANHOA</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn GiÊy An Hoµ</t>
-  </si>
-  <si>
-    <t>Th«n An Hoµ - x· VÜnh Lîi - HuyÖn S¬n D­¬ng - TØnh Tuyªn Quang</t>
+    <t>Công ty Cổ Phần Giấy An Hoà</t>
+  </si>
+  <si>
+    <t>Thôn An Hoà - xã Vĩnh Lợi - Huyện Sơn Dương - Tỉnh Tuyên Quang</t>
   </si>
   <si>
     <t>5000219471</t>
@@ -196,10 +196,10 @@
     <t>ANHTUNG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i biÓn vµ th­¬ng m¹i Anh Tïng</t>
-  </si>
-  <si>
-    <t>Xãm Xu©n LËp - X· H¶i Xu©n - HuyÖn H¶i HËu - TØnh Nam §Þnh</t>
+    <t>Công ty TNHH Vận Tải biển và thương mại Anh Tùng</t>
+  </si>
+  <si>
+    <t>Xóm Xuân Lập - Xã Hải Xuân - Huyện Hải Hậu - Tỉnh Nam Định</t>
   </si>
   <si>
     <t>0305366295</t>
@@ -208,10 +208,10 @@
     <t>ANNHUTHANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH DÞch Vô VËn T¶i Tµu BiÓn An Nh­ Thµnh</t>
-  </si>
-  <si>
-    <t>190 B¹ch §»ng - Ph­êng 24 - QuËn B×nh Th¹nh - TP. HCM</t>
+    <t>Công ty TNHH Dịch Vụ Vận Tải Tàu Biển An Như Thành</t>
+  </si>
+  <si>
+    <t>190 Bạch Đằng - Phường 24 - Quận Bình Thạnh - TP. HCM</t>
   </si>
   <si>
     <t>0309380999</t>
@@ -220,10 +220,10 @@
     <t>ANPHA HANOI</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i An Pha Hµ Néi</t>
-  </si>
-  <si>
-    <t>TÇng 8, sè nhµ 218 ®­êng Th­îng §×nh, Ph­êng Th­îng §×nh, QuËn Thanhh Xu©n, TP. HN</t>
+    <t>Công ty TNHH Vận Tải An Pha Hà Nội</t>
+  </si>
+  <si>
+    <t>Tầng 8, số nhà 218 đường Thượng Đình, Phường Thượng Đình, Quận Thanhh Xuân, TP. HN</t>
   </si>
   <si>
     <t>0108836431</t>
@@ -232,10 +232,10 @@
     <t>ANQUY</t>
   </si>
   <si>
-    <t>C«ng ty TNHH ThiÕt BÞ C«ng NghiÖp An Quý</t>
-  </si>
-  <si>
-    <t>Êp ThÞ V¶i - X· Mü Xu©n - HuyÖn T©n Thµnh - TØnh Bµ RÞa - Vòng Tµu</t>
+    <t>Công ty TNHH Thiết Bị Công Nghiệp An Quý</t>
+  </si>
+  <si>
+    <t>ấp Thị Vải - Xã Mỹ Xuân - Huyện Tân Thành - Tỉnh Bà Rịa - Vũng Tàu</t>
   </si>
   <si>
     <t>3502207130</t>
@@ -244,16 +244,16 @@
     <t>ANTRUNG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH An Trung</t>
+    <t>Công ty TNHH An Trung</t>
   </si>
   <si>
     <t>ANVIET</t>
   </si>
   <si>
-    <t>Cty CP An ViÖt</t>
-  </si>
-  <si>
-    <t>81 tæ 3, Thµnh C«ng, Hµ Néi</t>
+    <t>Cty CP An Việt</t>
+  </si>
+  <si>
+    <t>81 tổ 3, Thành Công, Hà Nội</t>
   </si>
   <si>
     <t>0101254988</t>
@@ -280,10 +280,10 @@
     <t>ARTEX</t>
   </si>
   <si>
-    <t>Artexport Hµ Néi</t>
-  </si>
-  <si>
-    <t>31-33 Ng« QuyÒn, Hµ Néi</t>
+    <t>Artexport Hà Nội</t>
+  </si>
+  <si>
+    <t>31-33 Ngô Quyền, Hà Nội</t>
   </si>
   <si>
     <t>ASIA</t>
@@ -295,10 +295,10 @@
     <t>ASIATRANS VN</t>
   </si>
   <si>
-    <t>C«ng Ty Cæ PhÇn ASIATRANS ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 421 TrÇn H­ng §¹o, ph­êng An H¶i, TP  §µ N½ng, ViÖt Nam</t>
+    <t>Công Ty Cổ Phần ASIATRANS Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 421 Trần Hưng Đạo, phường An Hải, TP  Đà Nẵng, Việt Nam</t>
   </si>
   <si>
     <t>0400459020</t>
@@ -322,10 +322,10 @@
     <t>AUA</t>
   </si>
   <si>
-    <t>C«ng Ty CP Cöa ¢u ¸</t>
-  </si>
-  <si>
-    <t>B¾c Linh §µm - Hoµng Mai - Hµ Néi</t>
+    <t>Công Ty CP Cửa Âu á</t>
+  </si>
+  <si>
+    <t>Bắc Linh Đàm - Hoàng Mai - Hà Nội</t>
   </si>
   <si>
     <t>0102543647</t>
@@ -334,10 +334,10 @@
     <t>AUREOLE</t>
   </si>
   <si>
-    <t>C«ng ty TNHH MTV kho vËn hãa chÊt Aureole</t>
-  </si>
-  <si>
-    <t>l« CN5.2C, KCN §×nh Vò, P. §«ng H¶i 2, Q. H¶i An, TP. H¶i Phßng</t>
+    <t>Công ty TNHH MTV kho vận hóa chất Aureole</t>
+  </si>
+  <si>
+    <t>lô CN5.2C, KCN Đình Vũ, P. Đông Hải 2, Q. Hải An, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201282347</t>
@@ -364,10 +364,10 @@
     <t>BACHA</t>
   </si>
   <si>
-    <t>Cty TNHH B¾c Hµ</t>
-  </si>
-  <si>
-    <t>30 V¨n Cao, Ng« QuyÒn, HP</t>
+    <t>Cty TNHH Bắc Hà</t>
+  </si>
+  <si>
+    <t>30 Văn Cao, Ngô Quyền, HP</t>
   </si>
   <si>
     <t>0200573600</t>
@@ -376,10 +376,10 @@
     <t>BACVIET</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn kim khÝ B¾c ViÖt</t>
-  </si>
-  <si>
-    <t>KCN §×nh Vò, Ph­êng §«ng H¶i 2, QuËn H¶i An, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần kim khí Bắc Việt</t>
+  </si>
+  <si>
+    <t>KCN Đình Vũ, Phường Đông Hải 2, Quận Hải An, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200942350</t>
@@ -412,10 +412,10 @@
     <t>BANMAI</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Sµi Gßn Ban Mai</t>
-  </si>
-  <si>
-    <t>44 Linh Lang, Ba §×nh, Hµ Néi</t>
+    <t>Công ty TNHH Sài Gòn Ban Mai</t>
+  </si>
+  <si>
+    <t>44 Linh Lang, Ba Đình, Hà Nội</t>
   </si>
   <si>
     <t>0100595632</t>
@@ -424,10 +424,10 @@
     <t>BAOBAO</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Kho¸ng S¶n B¶o B¶o</t>
-  </si>
-  <si>
-    <t>265/20 NguyÔn Th¸i S¬n, Ph­êng 7, QuËn Gß VÊp, TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH Khoáng Sản Bảo Bảo</t>
+  </si>
+  <si>
+    <t>265/20 Nguyễn Thái Sơn, Phường 7, Quận Gò Vấp, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>01</t>
@@ -439,10 +439,10 @@
     <t>BAODUY</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Quèc B¶o Duy</t>
-  </si>
-  <si>
-    <t>Tæ 1,Th«n T©n H¹nh,ThÞ TrÊn Phó Myc, H. T©n Thµnh,T. Bµ RÞa Vòng Tµu</t>
+    <t>Công ty TNHH Quốc Bảo Duy</t>
+  </si>
+  <si>
+    <t>Tổ 1,Thôn Tân Hạnh,Thị Trấn Phú Myc, H. Tân Thành,T. Bà Rịa Vũng Tàu</t>
   </si>
   <si>
     <t>3502273616</t>
@@ -451,10 +451,10 @@
     <t>BAOTUONG</t>
   </si>
   <si>
-    <t>C«ng ty TM &amp; DV B¶o T­êng</t>
-  </si>
-  <si>
-    <t>26F3 NghÜa §«, Tõ Liªm, Hµ Néi</t>
+    <t>Công ty TM &amp; DV Bảo Tường</t>
+  </si>
+  <si>
+    <t>26F3 Nghĩa Đô, Từ Liêm, Hà Nội</t>
   </si>
   <si>
     <t>0100427349-1</t>
@@ -475,10 +475,10 @@
     <t>BATECO</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn BATECO ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Tæ 16, Ph­êng LÜnh Nam, QuËn Hoµng Mai, TP. Hµ Néi, ViÖt Nam</t>
+    <t>Công ty cổ phần BATECO Việt Nam</t>
+  </si>
+  <si>
+    <t>Tổ 16, Phường Lĩnh Nam, Quận Hoàng Mai, TP. Hà Nội, Việt Nam</t>
   </si>
   <si>
     <t>0105992880</t>
@@ -487,10 +487,10 @@
     <t>BBNA</t>
   </si>
   <si>
-    <t>c«ng ty CP bao b× &amp; KD tæng hîp NghÖ An</t>
-  </si>
-  <si>
-    <t>Km 10, Quèc lé 1A, Nghi Liªn, Nghi Léc, NghÖ AN</t>
+    <t>công ty CP bao bì &amp; KD tổng hợp Nghệ An</t>
+  </si>
+  <si>
+    <t>Km 10, Quốc lộ 1A, Nghi Liên, Nghi Lộc, Nghệ AN</t>
   </si>
   <si>
     <t>2900326262</t>
@@ -499,10 +499,10 @@
     <t>BBRAUN</t>
   </si>
   <si>
-    <t>BBRAUN VIÖT NAM COMPANY LIMITED</t>
-  </si>
-  <si>
-    <t>Thanh Oai Industrial, Thanh oai Dist , Hµ Néi</t>
+    <t>BBRAUN VIệT NAM COMPANY LIMITED</t>
+  </si>
+  <si>
+    <t>Thanh Oai Industrial, Thanh oai Dist , Hà Nội</t>
   </si>
   <si>
     <t>0100114064</t>
@@ -517,10 +517,10 @@
     <t>BENKIEN</t>
   </si>
   <si>
-    <t>C«ng ty CN tµu thuû BÕn KiÒn</t>
-  </si>
-  <si>
-    <t>An §ång, An D­¬ng, H¶i Phßng</t>
+    <t>Công ty CN tàu thuỷ Bến Kiền</t>
+  </si>
+  <si>
+    <t>An Đồng, An Dương, Hải Phòng</t>
   </si>
   <si>
     <t>0200153412</t>
@@ -529,7 +529,7 @@
     <t>BENLINE</t>
   </si>
   <si>
-    <t>C«ng ty CP hµng h¶i liªn kÕt ViÖt Nam ( BENLINE AGENCYES ViÖt Nam)</t>
+    <t>Công ty CP hàng hải liên kết Việt Nam ( BENLINE AGENCYES Việt Nam)</t>
   </si>
   <si>
     <t>BENOCEAN</t>
@@ -565,10 +565,10 @@
     <t>BGIANG</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn XuÊt NhËp KhÈu B¾c Giang</t>
-  </si>
-  <si>
-    <t>Sè 1 - NguyÔn V¨n Cõ - TP. b¾c Giang - TØnh B¾c Giang</t>
+    <t>Công ty Cổ Phần Xuất Nhập Khẩu Bắc Giang</t>
+  </si>
+  <si>
+    <t>Số 1 - Nguyễn Văn Cừ - TP. bắc Giang - Tỉnh Bắc Giang</t>
   </si>
   <si>
     <t>2400110949</t>
@@ -592,10 +592,10 @@
     <t>BIENHOA</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn hµng tiªu dïng Biªn Hßa</t>
-  </si>
-  <si>
-    <t>KCN Biªn Hoµ 1 - Ph­êng B×nh An - Thµnh Phè Biªn Hoµ - TØnh §ång Nai</t>
+    <t>Công ty cổ phần hàng tiêu dùng Biên Hòa</t>
+  </si>
+  <si>
+    <t>KCN Biên Hoà 1 - Phường Bình An - Thành Phố Biên Hoà - Tỉnh Đồng Nai</t>
   </si>
   <si>
     <t>3600495818</t>
@@ -604,10 +604,10 @@
     <t>BIENHOA-TRIAN</t>
   </si>
   <si>
-    <t>Nhµ m¸y ®­êng TTC Biªn Hßa - TrÞ An</t>
-  </si>
-  <si>
-    <t>Êp 1, X· TrÞ An, HuyÖn VÜnh Cöu, TØnh §ång Nai</t>
+    <t>Nhà máy đường TTC Biên Hòa - Trị An</t>
+  </si>
+  <si>
+    <t>ấp 1, Xã Trị An, Huyện Vĩnh Cửu, Tỉnh Đồng Nai</t>
   </si>
   <si>
     <t>3600495818009</t>
@@ -616,10 +616,10 @@
     <t>BIENXANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH DÞch Vô vµ Kü ThuËt BiÓn Xanh</t>
-  </si>
-  <si>
-    <t>183C/5P T«n ThÊt thuyÕt, Ph­êng VÜnh Héi, TP. Hå ChÝ MInh, ViÖt Nam</t>
+    <t>Công ty TNHH Dịch Vụ và Kỹ Thuật Biển Xanh</t>
+  </si>
+  <si>
+    <t>183C/5P Tôn Thất thuyết, Phường Vĩnh Hội, TP. Hồ Chí MInh, Việt Nam</t>
   </si>
   <si>
     <t>0312265509</t>
@@ -628,10 +628,10 @@
     <t>BINH AN</t>
   </si>
   <si>
-    <t>Cty n¨ng l­îng B×nh An</t>
-  </si>
-  <si>
-    <t>57 BÕn BÝnh, H¶i Phßng</t>
+    <t>Cty năng lượng Bình An</t>
+  </si>
+  <si>
+    <t>57 Bến Bính, Hải Phòng</t>
   </si>
   <si>
     <t>0200108949</t>
@@ -640,10 +640,10 @@
     <t>BINHMINH</t>
   </si>
   <si>
-    <t>Cty TNHH Sx &amp; DVTM B×nh Minh</t>
-  </si>
-  <si>
-    <t>P204-CT1 Chung C­ Xu©n §Ønh, Tõ Liªm, HN</t>
+    <t>Cty TNHH Sx &amp; DVTM Bình Minh</t>
+  </si>
+  <si>
+    <t>P204-CT1 Chung Cư Xuân Đỉnh, Từ Liêm, HN</t>
   </si>
   <si>
     <t>0102592080</t>
@@ -652,10 +652,10 @@
     <t>BINHVIEN</t>
   </si>
   <si>
-    <t>Cty TNHH B×nh Viªn</t>
-  </si>
-  <si>
-    <t>Tasaco Km 104+200 NguyÔn BØnh Khiªm,HP</t>
+    <t>Cty TNHH Bình Viên</t>
+  </si>
+  <si>
+    <t>Tasaco Km 104+200 Nguyễn Bỉnh Khiêm,HP</t>
   </si>
   <si>
     <t>0200692781</t>
@@ -664,10 +664,10 @@
     <t>BLINH</t>
   </si>
   <si>
-    <t>C«ng ty CPTM &amp; VT Quèc TÕ B¶o Linh</t>
-  </si>
-  <si>
-    <t>356 §­êng §µ N½ng - Ng« QuyÒn - H¶i Phßng</t>
+    <t>Công ty CPTM &amp; VT Quốc Tế Bảo Linh</t>
+  </si>
+  <si>
+    <t>356 Đường Đà Nẵng - Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0200639844</t>
@@ -694,10 +694,10 @@
     <t>BONGSEN</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i vµ dÞch vô xuÊt nhËp khÈu B«ng Sen</t>
-  </si>
-  <si>
-    <t>Sè 12, l« BT3, khu d©n c­ §¹i An, Ph­êng Tø Minh, Thµnh Phè H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty cổ phần thương mại và dịch vụ xuất nhập khẩu Bông Sen</t>
+  </si>
+  <si>
+    <t>Số 12, lô BT3, khu dân cư Đại An, Phường Tứ Minh, Thành Phố Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0800932192</t>
@@ -706,10 +706,10 @@
     <t>BONGSENVANG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn s¶n xuÊt vµ xuÊt nhËp khÈu b«ng sen vµng</t>
-  </si>
-  <si>
-    <t>Sè 398 §µ N½ng, Ph­êng §«ng H¶i, Thµnh Phè h¶i Phßng, ViÖt Nam</t>
+    <t>Công ty cổ phần sản xuất và xuất nhập khẩu bông sen vàng</t>
+  </si>
+  <si>
+    <t>Số 398 Đà Nẵng, Phường Đông Hải, Thành Phố hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0200841715</t>
@@ -769,10 +769,10 @@
     <t>CANG-DV</t>
   </si>
   <si>
-    <t>Cty CP c¶ng DVDK §×nh Vò</t>
-  </si>
-  <si>
-    <t>KCN §Ünh Vò - P.§«ng H¶i II HA-HP</t>
+    <t>Cty CP cảng DVDK Đình Vũ</t>
+  </si>
+  <si>
+    <t>KCN Đĩnh Vũ - P.Đông Hải II HA-HP</t>
   </si>
   <si>
     <t>0200754420</t>
@@ -805,10 +805,10 @@
     <t>CARGO ROAD VN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Cargo Road ViÖt Nam</t>
-  </si>
-  <si>
-    <t>TÇng 4, Sè 15A NguyÔn Khang, P. Trung Hßa, Q. CÇu GiÊy, TP. Hµ Néi</t>
+    <t>Công ty TNHH Cargo Road Việt Nam</t>
+  </si>
+  <si>
+    <t>Tầng 4, Số 15A Nguyễn Khang, P. Trung Hòa, Q. Cầu Giấy, TP. Hà Nội</t>
   </si>
   <si>
     <t>0105141551</t>
@@ -826,10 +826,10 @@
     <t>CAYCAUVANG</t>
   </si>
   <si>
-    <t>C«ng Ty Cæ PhÇn C©y CÇu Vµng</t>
-  </si>
-  <si>
-    <t>Phßng 310 sè 31 - 33 Minh Khai, Ph­êng Hoµng v¨n Thô , QuËn Hång Bµng, TP. HP</t>
+    <t>Công Ty Cổ Phần Cây Cầu Vàng</t>
+  </si>
+  <si>
+    <t>Phòng 310 số 31 - 33 Minh Khai, Phường Hoàng văn Thụ , Quận Hồng Bàng, TP. HP</t>
   </si>
   <si>
     <t>0200823970</t>
@@ -841,7 +841,7 @@
     <t>Cty TNHH TM &amp; DV Vina C.C</t>
   </si>
   <si>
-    <t>14 BiÖt thù 3, Linh §µm, Hoµng Mai, HN</t>
+    <t>14 Biệt thự 3, Linh Đàm, Hoàng Mai, HN</t>
   </si>
   <si>
     <t>0101771961</t>
@@ -883,10 +883,10 @@
     <t>CGLDKT</t>
   </si>
   <si>
-    <t>Cty CP XNK Chuyªn gia lao ®éng &amp; kü thuËt</t>
-  </si>
-  <si>
-    <t>473 NguyÔn Tr·i, Thanh Xu©n, HN</t>
+    <t>Cty CP XNK Chuyên gia lao động &amp; kỹ thuật</t>
+  </si>
+  <si>
+    <t>473 Nguyễn Trãi, Thanh Xuân, HN</t>
   </si>
   <si>
     <t>0100107324</t>
@@ -895,10 +895,10 @@
     <t>CHANGHO</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i Chang Ho</t>
-  </si>
-  <si>
-    <t>Khu phè Song VÜnh, Ph­êng T©n Ph­íc, ThÞ X· Phó Mü, TØnh Bµ RÞa - Vòng Tµu, ViÖt Nam</t>
+    <t>Công ty TNHH Vận Tải Chang Ho</t>
+  </si>
+  <si>
+    <t>Khu phố Song Vĩnh, Phường Tân Phước, Thị Xã Phú Mỹ, Tỉnh Bà Rịa - Vũng Tàu, Việt Nam</t>
   </si>
   <si>
     <t>3502300027</t>
@@ -907,10 +907,10 @@
     <t>CHANNUOI C.P</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ch¨n nu«i C.P. ViÖt Nam - Chi nh¸nh NM5 t¹i §ång Nai</t>
-  </si>
-  <si>
-    <t>KCN Bµu XÐo, X· Tr¶ng Bom, TØnh §ång Nai</t>
+    <t>Công ty cổ phần chăn nuôi C.P. Việt Nam - Chi nhánh NM5 tại Đồng Nai</t>
+  </si>
+  <si>
+    <t>KCN Bàu Xéo, Xã Trảng Bom, Tỉnh Đồng Nai</t>
   </si>
   <si>
     <t>3600224423-019</t>
@@ -919,10 +919,10 @@
     <t>CHAUA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH DVHH Ch©u ¸ Th¸i B×nh D­¬ng</t>
-  </si>
-  <si>
-    <t>NguyÔn BØnh Khiªm - Ph­êng BÕn NghÐ - Q1 - TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH DVHH Châu á Thái Bình Dương</t>
+  </si>
+  <si>
+    <t>Nguyễn Bỉnh Khiêm - Phường Bến Nghé - Q1 - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0310783960</t>
@@ -931,10 +931,10 @@
     <t>CHAULUC</t>
   </si>
   <si>
-    <t>Cty TNHH Giao NhËn &amp; V©n T¶i Quèc TÕ Ch©u Lôc</t>
-  </si>
-  <si>
-    <t>55 Lª Quèc H­ng - P12 - QuËn 4 - TP Hå ChÝ Minh</t>
+    <t>Cty TNHH Giao Nhận &amp; Vân Tải Quốc Tế Châu Lục</t>
+  </si>
+  <si>
+    <t>55 Lê Quốc Hưng - P12 - Quận 4 - TP Hồ Chí Minh</t>
   </si>
   <si>
     <t>0304742638</t>
@@ -958,10 +958,10 @@
     <t>CHINFON</t>
   </si>
   <si>
-    <t>C«ng Ty Xi M¨ng Chinfon</t>
-  </si>
-  <si>
-    <t>Trµng Kªnh - Minh §øc - Thñy Nguyªn - H¶i Phßng</t>
+    <t>Công Ty Xi Măng Chinfon</t>
+  </si>
+  <si>
+    <t>Tràng Kênh - Minh Đức - Thủy Nguyên - Hải Phòng</t>
   </si>
   <si>
     <t>0200110200</t>
@@ -970,10 +970,10 @@
     <t>CHINGSU</t>
   </si>
   <si>
-    <t>C«ng ty Ching SSu Enterprise</t>
-  </si>
-  <si>
-    <t>§µi Loan</t>
+    <t>Công ty Ching SSu Enterprise</t>
+  </si>
+  <si>
+    <t>Đài Loan</t>
   </si>
   <si>
     <t>CHITTAGONG</t>
@@ -1000,10 +1000,10 @@
     <t>CK TLONG</t>
   </si>
   <si>
-    <t>Cty CP c¬ khÝ TM Th¨ng Long</t>
-  </si>
-  <si>
-    <t>Sè 9 Quèc lé 23B, Nam Hång, §«ng Anh, HN</t>
+    <t>Cty CP cơ khí TM Thăng Long</t>
+  </si>
+  <si>
+    <t>Số 9 Quốc lộ 23B, Nam Hồng, Đông Anh, HN</t>
   </si>
   <si>
     <t>0101651671</t>
@@ -1018,10 +1018,10 @@
     <t>CLIO SHIPPING</t>
   </si>
   <si>
-    <t>C¤NG TY TNHH CLIO SHIPPING AND LOGISTICS VIET NAM</t>
-  </si>
-  <si>
-    <t>Khu d©n c­ Nam Long - TrÇn Träng Cung, P. T©n ThuËn §«ng, QuËn 7, TP. HCM</t>
+    <t>CÔNG TY TNHH CLIO SHIPPING AND LOGISTICS VIET NAM</t>
+  </si>
+  <si>
+    <t>Khu dân cư Nam Long - Trần Trọng Cung, P. Tân Thuận Đông, Quận 7, TP. HCM</t>
   </si>
   <si>
     <t xml:space="preserve"> 0315479065</t>
@@ -1033,16 +1033,16 @@
     <t>Clipper Bulk Shipping PTE LTD</t>
   </si>
   <si>
-    <t>Warehouse 1J - 0811, Ham nyach Free Zone, Sh¹ah, Uni tcd</t>
+    <t>Warehouse 1J - 0811, Ham nyach Free Zone, Shạah, Uni tcd</t>
   </si>
   <si>
     <t>CLUC-HP</t>
   </si>
   <si>
-    <t>CN C«ng ty TNHH §¹i Lý Tµu BiÓn Ch©u Lôc t¹i H¶i Phßng</t>
-  </si>
-  <si>
-    <t>P.603 - Toµ nhµ DG - sè 15 TrÇn Phó - Ng« QuyÒn - H¶i Phßng</t>
+    <t>CN Công ty TNHH Đại Lý Tàu Biển Châu Lục tại Hải Phòng</t>
+  </si>
+  <si>
+    <t>P.603 - Toà nhà DG - số 15 Trần Phú - Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0302597086-001</t>
@@ -1051,10 +1051,10 @@
     <t>CMA</t>
   </si>
   <si>
-    <t>C«ng Ty Cæ PhÇn CMA - CGM VN JSC</t>
-  </si>
-  <si>
-    <t>81-85 Hµm Nghi - QuËn 1 - Hå ChÝ Minh - ViÖt Nam</t>
+    <t>Công Ty Cổ Phần CMA - CGM VN JSC</t>
+  </si>
+  <si>
+    <t>81-85 Hàm Nghi - Quận 1 - Hồ Chí Minh - Việt Nam</t>
   </si>
   <si>
     <t>0304207743</t>
@@ -1063,10 +1063,10 @@
     <t>CNSAOSANG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Cung óng VËt T­ C«ng NghiÖp Sao S¸ng</t>
-  </si>
-  <si>
-    <t>17/53 Hoµng DiÖu - TP. Nha Trang - Kh¸nh Hßa</t>
+    <t>Công ty TNHH Cung úng Vật Tư Công Nghiệp Sao Sáng</t>
+  </si>
+  <si>
+    <t>17/53 Hoàng Diệu - TP. Nha Trang - Khánh Hòa</t>
   </si>
   <si>
     <t>4200709866</t>
@@ -1075,10 +1075,10 @@
     <t>CNTT</t>
   </si>
   <si>
-    <t>C«ng ty tµi chÝnh TNHH MTV c«ng nghiÖp tµu thñy</t>
-  </si>
-  <si>
-    <t>Sè 120 - Hµng Trèng - Hoµn KiÕm - Hµ Néi</t>
+    <t>Công ty tài chính TNHH MTV công nghiệp tàu thủy</t>
+  </si>
+  <si>
+    <t>Số 120 - Hàng Trống - Hoàn Kiếm - Hà Nội</t>
   </si>
   <si>
     <t>0100996345</t>
@@ -1102,10 +1102,10 @@
     <t>CONCORD</t>
   </si>
   <si>
-    <t>CN H¶i Phogf - Cty TNHH Star Concord ( ViÖt Nam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tßa nhµ TD l« 20A §­êng Lª Hång Phong - Ng« QuyÒn - H¶i Phßng</t>
+    <t>CN Hải Phogf - Cty TNHH Star Concord ( Việt Nam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tòa nhà TD lô 20A Đường Lê Hồng Phong - Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0313647412001</t>
@@ -1114,10 +1114,10 @@
     <t>CONECO</t>
   </si>
   <si>
-    <t>Cty CP CONECO th­¬ng m¹i</t>
-  </si>
-  <si>
-    <t>58 Thiªn §øc, Yªn Viªn, Gia L©m, HN</t>
+    <t>Cty CP CONECO thương mại</t>
+  </si>
+  <si>
+    <t>58 Thiên Đức, Yên Viên, Gia Lâm, HN</t>
   </si>
   <si>
     <t>0101993146</t>
@@ -1126,10 +1126,10 @@
     <t>CONGNGHEHOABINH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ph©n bãn vµ chuyÓn giao C«ng NghÖ Hoµ B×nh</t>
-  </si>
-  <si>
-    <t>Khu c«ng nghiÖp M«ng Ho¸, Ph­êng Kú S¬n, TØnh Phó Thä, ViÖt Nam</t>
+    <t>Công ty cổ phần phân bón và chuyển giao Công Nghệ Hoà Bình</t>
+  </si>
+  <si>
+    <t>Khu công nghiệp Mông Hoá, Phường Kỳ Sơn, Tỉnh Phú Thọ, Việt Nam</t>
   </si>
   <si>
     <t>5400480712</t>
@@ -1138,10 +1138,10 @@
     <t>CONGTHANH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i dich vô C«ng Thµnh</t>
-  </si>
-  <si>
-    <t>Sè nhµ 320, ®­êng 3 th¸ng 2, tæ d©n phè sè 6, X· Th¸i Huy, TØnh H­ng Yªn</t>
+    <t>Công ty cổ phần thương mại dich vụ Công Thành</t>
+  </si>
+  <si>
+    <t>Số nhà 320, đường 3 tháng 2, tổ dân phố số 6, Xã Thái Huy, Tỉnh Hưng Yên</t>
   </si>
   <si>
     <t>1000335625</t>
@@ -1150,10 +1150,10 @@
     <t>CONTAINER HSON</t>
   </si>
   <si>
-    <t>C«ng ty CP DÞch Vô VËn t¶i Container Hoµng S¬n</t>
-  </si>
-  <si>
-    <t>Tæ d©n phè H¹ §o¹n 2 - §«ng H¶i 2 - H¶i An - H¶i Phßng</t>
+    <t>Công ty CP Dịch Vụ Vận tải Container Hoàng Sơn</t>
+  </si>
+  <si>
+    <t>Tổ dân phố Hạ Đoạn 2 - Đông Hải 2 - Hải An - Hải Phòng</t>
   </si>
   <si>
     <t>0201231818</t>
@@ -1162,10 +1162,10 @@
     <t>CONTAINERDINHVU</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn n©ng h¹ Container §×nh Vò</t>
-  </si>
-  <si>
-    <t>508 Lª Th¸nh T«ng, Ph­êng Ng« QuyÒn, TP. H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty cổ phần nâng hạ Container Đình Vũ</t>
+  </si>
+  <si>
+    <t>508 Lê Thánh Tông, Phường Ngô Quyền, TP. Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0202255917</t>
@@ -1174,19 +1174,19 @@
     <t>CONTAINERPHIANAM</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn container PhÝa Nam</t>
-  </si>
-  <si>
-    <t>Sè 11 NguyÔn HuÖ - Ph­êng BÕn NghÐ - QuËn 1 - TP. Hå ChÝ Minh</t>
+    <t>Công ty cổ phần container Phía Nam</t>
+  </si>
+  <si>
+    <t>Số 11 Nguyễn Huệ - Phường Bến Nghé - Quận 1 - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>CONTENOQUOCTEHP</t>
   </si>
   <si>
-    <t>C«ng ty TNHH C¶ng C«ng Ten N¬ Quèc TÕ H¶i Phßng</t>
-  </si>
-  <si>
-    <t>§­êng Lª Hång Phong, Ph­êng Thµnh Tpp, QuËn h¶i An, TP. H¶i Phßng</t>
+    <t>Công ty TNHH Cảng Công Ten Nơ Quốc Tế Hải Phòng</t>
+  </si>
+  <si>
+    <t>Đường Lê Hồng Phong, Phường Thành Tpp, Quận hải An, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201222436</t>
@@ -1195,10 +1195,10 @@
     <t>COPHANPHUAN</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn Phó An</t>
-  </si>
-  <si>
-    <t>Th«n Phó An, ThÞ TrÊn C¸t Thµnh, HuyÖn Trùc Ninh, Nam §Inh, ViÖt Nam</t>
+    <t>Công ty cổ phần Phú An</t>
+  </si>
+  <si>
+    <t>Thôn Phú An, Thị Trấn Cát Thành, Huyện Trực Ninh, Nam ĐInh, Việt Nam</t>
   </si>
   <si>
     <t>0600296486</t>
@@ -1207,10 +1207,10 @@
     <t>COSCO SHIPPING</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Cosco Shipping Lines ( ViÖt Nam)</t>
-  </si>
-  <si>
-    <t>Sè 5 Hå BiÓu Ch¸nh, Ph­êng 11, QuËn Phó NhuËn, Thµnh Phè Hå ChÝ Minh, ViÖt Nam</t>
+    <t>Công ty TNHH Cosco Shipping Lines ( Việt Nam)</t>
+  </si>
+  <si>
+    <t>Số 5 Hồ Biểu Chánh, Phường 11, Quận Phú Nhuận, Thành Phố Hồ Chí Minh, Việt Nam</t>
   </si>
   <si>
     <t>0301471348</t>
@@ -1234,16 +1234,16 @@
     <t>CPDAIDUONG</t>
   </si>
   <si>
-    <t>C«ng ty CP Ph¸t TriÓn vµ VËn t¶i §¹i D­¬ng</t>
+    <t>Công ty CP Phát Triển và Vận tải Đại Dương</t>
   </si>
   <si>
     <t>CPKS</t>
   </si>
   <si>
-    <t>C«ng Ty Cæ PhÇn Kho¸ng S¶n Vµ §Çu T­ VINASHIN</t>
-  </si>
-  <si>
-    <t>109 Qu¸n Th¸nh - Ba §×nh - Hµ Néi</t>
+    <t>Công Ty Cổ Phần Khoáng Sản Và Đầu Tư VINASHIN</t>
+  </si>
+  <si>
+    <t>109 Quán Thánh - Ba Đình - Hà Nội</t>
   </si>
   <si>
     <t>0102167505</t>
@@ -1261,10 +1261,10 @@
     <t>CTTT</t>
   </si>
   <si>
-    <t>Cty TNHH Trang Thµnh</t>
-  </si>
-  <si>
-    <t>119 NguyÔn §øc C¶nh, HP</t>
+    <t>Cty TNHH Trang Thành</t>
+  </si>
+  <si>
+    <t>119 Nguyễn Đức Cảnh, HP</t>
   </si>
   <si>
     <t>0200413565</t>
@@ -1273,10 +1273,10 @@
     <t>D AN</t>
   </si>
   <si>
-    <t>C«ng Ty TNHH §«ng Ên</t>
-  </si>
-  <si>
-    <t>Trung Hoµ - Nh©n ChÝnh - Thanh Xu©n - Hµ Néi</t>
+    <t>Công Ty TNHH Đông ấn</t>
+  </si>
+  <si>
+    <t>Trung Hoà - Nhân Chính - Thanh Xuân - Hà Nội</t>
   </si>
   <si>
     <t>0101126584</t>
@@ -1285,10 +1285,10 @@
     <t>D&amp;A SHIPPING</t>
   </si>
   <si>
-    <t>C«ng ty TNHH D &amp; A Shipping ( ViÖt Nam)</t>
-  </si>
-  <si>
-    <t>9 §­êng sè 1, Ph­êng An L¹c A, QuËn B×nh t©n, Thµnh Phè Hå ChÝ  Minh, ViÖt Nam</t>
+    <t>Công ty TNHH D &amp; A Shipping ( Việt Nam)</t>
+  </si>
+  <si>
+    <t>9 Đường số 1, Phường An Lạc A, Quận Bình tân, Thành Phố Hồ Chí  Minh, Việt Nam</t>
   </si>
   <si>
     <t>0316345811</t>
@@ -1303,10 +1303,10 @@
     <t>DABINHMINH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn §¸ B×nh Minh</t>
-  </si>
-  <si>
-    <t>Sè nhµ 205, ®­êng §iÖn Biªn, Tæ 4, Ph­êng Yªn Ninh, TP. Yªn B¸i, T. Yªn B¸i, VN</t>
+    <t>Công ty cổ phần Đá Bình Minh</t>
+  </si>
+  <si>
+    <t>Số nhà 205, đường Điện Biên, Tổ 4, Phường Yên Ninh, TP. Yên Bái, T. Yên Bái, VN</t>
   </si>
   <si>
     <t>5200811565</t>
@@ -1315,10 +1315,10 @@
     <t>DAIDUONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH ®ãng tµu §¹i D­¬ng</t>
-  </si>
-  <si>
-    <t>Sè 45 - chî §Çm TriÒu - Qu¸n Tr÷ - KiÕn An - HP</t>
+    <t>Công ty TNHH đóng tàu Đại Dương</t>
+  </si>
+  <si>
+    <t>Số 45 - chợ Đầm Triều - Quán Trữ - Kiến An - HP</t>
   </si>
   <si>
     <t>0200655726</t>
@@ -1327,10 +1327,10 @@
     <t>DAIPHAT</t>
   </si>
   <si>
-    <t>C«ng Ty TNHH VËn T¶i BiÓn §¹i Ph¸t</t>
-  </si>
-  <si>
-    <t>Sè 8/161 MiÕu HAi X·, P D­ Hµng Kªnh, Lª ch©n, HP</t>
+    <t>Công Ty TNHH Vận Tải Biển Đại Phát</t>
+  </si>
+  <si>
+    <t>Số 8/161 Miếu HAi Xã, P Dư Hàng Kênh, Lê chân, HP</t>
   </si>
   <si>
     <t>0200838078</t>
@@ -1339,10 +1339,10 @@
     <t>DAISON</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn t­ vÊn vµ th­¬ng m¹i §¹i S¬n</t>
-  </si>
-  <si>
-    <t>Tæ 1 Khu VÜnh Tuy 2 - TT M¹o Khª - H. §«ng TriÒu - TØnh Qu¶ng Ninh</t>
+    <t>Công ty cổ phần tư vấn và thương mại Đại Sơn</t>
+  </si>
+  <si>
+    <t>Tổ 1 Khu Vĩnh Tuy 2 - TT Mạo Khê - H. Đông Triều - Tỉnh Quảng Ninh</t>
   </si>
   <si>
     <t>5700705364</t>
@@ -1351,10 +1351,10 @@
     <t>DAIVU</t>
   </si>
   <si>
-    <t>C«ng ty tr¸ch nhiÖm h÷u han §¹i Vò</t>
-  </si>
-  <si>
-    <t>Sè 3, L« H, Ngâ 19/5 §­êng Lª Th¸nh T«ng, P. M¸y T¬, QuËn Ng« , TP.HP</t>
+    <t>Công ty trách nhiệm hữu han Đại Vũ</t>
+  </si>
+  <si>
+    <t>Số 3, Lô H, Ngõ 19/5 Đường Lê Thánh Tông, P. Máy Tơ, Quận Ngô , TP.HP</t>
   </si>
   <si>
     <t>0200438640</t>
@@ -1372,10 +1372,10 @@
     <t>DANCO</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn t¶i vµ Th­¬ng M¹i Quèc tÕ Danco</t>
-  </si>
-  <si>
-    <t>Sè 342 Lª DuÈn, Ph­êng b¾c S¬n, QuaanjKieens An, Thµnh Phè H¶i Phogf, ViÖt Nam</t>
+    <t>Công ty TNHH Vận tải và Thương Mại Quốc tế Danco</t>
+  </si>
+  <si>
+    <t>Số 342 Lê Duẩn, Phường bắc Sơn, QuaanjKieens An, Thành Phố Hải Phogf, Việt Nam</t>
   </si>
   <si>
     <t>0201635232</t>
@@ -1384,10 +1384,10 @@
     <t>DATTHANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §¹t Thµnh ( ViÖt Nam)</t>
-  </si>
-  <si>
-    <t>X· §«ng L¹c, HuyÖn Nam S¸ch, TØnh H¶i D­¬ng</t>
+    <t>Công ty TNHH Đạt Thành ( Việt Nam)</t>
+  </si>
+  <si>
+    <t>Xã Đông Lạc, Huyện Nam Sách, Tỉnh Hải Dương</t>
   </si>
   <si>
     <t>0800270559</t>
@@ -1396,10 +1396,10 @@
     <t>DAUKHI FGAS</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dÇu khÝ FGAS</t>
-  </si>
-  <si>
-    <t>Sè 36 ngâ 294 Kim M·, QuËn Ba §×nh, Thµnh Phè Hµ Néi, ViÖt Nam</t>
+    <t>Công ty cổ phần dầu khí FGAS</t>
+  </si>
+  <si>
+    <t>Số 36 ngõ 294 Kim Mã, Quận Ba Đình, Thành Phố Hà Nội, Việt Nam</t>
   </si>
   <si>
     <t>0104356931</t>
@@ -1408,10 +1408,10 @@
     <t>DAUKHI VN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Gi¶i Ph¸p DÇu KhÝ ViÖt Nam</t>
-  </si>
-  <si>
-    <t>P1806, TÇng 18, TTTM C¸t Bi Plaza, Sè 1 Lª Hång Phong, P. L¹c Viªn,HP</t>
+    <t>Công ty TNHH Giải Pháp Dầu Khí Việt Nam</t>
+  </si>
+  <si>
+    <t>P1806, Tầng 18, TTTM Cát Bi Plaza, Số 1 Lê Hồng Phong, P. Lạc Viên,HP</t>
   </si>
   <si>
     <t>0200934342</t>
@@ -1420,10 +1420,10 @@
     <t>DAUKHIHAIAU</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn hµng h¶i dÇu khÝ H¶i ¢u</t>
-  </si>
-  <si>
-    <t>159 TrÇn Träng Cung - Khu d©n c­ Nam Long - P. T©n ThuËn §«ng - HCM</t>
+    <t>Công ty cổ phần hàng hải dầu khí Hải Âu</t>
+  </si>
+  <si>
+    <t>159 Trần Trọng Cung - Khu dân cư Nam Long - P. Tân Thuận Đông - HCM</t>
   </si>
   <si>
     <t>0304703484</t>
@@ -1432,10 +1432,10 @@
     <t>DAUKHIHANOI</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i dÇu khÝ Hµ Néi</t>
-  </si>
-  <si>
-    <t>TÇng 5 tßa Oriental Tower, Sè 324 Phè T©y S¬n, P. Ng· T­ Së, Q. §èng §a, TP. HN</t>
+    <t>Công ty cổ phần vận tải dầu khí Hà Nội</t>
+  </si>
+  <si>
+    <t>Tầng 5 tòa Oriental Tower, Số 324 Phố Tây Sơn, P. Ngã Tư Sở, Q. Đống Đa, TP. HN</t>
   </si>
   <si>
     <t>0102396287</t>
@@ -1444,10 +1444,10 @@
     <t>DAUKHIPHUONGDONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i DÇu KhÝ Ph­¬ng §«ng</t>
-  </si>
-  <si>
-    <t>TÇng 6, Sky City Tower A, Sè 88 L¸ng h¹, Ph­êng L¸ng H¹, QuËn §èng §a, TP. Hµ Néi</t>
+    <t>Công ty TNHH Vận Tải Dầu Khí Phương Đông</t>
+  </si>
+  <si>
+    <t>Tầng 6, Sky City Tower A, Số 88 Láng hạ, Phường Láng Hạ, Quận Đống Đa, TP. Hà Nội</t>
   </si>
   <si>
     <t>0109823280</t>
@@ -1456,10 +1456,10 @@
     <t>DAUKHISAOVIET</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn t¶i DÇu KhÝ Sao ViÖt</t>
-  </si>
-  <si>
-    <t>TÇng 3, tßa nhµ Viet Tower, sè 1 phè Th¸i hµ, Ph­êng Trung LiÖt, QuËn §èng §a, HN</t>
+    <t>Công ty TNHH Vận tải Dầu Khí Sao Việt</t>
+  </si>
+  <si>
+    <t>Tầng 3, tòa nhà Viet Tower, số 1 phố Thái hà, Phường Trung Liệt, Quận Đống Đa, HN</t>
   </si>
   <si>
     <t>0109132188</t>
@@ -1474,10 +1474,10 @@
     <t>DBAC</t>
   </si>
   <si>
-    <t>Cty TNHH VËn T¶i &amp; §Çu T­ §«ng B¾c</t>
-  </si>
-  <si>
-    <t>TÇng 8, tµo nhµ 508, Lª Th¸nh T«ng, Ng« QuyÒn - HP</t>
+    <t>Cty TNHH Vận Tải &amp; Đầu Tư Đông Bắc</t>
+  </si>
+  <si>
+    <t>Tầng 8, tào nhà 508, Lê Thánh Tông, Ngô Quyền - HP</t>
   </si>
   <si>
     <t>0200760590</t>
@@ -1510,10 +1510,10 @@
     <t>DIC</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ®Çu t­ vµ th­¬ng m¹i DIC</t>
-  </si>
-  <si>
-    <t>13-13 bis Kú §ång - Ph­êng 9 - QuËn 3 - TP. Hå ChÝ Minh</t>
+    <t>Công ty cổ phần đầu tư và thương mại DIC</t>
+  </si>
+  <si>
+    <t>13-13 bis Kỳ Đồng - Phường 9 - Quận 3 - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0302979487</t>
@@ -1522,10 +1522,10 @@
     <t>DICHVU ASP</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i Vµ DÞch Vô ASP</t>
-  </si>
-  <si>
-    <t>24/600 ®­êng Phó L­¬ng, Phñ Th­îng §o¹n, Ph­êng §«ng H¶i 1, QuËn H¶i An, H¶i Phßng</t>
+    <t>Công ty TNHH Thương Mại Và Dịch Vụ ASP</t>
+  </si>
+  <si>
+    <t>24/600 đường Phú Lương, Phủ Thượng Đoạn, Phường Đông Hải 1, Quận Hải An, Hải Phòng</t>
   </si>
   <si>
     <t>0201562993</t>
@@ -1534,10 +1534,10 @@
     <t>DIENNUOCLAPMAYHP</t>
   </si>
   <si>
-    <t>C«ng ty CP §iÖn N­íc L¾p m¸y H¶i Phßng</t>
-  </si>
-  <si>
-    <t>34 Thiªn L«i - P. NghÜa X· - Q. Lª Ch©n - TP. H¶i Phßng</t>
+    <t>Công ty CP Điện Nước Lắp máy Hải Phòng</t>
+  </si>
+  <si>
+    <t>34 Thiên Lôi - P. Nghĩa Xã - Q. Lê Chân - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200155561</t>
@@ -1546,10 +1546,10 @@
     <t>DIENTUTCL</t>
   </si>
   <si>
-    <t>C«ng ty §iÖn vµ §iÖn Tö TCL ( ViÖt Nam)</t>
-  </si>
-  <si>
-    <t>Xa lé Hµ Néi, Ph­êng T©n Biªn, TP. Biªn Hßa, TØnh §ång Nai, ViÖt Nam</t>
+    <t>Công ty Điện và Điện Tử TCL ( Việt Nam)</t>
+  </si>
+  <si>
+    <t>Xa lộ Hà Nội, Phường Tân Biên, TP. Biên Hòa, Tỉnh Đồng Nai, Việt Nam</t>
   </si>
   <si>
     <t>3600243296</t>
@@ -1558,10 +1558,10 @@
     <t>DKP</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn gi¶i ph¸p tiÕp vËn DKP</t>
-  </si>
-  <si>
-    <t>Sè 5 Lý Tù Träng - QuËn Hång Bµng - TP H¶i Phßng</t>
+    <t>Công ty cổ phần giải pháp tiếp vận DKP</t>
+  </si>
+  <si>
+    <t>Số 5 Lý Tự Trọng - Quận Hồng Bàng - TP Hải Phòng</t>
   </si>
   <si>
     <t>0200672425</t>
@@ -1579,10 +1579,10 @@
     <t>DLHHQN</t>
   </si>
   <si>
-    <t>§¹i lý hµng h¶i Qu¶ng Ninh</t>
-  </si>
-  <si>
-    <t>70 Lª Th¸nh T«ng - TP. H¹ Long</t>
+    <t>Đại lý hàng hải Quảng Ninh</t>
+  </si>
+  <si>
+    <t>70 Lê Thánh Tông - TP. Hạ Long</t>
   </si>
   <si>
     <t>0300437898006</t>
@@ -1591,10 +1591,10 @@
     <t>DNHAN</t>
   </si>
   <si>
-    <t>C«ng Ty Cæ PhÇn ®Çu T­ Vµ Th­¬ng M¹i Doanh Nh©n</t>
-  </si>
-  <si>
-    <t>59 Ph¹m Ngäc Th¹ch - P.6 - QuËn 3 - TP. Hå ChÝ Minh</t>
+    <t>Công Ty Cổ Phần đầu Tư Và Thương Mại Doanh Nhân</t>
+  </si>
+  <si>
+    <t>59 Phạm Ngọc Thạch - P.6 - Quận 3 - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0305130765</t>
@@ -1603,19 +1603,19 @@
     <t>DOANHNHAN</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ®Çu t­ vµ th­¬ng m¹i Doanh Nh©n</t>
-  </si>
-  <si>
-    <t>TÇng 5, tßa nhµ Songdo, 62A Ph¹m Ngäc Th¹ch, Ph­êng 6, QuËn 3, TP.HCM</t>
+    <t>Công ty cổ phần đầu tư và thương mại Doanh Nhân</t>
+  </si>
+  <si>
+    <t>Tầng 5, tòa nhà Songdo, 62A Phạm Ngọc Thạch, Phường 6, Quận 3, TP.HCM</t>
   </si>
   <si>
     <t>DONG JIE</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng m¹i vµ DÞch Vô Dong Jie Mining ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Tæ d©n phos Nam Phong - Ph­êng Kú ThÞnh - ThÞ X· Kú Anh - T. Hµ TÜnh</t>
+    <t>Công ty TNHH Thương mại và Dịch Vụ Dong Jie Mining Việt Nam</t>
+  </si>
+  <si>
+    <t>Tổ dân phos Nam Phong - Phường Kỳ Thịnh - Thị Xã Kỳ Anh - T. Hà Tĩnh</t>
   </si>
   <si>
     <t>3002053203</t>
@@ -1630,10 +1630,10 @@
     <t>DONGANH</t>
   </si>
   <si>
-    <t>C«ng ty CP Kim KhÝ §«ng Anh</t>
-  </si>
-  <si>
-    <t>§«ng Anh, Hµ Néi</t>
+    <t>Công ty CP Kim Khí Đông Anh</t>
+  </si>
+  <si>
+    <t>Đông Anh, Hà Nội</t>
   </si>
   <si>
     <t>0102024056</t>
@@ -1642,10 +1642,10 @@
     <t>DONGBU</t>
   </si>
   <si>
-    <t>C«ng ty TNHH ThÐp Dongbu ViÖt Nam</t>
-  </si>
-  <si>
-    <t>L« CN3.2A, CN3.2B, CN3.1C KCN §×nh Vò, P.§«ng H¶i 2 - Q. H¶i An - HP</t>
+    <t>Công ty TNHH Thép Dongbu Việt Nam</t>
+  </si>
+  <si>
+    <t>Lô CN3.2A, CN3.2B, CN3.1C KCN Đình Vũ, P.Đông Hải 2 - Q. Hải An - HP</t>
   </si>
   <si>
     <t>0201303910</t>
@@ -1654,10 +1654,10 @@
     <t>DONGDUONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËt liÖu tõ §«ng D­¬ng</t>
-  </si>
-  <si>
-    <t>L« C12, KCN Kh¸nh PHó, X· Kh¸nh Phó, HuyÖn Yªn Kh¸nh, TØnh Ninh B×nh, ViÖt Nam</t>
+    <t>Công ty cổ phần vật liệu từ Đông Dương</t>
+  </si>
+  <si>
+    <t>Lô C12, KCN Khánh PHú, Xã Khánh Phú, Huyện Yên Khánh, Tỉnh Ninh Bình, Việt Nam</t>
   </si>
   <si>
     <t>2700618035</t>
@@ -1666,10 +1666,10 @@
     <t>DONGLUC</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i vµ S¶n XuÊt §ång Lùc</t>
-  </si>
-  <si>
-    <t>12/100 NguyÔn BØnh Khiªm - Ph­êng §»ng Giang - QuËn Ng« QuyÒn - Tßngg</t>
+    <t>Công ty TNHH Thương Mại và Sản Xuất Đồng Lực</t>
+  </si>
+  <si>
+    <t>12/100 Nguyễn Bỉnh Khiêm - Phường Đằng Giang - Quận Ngô Quyền - Tòngg</t>
   </si>
   <si>
     <t>0201138248</t>
@@ -1678,10 +1678,10 @@
     <t>DONGNAMA</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i vµ Giao NhËn §«ng Nam ¸</t>
-  </si>
-  <si>
-    <t>Sè 12 NguyÔn ThÞ §Þnh - P. NguyÔn v¨n Cõ - TP. Quy Nh¬n - TØnh B×Þnh</t>
+    <t>Công ty cổ phần vận tải và Giao Nhận Đông Nam á</t>
+  </si>
+  <si>
+    <t>Số 12 Nguyễn Thị Định - P. Nguyễn văn Cừ - TP. Quy Nhơn - Tỉnh Bìịnh</t>
   </si>
   <si>
     <t>4101449663</t>
@@ -1690,10 +1690,10 @@
     <t>DONGNAMPETROVINA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Dong Nam Petrovina</t>
-  </si>
-  <si>
-    <t>KCN §×nh Vò - Ph­êng §«ng h¶i - QuËn h¶i An - H¶i Phßng</t>
+    <t>Công ty TNHH Dong Nam Petrovina</t>
+  </si>
+  <si>
+    <t>KCN Đình Vũ - Phường Đông hải - Quận hải An - Hải Phòng</t>
   </si>
   <si>
     <t xml:space="preserve"> 01</t>
@@ -1720,10 +1720,10 @@
     <t>DTAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH ¤ T« §ång T©m</t>
-  </si>
-  <si>
-    <t>49 Gi¶i Phãng - §ång T©m - Hai Bµ Tr­ng - Hµ Néi</t>
+    <t>Công ty TNHH Ô Tô Đồng Tâm</t>
+  </si>
+  <si>
+    <t>49 Giải Phóng - Đồng Tâm - Hai Bà Trưng - Hà Nội</t>
   </si>
   <si>
     <t>0102363919</t>
@@ -1732,37 +1732,37 @@
     <t>DTC</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇm ®Çu t­ vµ th­¬ng m¹i DTC</t>
-  </si>
-  <si>
-    <t>13-13 Bis Kú §ång - Ph­êng 9 - QuËn 3 - TP. HCM</t>
+    <t>Công ty cổ phầm đầu tư và thương mại DTC</t>
+  </si>
+  <si>
+    <t>13-13 Bis Kỳ Đồng - Phường 9 - Quận 3 - TP. HCM</t>
   </si>
   <si>
     <t>DTHLONG</t>
   </si>
   <si>
-    <t>C«ng ty §ãng Tµu H¹ Long</t>
-  </si>
-  <si>
-    <t>P. GiÕng §¸y - PT H¹ Long - Qu¶ng Ninh</t>
+    <t>Công ty Đóng Tàu Hạ Long</t>
+  </si>
+  <si>
+    <t>P. Giếng Đáy - PT Hạ Long - Quảng Ninh</t>
   </si>
   <si>
     <t>DTPMIENNAM</t>
   </si>
   <si>
-    <t>C«ng Ty Cæ PhÇn §«ng Thiªn Phó MiÒn Nam</t>
-  </si>
-  <si>
-    <t>81-83 ®­êng 11, KDC Him lam 6A - B×nh H­ng - B×nh Ch¸nh - HCM</t>
+    <t>Công Ty Cổ Phần Đông Thiên Phú Miền Nam</t>
+  </si>
+  <si>
+    <t>81-83 đường 11, KDC Him lam 6A - Bình Hưng - Bình Chánh - HCM</t>
   </si>
   <si>
     <t>DTTAIMINH</t>
   </si>
   <si>
-    <t>VP§D c«ng ty TNHH t­ vÊn gi¸o dôc vµ dÞch thuËt Tµi Minh t¹i H¶i HP</t>
-  </si>
-  <si>
-    <t>P501 tßa nhµ Lª Ph¹m sè 98-100 T« HiÖu, P Tr¹i Cau, Lª Ch©n, HP</t>
+    <t>VPĐD công ty TNHH tư vấn giáo dục và dịch thuật Tài Minh tại Hải HP</t>
+  </si>
+  <si>
+    <t>P501 tòa nhà Lê Phạm số 98-100 Tô Hiệu, P Trại Cau, Lê Chân, HP</t>
   </si>
   <si>
     <t>0400510333005</t>
@@ -1771,10 +1771,10 @@
     <t>DUAFAT</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn nÒn mãng §ua Fat</t>
-  </si>
-  <si>
-    <t>Phßng 704, CT8A, KDT V¨n Qu¸n, P. Tróc Lai, Q. Hµ §«ng, TP. hµ Néi</t>
+    <t>Công ty cổ phần nền móng Đua Fat</t>
+  </si>
+  <si>
+    <t>Phòng 704, CT8A, KDT Văn Quán, P. Trúc Lai, Q. Hà Đông, TP. hà Nội</t>
   </si>
   <si>
     <t>0104008162</t>
@@ -1783,10 +1783,10 @@
     <t>DUCPHAT</t>
   </si>
   <si>
-    <t>Cty TNHH TM §øc Ph¸t</t>
-  </si>
-  <si>
-    <t>30D - K40 Gi¶ng Vâ, §èng §a, Hµ Néi</t>
+    <t>Cty TNHH TM Đức Phát</t>
+  </si>
+  <si>
+    <t>30D - K40 Giảng Võ, Đống Đa, Hà Nội</t>
   </si>
   <si>
     <t>0100979910</t>
@@ -1795,10 +1795,10 @@
     <t>DUCTHAI</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn §øc Th¸i</t>
-  </si>
-  <si>
-    <t>Sè 480 Lª Th¸nh T«ng - P. v¹n Mü, Q. Ng« QuyÒn, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần Đức Thái</t>
+  </si>
+  <si>
+    <t>Số 480 Lê Thánh Tông - P. vạn Mỹ, Q. Ngô Quyền, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200606380</t>
@@ -1807,10 +1807,10 @@
     <t>DUNGMON</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Dòng Mon Entertainment</t>
-  </si>
-  <si>
-    <t>Phßng 702 tßa nhµ Lp sè 100 T« HiÖu, Ph­êng Tr¹i Cau, QuËn Lª Ch©n, TP. H¶i PhßngVN</t>
+    <t>Công ty TNHH Dũng Mon Entertainment</t>
+  </si>
+  <si>
+    <t>Phòng 702 tòa nhà Lp số 100 Tô Hiệu, Phường Trại Cau, Quận Lê Chân, TP. Hải PhòngVN</t>
   </si>
   <si>
     <t>0202041087</t>
@@ -1819,10 +1819,10 @@
     <t>DUONGHUY</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Antimon D­¬ng Huy Qu¶ng Nnh ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Th«n 1, x· H¹ long, HuyÖn V©n §ån, tØnh Qu¶ng Ninh</t>
+    <t>Công ty TNHH Antimon Dương Huy Quảng Nnh Việt Nam</t>
+  </si>
+  <si>
+    <t>Thôn 1, xã Hạ long, Huyện Vân Đồn, tỉnh Quảng Ninh</t>
   </si>
   <si>
     <t>5701572741</t>
@@ -1831,16 +1831,16 @@
     <t>DUYENHAI STAR</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Duyªn H¶i Star</t>
+    <t>Công ty TNHH Duyên Hải Star</t>
   </si>
   <si>
     <t>DUYHM</t>
   </si>
   <si>
-    <t>Doanh nghiÖp t­ nh©n Duy Hoµng Minh</t>
-  </si>
-  <si>
-    <t>19 B H¹ Håi, Hoµn kiÕm, Hµ Néi</t>
+    <t>Doanh nghiệp tư nhân Duy Hoàng Minh</t>
+  </si>
+  <si>
+    <t>19 B Hạ Hồi, Hoàn kiếm, Hà Nội</t>
   </si>
   <si>
     <t>0100519286</t>
@@ -1849,10 +1849,10 @@
     <t>DVQUOCTE</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ®Çu t­ th­¬ng m¹i vµ dÞch vô Quèc TÕ</t>
-  </si>
-  <si>
-    <t>Sè 17 ®­êng Ph¹m Hïng, Ph­êng CÇu GiÊy, Thµnh Phè Hµ Néi, ViÖt Nam</t>
+    <t>Công ty cổ phần đầu tư thương mại và dịch vụ Quốc Tế</t>
+  </si>
+  <si>
+    <t>Số 17 đường Phạm Hùng, Phường Cầu Giấy, Thành Phố Hà Nội, Việt Nam</t>
   </si>
   <si>
     <t>0100110052</t>
@@ -1939,10 +1939,10 @@
     <t>EVERICH</t>
   </si>
   <si>
-    <t>CN Cty TNHH Everich ®Êt biÓn t¹i HP</t>
-  </si>
-  <si>
-    <t>254 Lª Th¸nh T«ng, NQ, HP</t>
+    <t>CN Cty TNHH Everich đất biển tại HP</t>
+  </si>
+  <si>
+    <t>254 Lê Thánh Tông, NQ, HP</t>
   </si>
   <si>
     <t>0302042398001</t>
@@ -1975,10 +1975,10 @@
     <t>FEROCROM THANHHOA</t>
   </si>
   <si>
-    <t>C¤NG TY TNHH FEROCROM THANH HOA</t>
-  </si>
-  <si>
-    <t>Tæ d©n phè Liªn S¬n, Ph­êng H¶i Th­îng, thÞ x· Nghi S¬n, Thanh Hãa</t>
+    <t>CÔNG TY TNHH FEROCROM THANH HOA</t>
+  </si>
+  <si>
+    <t>Tổ dân phố Liên Sơn, Phường Hải Thượng, thị xã Nghi Sơn, Thanh Hóa</t>
   </si>
   <si>
     <t>2801148153</t>
@@ -2059,10 +2059,10 @@
     <t>GAHANGHOA ALS</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn nhµ ga hµng ho¸ ALS</t>
-  </si>
-  <si>
-    <t>TÇng 4, Ga hµng ho¸ ALS, C¶ng HKQT Néi Bµi, X· Néi Bµi, TP. Hµ Néi</t>
+    <t>Công ty cổ phần nhà ga hàng hoá ALS</t>
+  </si>
+  <si>
+    <t>Tầng 4, Ga hàng hoá ALS, Cảng HKQT Nội Bài, Xã Nội Bài, TP. Hà Nội</t>
   </si>
   <si>
     <t>0106232917</t>
@@ -2086,10 +2086,10 @@
     <t>GAS VENUS</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Gas Venus</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ngâ 40 ®­êng V¹n B¶o, Ph­êng LiÔu Giai, QuËn Ba §×nh, Thµnh Phè Hµ Néi, ViÖt Nam</t>
+    <t>Công ty TNHH Gas Venus</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ngõ 40 đường Vạn Bảo, Phường Liễu Giai, Quận Ba Đình, Thành Phố Hà Nội, Việt Nam</t>
   </si>
   <si>
     <t>0105162576</t>
@@ -2098,10 +2098,10 @@
     <t>GIAHUNG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn Gia H­ng</t>
-  </si>
-  <si>
-    <t>Sè 85 ®­êng 5 míi - P. Hïng V­¬ng - Q. Hång Bµng - TP. H¶i Phßng</t>
+    <t>Công ty cổ phần Gia Hưng</t>
+  </si>
+  <si>
+    <t>Số 85 đường 5 mới - P. Hùng Vương - Q. Hồng Bàng - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200788155</t>
@@ -2110,10 +2110,10 @@
     <t>GIAIPHAP EZ</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn gi¶i ph¸p E Z</t>
-  </si>
-  <si>
-    <t>P.1109, Tßa nhµ TTC, L« B1A, Côm SX TTCN, P.DÞch Väng, CÇu GiÊy, HN</t>
+    <t>Công ty cổ phần giải pháp E Z</t>
+  </si>
+  <si>
+    <t>P.1109, Tòa nhà TTC, Lô B1A, Cụm SX TTCN, P.Dịch Vọng, Cầu Giấy, HN</t>
   </si>
   <si>
     <t>0105653567</t>
@@ -2122,10 +2122,10 @@
     <t>GIAKHANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Smart House Gia Kh¸nh</t>
-  </si>
-  <si>
-    <t>Khu 7 9 nhµ «ng NguyÔn Ngäc Linh) ph­êng Nam H¶i, QuËn H¶i An, TPßngg</t>
+    <t>Công ty TNHH Smart House Gia Khánh</t>
+  </si>
+  <si>
+    <t>Khu 7 9 nhà ông Nguyễn Ngọc Linh) phường Nam Hải, Quận Hải An, TPòngg</t>
   </si>
   <si>
     <t>0201777188</t>
@@ -2134,10 +2134,10 @@
     <t>GIALAI</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn n«ng nghiÖp Agris Gia Lai</t>
-  </si>
-  <si>
-    <t>561 TrÇn H­ng §¹o - Ph­êng Ayunpa, tØnh Gia Lai, ViÖt Nam</t>
+    <t>Công ty cổ phần nông nghiệp Agris Gia Lai</t>
+  </si>
+  <si>
+    <t>561 Trần Hưng Đạo - Phường Ayunpa, tỉnh Gia Lai, Việt Nam</t>
   </si>
   <si>
     <t>5900421955</t>
@@ -2146,10 +2146,10 @@
     <t>GIAONHAN AV</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng m¹i vµ Giao NhËn AV</t>
-  </si>
-  <si>
-    <t>Sè 1/115 Ph­¬ng L­u, Ph­êng Ng« QuyÒn, TP H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Thương mại và Giao Nhận AV</t>
+  </si>
+  <si>
+    <t>Số 1/115 Phương Lưu, Phường Ngô Quyền, TP Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0202116800</t>
@@ -2158,10 +2158,10 @@
     <t>GIAPHAM</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn hãa chÊt Gia Ph¹m</t>
-  </si>
-  <si>
-    <t>Phßng 501, sè 156 Vò Ph¹m Hµm, Ph­êng Yªn Hßa, Q.CÇu GiÊy, TP.Hµ Néi</t>
+    <t>Công ty cổ phần hóa chất Gia Phạm</t>
+  </si>
+  <si>
+    <t>Phòng 501, số 156 Vũ Phạm Hàm, Phường Yên Hòa, Q.Cầu Giấy, TP.Hà Nội</t>
   </si>
   <si>
     <t>0107733338</t>
@@ -2170,10 +2170,10 @@
     <t>GIAPHAT</t>
   </si>
   <si>
-    <t>Cty CP TM &amp; DV Gia Ph¸t</t>
-  </si>
-  <si>
-    <t>16/83 Chïa Hµng, Hå Nam, Lª Ch©n, HP</t>
+    <t>Cty CP TM &amp; DV Gia Phát</t>
+  </si>
+  <si>
+    <t>16/83 Chùa Hàng, Hồ Nam, Lê Chân, HP</t>
   </si>
   <si>
     <t>0200766514</t>
@@ -2182,10 +2182,10 @@
     <t>GIASAN IWEALTH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §Çu T­ Gia S¶n IWEALTH</t>
-  </si>
-  <si>
-    <t>Sè 15 Phè §µo Duy Tõ, Ph­êng Hµng Buåm, QuËn Hoµn KiÕm, Thµnh Phè Hµ Néi, ViÖt Nam</t>
+    <t>Công ty TNHH Đầu Tư Gia Sản IWEALTH</t>
+  </si>
+  <si>
+    <t>Số 15 Phố Đào Duy Từ, Phường Hàng Buồm, Quận Hoàn Kiếm, Thành Phố Hà Nội, Việt Nam</t>
   </si>
   <si>
     <t>1101612106</t>
@@ -2212,16 +2212,16 @@
     <t>GMDHCM</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn tiÕp vËn Gemadept</t>
+    <t>Công ty cổ phần tiếp vận Gemadept</t>
   </si>
   <si>
     <t>GMHCM</t>
   </si>
   <si>
-    <t>C«ng Ty Cæ PhÇn Gemadept</t>
-  </si>
-  <si>
-    <t>2 Bis - 4- 6 Lª Th¸nh T«n, P BÕn NghÐ, QuËn 01, HCM</t>
+    <t>Công Ty Cổ Phần Gemadept</t>
+  </si>
+  <si>
+    <t>2 Bis - 4- 6 Lê Thánh Tôn, P Bến Nghé, Quận 01, HCM</t>
   </si>
   <si>
     <t>GOLD</t>
@@ -2233,10 +2233,10 @@
     <t>GOLDMARINE</t>
   </si>
   <si>
-    <t>C¤NG TY TNHH GOLD MARINE</t>
-  </si>
-  <si>
-    <t>Sè nhµ 5, ®­êng Hoa S÷a 07, Vinhomes Riveride, Ph­êng Phóc Lîi, quËn Long Biªn,HN</t>
+    <t>CÔNG TY TNHH GOLD MARINE</t>
+  </si>
+  <si>
+    <t>Số nhà 5, đường Hoa Sữa 07, Vinhomes Riveride, Phường Phúc Lợi, quận Long Biên,HN</t>
   </si>
   <si>
     <t>0313610229</t>
@@ -2299,16 +2299,16 @@
     <t>Green Pine Shipping Co; Ltd</t>
   </si>
   <si>
-    <t>Trung Quèc</t>
+    <t>Trung Quốc</t>
   </si>
   <si>
     <t>GREENSKY LOGISTICS</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Greensky Logistics ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 17, ngâ 529, §­êng 72, TDP Trung B×nh, Ph­êng D­¬ng Néi, QuËn Hµ §«ng, TP. HN</t>
+    <t>Công ty TNHH Greensky Logistics Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 17, ngõ 529, Đường 72, TDP Trung Bình, Phường Dương Nội, Quận Hà Đông, TP. HN</t>
   </si>
   <si>
     <t>0109475964</t>
@@ -2335,10 +2335,10 @@
     <t>GUOXIANG HP</t>
   </si>
   <si>
-    <t>C«ng ty TNHH GUOXIANG H¶i Phßng</t>
-  </si>
-  <si>
-    <t>L« I8 - KCN Nomura, X· An H­ng - HuyÖn An D­¬ng - TP. H¶i Phßng</t>
+    <t>Công ty TNHH GUOXIANG Hải Phòng</t>
+  </si>
+  <si>
+    <t>Lô I8 - KCN Nomura, Xã An Hưng - Huyện An Dương - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201648545</t>
@@ -2347,10 +2347,10 @@
     <t>H AU</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dÞch vô hµng h¶i H¶i ¢U</t>
-  </si>
-  <si>
-    <t>TÇng 7 - Toµ Nhµ LP - Sè 508 Lª Th¸nh T«ng - Ng« QuyÒn - H¶i Phßng</t>
+    <t>Công ty cổ phần dịch vụ hàng hải Hải ÂU</t>
+  </si>
+  <si>
+    <t>Tầng 7 - Toà Nhà LP - Số 508 Lê Thánh Tông - Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0201234801</t>
@@ -2359,10 +2359,10 @@
     <t>H&amp;B</t>
   </si>
   <si>
-    <t>C«ng ty TNHH x©y dùng vµ TM H &amp; B</t>
-  </si>
-  <si>
-    <t>33D, C¸t Linh, §èng §a, Hµ Néi</t>
+    <t>Công ty TNHH xây dựng và TM H &amp; B</t>
+  </si>
+  <si>
+    <t>33D, Cát Linh, Đống Đa, Hà Nội</t>
   </si>
   <si>
     <t>0101101879</t>
@@ -2371,10 +2371,10 @@
     <t>H.ANH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i biÓn Hoµng Anh</t>
-  </si>
-  <si>
-    <t>H¹ §o¹n II - §«ng H¶i II - H¶i An - H¶i Phßng</t>
+    <t>Công ty cổ phần vận tải biển Hoàng Anh</t>
+  </si>
+  <si>
+    <t>Hạ Đoạn II - Đông Hải II - Hải An - Hải Phòng</t>
   </si>
   <si>
     <t>0200861013</t>
@@ -2383,10 +2383,10 @@
     <t>HAHAI</t>
   </si>
   <si>
-    <t>C«ng ty CP DV &amp; vËn t¶i Hµ H¶i</t>
-  </si>
-  <si>
-    <t>P105, C4, TT Quúnh Mai, hai Bµ Tr­ng, HN</t>
+    <t>Công ty CP DV &amp; vận tải Hà Hải</t>
+  </si>
+  <si>
+    <t>P105, C4, TT Quỳnh Mai, hai Bà Trưng, HN</t>
   </si>
   <si>
     <t>0101491925</t>
@@ -2395,10 +2395,10 @@
     <t>HAIHA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH vËn t¶i thuû bé H¶i Hµ</t>
-  </si>
-  <si>
-    <t>Sè 132 Khu 6 - Diªm §iÒn - Th¸i Thuþ - Th¸i B×nh</t>
+    <t>Công ty TNHH vận tải thuỷ bộ Hải Hà</t>
+  </si>
+  <si>
+    <t>Số 132 Khu 6 - Diêm Điền - Thái Thuỵ - Thái Bình</t>
   </si>
   <si>
     <t>1000336805</t>
@@ -2407,10 +2407,10 @@
     <t>HAINAM</t>
   </si>
   <si>
-    <t>C«ng Ty TNHH §¹i Lý Tµu BiÓn H¶i Nam</t>
-  </si>
-  <si>
-    <t>Huúnh Kh­¬ng An - P.3 - TP. Vòng Tµu</t>
+    <t>Công Ty TNHH Đại Lý Tàu Biển Hải Nam</t>
+  </si>
+  <si>
+    <t>Huỳnh Khương An - P.3 - TP. Vũng Tàu</t>
   </si>
   <si>
     <t>3500545991</t>
@@ -2419,10 +2419,10 @@
     <t>HAIPHAT</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng vËn H¶i Ph¸t</t>
-  </si>
-  <si>
-    <t>SN3 g¸c 2 ngâ 15, Phè Ph¹m Hång Th¸i, Ph­êng Phan Béi Ch©u, QuËn Hång Bµng, HP</t>
+    <t>Công ty cổ phần thương vận Hải Phát</t>
+  </si>
+  <si>
+    <t>SN3 gác 2 ngõ 15, Phố Phạm Hồng Thái, Phường Phan Bội Châu, Quận Hồng Bàng, HP</t>
   </si>
   <si>
     <t>0201293589</t>
@@ -2431,10 +2431,10 @@
     <t>HAIPHUONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn t¶i H¶i Ph­¬ng</t>
-  </si>
-  <si>
-    <t>Sè 94 No 4/97 B¹ch §»ng - P. h¹ Lý - Q. Hång bµng - H¶i Phßng</t>
+    <t>Công ty TNHH Vận tải Hải Phương</t>
+  </si>
+  <si>
+    <t>Số 94 No 4/97 Bạch Đằng - P. hạ Lý - Q. Hồng bàng - Hải Phòng</t>
   </si>
   <si>
     <t>0600337799</t>
@@ -2443,10 +2443,10 @@
     <t>HAITHANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TiÕp VËn H¶i Thµnh</t>
-  </si>
-  <si>
-    <t>Sè 107/36 C8 V¹n Mü, Ph­êng V¹n Mü, QuËn Ng« QuyÒn, TP. H¶i Phßng</t>
+    <t>Công ty TNHH Tiếp Vận Hải Thành</t>
+  </si>
+  <si>
+    <t>Số 107/36 C8 Vạn Mỹ, Phường Vạn Mỹ, Quận Ngô Quyền, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201911362</t>
@@ -2455,10 +2455,10 @@
     <t>HAITIEN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i BiÓn H¶i Tiªn</t>
-  </si>
-  <si>
-    <t>50/3 D©n Chñ - KP3 - P. B×nh Thä - Q. Thñ §øc - TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH Vận Tải Biển Hải Tiên</t>
+  </si>
+  <si>
+    <t>50/3 Dân Chủ - KP3 - P. Bình Thọ - Q. Thủ Đức - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0305304323</t>
@@ -2467,10 +2467,10 @@
     <t>HALINH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ®Çu t­ th­¬ng m¹i Hµ Linh</t>
-  </si>
-  <si>
-    <t>Sè 56 C¶ng Míi  - Thµnh Phè H¹ Long - TØnh Qu¶ng Ninh</t>
+    <t>Công ty cổ phần đầu tư thương mại Hà Linh</t>
+  </si>
+  <si>
+    <t>Số 56 Cảng Mới  - Thành Phố Hạ Long - Tỉnh Quảng Ninh</t>
   </si>
   <si>
     <t>5701311524</t>
@@ -2485,16 +2485,16 @@
     <t>HANGHAI H.D</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Hµng H¶i H.D</t>
+    <t>Công ty TNHH Hàng Hải H.D</t>
   </si>
   <si>
     <t>HANGHAI MD</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn Hµng H¶i MD</t>
-  </si>
-  <si>
-    <t>Sè 5/44 Lª Lai, Ph­êng L¹c Viªn, QuËn Ng« QuyÒn, H¶i Phßng</t>
+    <t>Công ty cổ phần Hàng Hải MD</t>
+  </si>
+  <si>
+    <t>Số 5/44 Lê Lai, Phường Lạc Viên, Quận Ngô Quyền, Hải Phòng</t>
   </si>
   <si>
     <t>0201905048</t>
@@ -2503,10 +2503,10 @@
     <t>HANGHAI S&amp;A</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn hµng h¶i S &amp; A</t>
-  </si>
-  <si>
-    <t>Sè 64, Tæ 4 , Khu 6A, P. CÈm Trung , TP. CÈm Ph¶ , TØnh Qu¶ng Ninh</t>
+    <t>Công ty cổ phần hàng hải S &amp; A</t>
+  </si>
+  <si>
+    <t>Số 64, Tổ 4 , Khu 6A, P. Cẩm Trung , TP. Cẩm Phả , Tỉnh Quảng Ninh</t>
   </si>
   <si>
     <t>5701692799</t>
@@ -2515,10 +2515,10 @@
     <t>HANGHAI SUNRISE</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dÞch vô hµng h¶i Sunrise</t>
-  </si>
-  <si>
-    <t>Sè 243, phè Ph¹m Ngäc Th¹ch, Ph­êng Cao Xanh, TP. H¹ Long, T. QN</t>
+    <t>Công ty cổ phần dịch vụ hàng hải Sunrise</t>
+  </si>
+  <si>
+    <t>Số 243, phố Phạm Ngọc Thạch, Phường Cao Xanh, TP. Hạ Long, T. QN</t>
   </si>
   <si>
     <t>5701847604</t>
@@ -2527,10 +2527,10 @@
     <t>HANGHAIACHAU</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn thiÕt bÞ vµ dÞch vô hµng h¶i ¸ Ch©u</t>
-  </si>
-  <si>
-    <t>TÇng 7, Tßa nhµ Thµnh §¹t 1, sè 3 Lª Th¸nh T«ng, Ph­êng M¸y T¬, QuËn Ng« QuyÒn, HP</t>
+    <t>Công ty cổ phần thiết bị và dịch vụ hàng hải á Châu</t>
+  </si>
+  <si>
+    <t>Tầng 7, Tòa nhà Thành Đạt 1, số 3 Lê Thánh Tông, Phường Máy Tơ, Quận Ngô Quyền, HP</t>
   </si>
   <si>
     <t>0201725831</t>
@@ -2539,10 +2539,10 @@
     <t>HANGHAIDONGDO</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn hµng h¶i §«ng §«</t>
-  </si>
-  <si>
-    <t>TÇng 19 th¸p VPQT Hßa B×nh, Sè 106 Hoµng Quèc ViÖt, P. NghÜa §«, QuËn CÇu GiÊy, HN</t>
+    <t>Công ty cổ phần hàng hải Đông Đô</t>
+  </si>
+  <si>
+    <t>Tầng 19 tháp VPQT Hòa Bình, Số 106 Hoàng Quốc Việt, P. Nghĩa Đô, Quận Cầu Giấy, HN</t>
   </si>
   <si>
     <t>0100105253</t>
@@ -2551,16 +2551,16 @@
     <t>HANGHAIHAIDANG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Hµng H¶i H¶i §¨ng</t>
+    <t>Công ty TNHH Hàng Hải Hải Đăng</t>
   </si>
   <si>
     <t>HANGHAIISM</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dÞch vô hµng h¶i ISM ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 70 M¹c QuyÕt, Ph­êng Anh Dòng, QuËn D­¬ng Kinh, TP. H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty cổ phần dịch vụ hàng hải ISM Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 70 Mạc Quyết, Phường Anh Dũng, Quận Dương Kinh, TP. Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0201896668</t>
@@ -2569,7 +2569,7 @@
     <t>HANGHAIT&amp;T</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §¹i Lý hµng H¶i T &amp; T</t>
+    <t>Công ty TNHH Đại Lý hàng Hải T &amp; T</t>
   </si>
   <si>
     <t>HANGKANG</t>
@@ -2581,19 +2581,19 @@
     <t>HANGKENH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn hµng kªnh</t>
-  </si>
-  <si>
-    <t>Sè 124 NguyÔn §øc C¶nh - P. C¸t Dµi, QuËn Lª Ch©n, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần hàng kênh</t>
+  </si>
+  <si>
+    <t>Số 124 Nguyễn Đức Cảnh - P. Cát Dài, Quận Lê Chân, TP. Hải Phòng</t>
   </si>
   <si>
     <t>HANGTHINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH th­¬ng m¹i dÞch vô H»ng ThÞnh</t>
-  </si>
-  <si>
-    <t>Sè 43/38 An §µ, L¹ch Tray, Ng« QuyÒn, H¶i Phßng</t>
+    <t>Công ty TNHH thương mại dịch vụ Hằng Thịnh</t>
+  </si>
+  <si>
+    <t>Số 43/38 An Đà, Lạch Tray, Ngô Quyền, Hải Phòng</t>
   </si>
   <si>
     <t>0201161783</t>
@@ -2611,10 +2611,10 @@
     <t>HANOSIMEX</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i H¶i Phßng - Hanosimex</t>
-  </si>
-  <si>
-    <t>Sè 508 Lª Th¸nh T«ng, ph­êng Ng« QuyÒn - Thµnh Phè H¶i Phßng - ViÖt Nam</t>
+    <t>Công ty cổ phần thương mại Hải Phòng - Hanosimex</t>
+  </si>
+  <si>
+    <t>Số 508 Lê Thánh Tông, phường Ngô Quyền - Thành Phố Hải Phòng - Việt Nam</t>
   </si>
   <si>
     <t>0200736929</t>
@@ -2638,10 +2638,10 @@
     <t>HATRANG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i DÇu KhÝ Hµ Trang</t>
-  </si>
-  <si>
-    <t>Sè 75, ngâ 119, §­êng Gi¸p B¸t, Ph­êng Gi¸p B¸t, QuËn Hoµng Mai, Thµnh Phè Hµ Néi</t>
+    <t>Công ty TNHH Vận Tải Dầu Khí Hà Trang</t>
+  </si>
+  <si>
+    <t>Số 75, ngõ 119, Đường Giáp Bát, Phường Giáp Bát, Quận Hoàng Mai, Thành Phố Hà Nội</t>
   </si>
   <si>
     <t>0109988726</t>
@@ -2653,7 +2653,7 @@
     <t>Cty TNHH TM HATUNA</t>
   </si>
   <si>
-    <t>Minh Bét, Minh N«ng, ViÖt Tr×, Phó Thä</t>
+    <t>Minh Bột, Minh Nông, Việt Trì, Phú Thọ</t>
   </si>
   <si>
     <t>2600407094</t>
@@ -2677,10 +2677,10 @@
     <t>HHDUONGBIEN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Mét Thµnh Viªn §¹i Lý Hµng H¶i §­êng BiÓn</t>
-  </si>
-  <si>
-    <t>Phßng TS2.02.01 tÇng 2, Khèi th¸p TS2, 39-39B BÕn V©n §ån, Ph­êng Xãm ChiÕu, TP HCM, VN</t>
+    <t>Công ty TNHH Một Thành Viên Đại Lý Hàng Hải Đường Biển</t>
+  </si>
+  <si>
+    <t>Phòng TS2.02.01 tầng 2, Khối tháp TS2, 39-39B Bến Vân Đồn, Phường Xóm Chiếu, TP HCM, VN</t>
   </si>
   <si>
     <t>0312593725</t>
@@ -2689,10 +2689,10 @@
     <t>HHHDUONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Hµng H¶i H¶i D­¬ng</t>
-  </si>
-  <si>
-    <t>Sè 186 l« 9 më réng, Ph­êng §»ng h¶i, QuËn H¶i An, Thµnh Phè H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Hàng Hải Hải Dương</t>
+  </si>
+  <si>
+    <t>Số 186 lô 9 mở rộng, Phường Đằng hải, Quận Hải An, Thành Phố Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0201586151</t>
@@ -2701,10 +2701,10 @@
     <t>HHHOANGGIA</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn hµng h¶i Hoµng Gia</t>
-  </si>
-  <si>
-    <t>Sè 45 Lý Th­êng KiÖt - Ph­êng Quang Trung - Q. Hång Bµng - H¶i Phßng</t>
+    <t>Công ty cổ phần hàng hải Hoàng Gia</t>
+  </si>
+  <si>
+    <t>Số 45 Lý Thường Kiệt - Phường Quang Trung - Q. Hồng Bàng - Hải Phòng</t>
   </si>
   <si>
     <t>0201112666</t>
@@ -2713,10 +2713,10 @@
     <t>HHNHATANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i Hµng H¶i NhËt Anh</t>
-  </si>
-  <si>
-    <t>Sè 13/82 Lª lai - Ph­êng l¹c Viªn - QuËn Ng« QuyÒn - H¶i Phßng</t>
+    <t>Công ty TNHH Thương Mại Hàng Hải Nhật Anh</t>
+  </si>
+  <si>
+    <t>Số 13/82 Lê lai - Phường lạc Viên - Quận Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0201617762</t>
@@ -2725,10 +2725,10 @@
     <t>HHOCEANIC</t>
   </si>
   <si>
-    <t>C«ng ty TNHH dÞch vô hµng h¶i vµ ®¹i lý Oceanic</t>
-  </si>
-  <si>
-    <t>212 B/1 NguyÔn Tr·i - Ph­êng NguyÔn C¬ Trinh - QuËn 1 - TP. HCM</t>
+    <t>Công ty TNHH dịch vụ hàng hải và đại lý Oceanic</t>
+  </si>
+  <si>
+    <t>212 B/1 Nguyễn Trãi - Phường Nguyễn Cơ Trinh - Quận 1 - TP. HCM</t>
   </si>
   <si>
     <t>0312784776</t>
@@ -2737,10 +2737,10 @@
     <t>HHPHC</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Hµng H¶i PHC</t>
-  </si>
-  <si>
-    <t>Sè 2/3C ®­êng Lª Hång Phong - P. §«ng Khª - Q. Ng« QuyÒn - h¶i Phßng</t>
+    <t>Công ty TNHH Hàng Hải PHC</t>
+  </si>
+  <si>
+    <t>Số 2/3C đường Lê Hồng Phong - P. Đông Khê - Q. Ngô Quyền - hải Phòng</t>
   </si>
   <si>
     <t>0201583288</t>
@@ -2749,10 +2749,10 @@
     <t>HHPHIANAM</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dich vô hµng h¶i PhÝa Nam</t>
-  </si>
-  <si>
-    <t>Sè 4 TrÇn Träng Cung, Ph­êng T©n ThuËn §«ng, QuËn 7, TP. HCM</t>
+    <t>Công ty cổ phần dich vụ hàng hải Phía Nam</t>
+  </si>
+  <si>
+    <t>Số 4 Trần Trọng Cung, Phường Tân Thuận Đông, Quận 7, TP. HCM</t>
   </si>
   <si>
     <t>0312648533</t>
@@ -2761,10 +2761,10 @@
     <t>HHQUANGNINH</t>
   </si>
   <si>
-    <t>CN C«ng ty CP §¹i Lý Hµng H¶i ViÖt Nam - §¹i lý hµng h¶i Qu¶ng Ninh</t>
-  </si>
-  <si>
-    <t>Sè 70, ®­êng Lª Th¸nh T«ng, Ph­êng Hång Gai, TP. H¹ Long,TØnh Qu¶ng Ninh, ViÖt Nam</t>
+    <t>CN Công ty CP Đại Lý Hàng Hải Việt Nam - Đại lý hàng hải Quảng Ninh</t>
+  </si>
+  <si>
+    <t>Số 70, đường Lê Thánh Tông, Phường Hồng Gai, TP. Hạ Long,Tỉnh Quảng Ninh, Việt Nam</t>
   </si>
   <si>
     <t>0300437898-006</t>
@@ -2773,10 +2773,10 @@
     <t>HHSAIGON</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn hµng h¶i Sµi Gßn</t>
-  </si>
-  <si>
-    <t>422 NguyÔn tÊt Thµnh, Ph­êng 18, QuËn 4, TP. Hå ChÝ Minh</t>
+    <t>Công ty cổ phần hàng hải Sài Gòn</t>
+  </si>
+  <si>
+    <t>422 Nguyễn tất Thành, Phường 18, Quận 4, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0302590764</t>
@@ -2785,10 +2785,10 @@
     <t>HHTHIENBINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i &amp; Hµng h¶i Thiªn B×nh</t>
-  </si>
-  <si>
-    <t>P1906, tÇng 19, TTTM C¸t Bi Plaza, Sè 1 Lª Hång Phong, P. L¹cPViªn,HP</t>
+    <t>Công ty TNHH Thương Mại &amp; Hàng hải Thiên Bình</t>
+  </si>
+  <si>
+    <t>P1906, tầng 19, TTTM Cát Bi Plaza, Số 1 Lê Hồng Phong, P. LạcPViên,HP</t>
   </si>
   <si>
     <t>1001012472</t>
@@ -2797,19 +2797,19 @@
     <t>HHVIETSTAR</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ®¹i lý hµng h¶i Vietstar</t>
-  </si>
-  <si>
-    <t>Qu¶ng Ninh</t>
+    <t>Công ty cổ phần đại lý hàng hải Vietstar</t>
+  </si>
+  <si>
+    <t>Quảng Ninh</t>
   </si>
   <si>
     <t>HHVINA</t>
   </si>
   <si>
-    <t>C«ng Ty Hµng H¶i Vinashin</t>
-  </si>
-  <si>
-    <t>TÇng 12 Tßa Nhµ S«ng §µ - CÇu GiÊy - Hµ Néi - ViÖt Nam</t>
+    <t>Công Ty Hàng Hải Vinashin</t>
+  </si>
+  <si>
+    <t>Tầng 12 Tòa Nhà Sông Đà - Cầu Giấy - Hà Nội - Việt Nam</t>
   </si>
   <si>
     <t>0101815295</t>
@@ -2818,10 +2818,10 @@
     <t>HHVN</t>
   </si>
   <si>
-    <t>CN Tæng c«ng ty Hµng H¶i ViÖt nam t¹i Hå chÝ Minh</t>
-  </si>
-  <si>
-    <t>163 NguyÔn V¨n Trçii -P11,  QuËn Phó NhuËn - TP. Hå ChÝ Minh</t>
+    <t>CN Tổng công ty Hàng Hải Việt nam tại Hồ chí Minh</t>
+  </si>
+  <si>
+    <t>163 Nguyễn Văn Trỗii -P11,  Quận Phú Nhuận - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0100104595-002</t>
@@ -2830,10 +2830,10 @@
     <t>HIEPPHONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH HiÖp Phong ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Km 9 ®­êng Ph¹m V¨n §ång - P. h¶i Thµnh - Q. D­¬ng Kinh - TP. HP</t>
+    <t>Công ty TNHH Hiệp Phong Việt Nam</t>
+  </si>
+  <si>
+    <t>Km 9 đường Phạm Văn Đồng - P. hải Thành - Q. Dương Kinh - TP. HP</t>
   </si>
   <si>
     <t>0200633803</t>
@@ -2842,10 +2842,10 @@
     <t>HIEPT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH V«i HiÖp Thµnh</t>
-  </si>
-  <si>
-    <t>A24 A/6 Êp 1 X· h­ng Long - HuyÖn B×nh Ch¸nh</t>
+    <t>Công ty TNHH Vôi Hiệp Thành</t>
+  </si>
+  <si>
+    <t>A24 A/6 ấp 1 Xã hưng Long - Huyện Bình Chánh</t>
   </si>
   <si>
     <t>0303847620</t>
@@ -2854,10 +2854,10 @@
     <t>HIGHSEA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §¹i lý VËn T¶i High Sea</t>
-  </si>
-  <si>
-    <t>28 §Æng Thai Mai, Ph­êng 7, QuËn Phó NhuËn, TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH Đại lý Vận Tải High Sea</t>
+  </si>
+  <si>
+    <t>28 Đặng Thai Mai, Phường 7, Quận Phú Nhuận, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0309837957</t>
@@ -2866,10 +2866,10 @@
     <t>HITACHITRANSPORT</t>
   </si>
   <si>
-    <t>Chi nh¸nh c«ng ty TNHH Hitachi Transport System (ViÖt Nam) t¹i Hµ Néi</t>
-  </si>
-  <si>
-    <t>Phßng 1804, tÇng 18, Tßa nhµ V¨n Phßng Th¨ng Long, P. Nh©n ChÝnh, Q. Thanh Xu©n, HN</t>
+    <t>Chi nhánh công ty TNHH Hitachi Transport System (Việt Nam) tại Hà Nội</t>
+  </si>
+  <si>
+    <t>Phòng 1804, tầng 18, Tòa nhà Văn Phòng Thăng Long, P. Nhân Chính, Q. Thanh Xuân, HN</t>
   </si>
   <si>
     <t>0311333675-001</t>
@@ -2884,10 +2884,10 @@
     <t>HK LINE</t>
   </si>
   <si>
-    <t>C«ng ty TNHH HK Line</t>
-  </si>
-  <si>
-    <t>Sè 275 ®­êng L¹ch Tray, ph­êng Gia Viªn, TP H¶i Phßng, ViÖt Nam.</t>
+    <t>Công ty TNHH HK Line</t>
+  </si>
+  <si>
+    <t>Số 275 đường Lạch Tray, phường Gia Viên, TP Hải Phòng, Việt Nam.</t>
   </si>
   <si>
     <t>0202150255</t>
@@ -2902,10 +2902,10 @@
     <t>HLT</t>
   </si>
   <si>
-    <t>C«ng ty CP ph¸t triÓn TM HLT</t>
-  </si>
-  <si>
-    <t>Ngâ 267/2/75 nhµ sè 29, Hoµng Hoa Th¸m, LiÔu Giai, B§, HN</t>
+    <t>Công ty CP phát triển TM HLT</t>
+  </si>
+  <si>
+    <t>Ngõ 267/2/75 nhà số 29, Hoàng Hoa Thám, Liễu Giai, BĐ, HN</t>
   </si>
   <si>
     <t>0102459307</t>
@@ -2914,10 +2914,10 @@
     <t>HMINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Kim KhÝ Hoµng Minh</t>
-  </si>
-  <si>
-    <t>71A4 B¾c NghÜa T©n, CÇu GiÊy, Hµ Néi</t>
+    <t>Công ty TNHH Kim Khí Hoàng Minh</t>
+  </si>
+  <si>
+    <t>71A4 Bắc Nghĩa Tân, Cầu Giấy, Hà Nội</t>
   </si>
   <si>
     <t>0101234942</t>
@@ -2926,10 +2926,10 @@
     <t>HNL</t>
   </si>
   <si>
-    <t>Doanh NghiÖp T­ Nh©n Hµ Nam Linh</t>
-  </si>
-  <si>
-    <t>A7/96 §­êng 41 - P. Phó Thä Hoµ - Q. T©n Phó - TP. Hå ChÝ Minh</t>
+    <t>Doanh Nghiệp Tư Nhân Hà Nam Linh</t>
+  </si>
+  <si>
+    <t>A7/96 Đường 41 - P. Phú Thọ Hoà - Q. Tân Phú - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0309903670</t>
@@ -2938,10 +2938,10 @@
     <t>HOABAN</t>
   </si>
   <si>
-    <t>Cty Cæ PhÇn Th­¬ng M¹i Hoa Ban</t>
-  </si>
-  <si>
-    <t>X· ViÖt Hoµ - TP. H¶i D­¬ng - T. H¶i D­¬ng</t>
+    <t>Cty Cổ Phần Thương Mại Hoa Ban</t>
+  </si>
+  <si>
+    <t>Xã Việt Hoà - TP. Hải Dương - T. Hải Dương</t>
   </si>
   <si>
     <t>0800394480</t>
@@ -2950,19 +2950,19 @@
     <t>HOABINH68</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ®Çu t­ ph¸t triÓn Hoµ B×nh 68</t>
-  </si>
-  <si>
-    <t>Sè 38 ®­êng Lª C«ng Thnah, Ph­êng Phñ Lý, TØnh Ninh B×nh, ViÖt Nam</t>
+    <t>Công ty cổ phần đầu tư phát triển Hoà Bình 68</t>
+  </si>
+  <si>
+    <t>Số 38 đường Lê Công Thnah, Phường Phủ Lý, Tỉnh Ninh Bình, Việt Nam</t>
   </si>
   <si>
     <t>HOACHATACHAU</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn bÊt ®éng s¶n s¬n vµ ho¸ chÊt ¸ Ch©u</t>
-  </si>
-  <si>
-    <t>Sè 12 §­êng L¹ch Tray, Ph­êng L¹ch tray, Q. Ng« QuyÒn, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần bất động sản sơn và hoá chất á Châu</t>
+  </si>
+  <si>
+    <t>Số 12 Đường Lạch Tray, Phường Lạch tray, Q. Ngô Quyền, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200988891</t>
@@ -2971,10 +2971,10 @@
     <t>HOADAUQD</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn hãa dÇu hãa dÇu Qu©n §éi</t>
-  </si>
-  <si>
-    <t>SèN1- 33B Ph¹m Ngò L·o, P Phan Chu Trinh, Q Hoµn KiÕm, TP Hµ Néi</t>
+    <t>Công ty cổ phần hóa dầu hóa dầu Quân Đội</t>
+  </si>
+  <si>
+    <t>SốN1- 33B Phạm Ngũ Lão, P Phan Chu Trinh, Q Hoàn Kiếm, TP Hà Nội</t>
   </si>
   <si>
     <t>0101436307</t>
@@ -2983,10 +2983,10 @@
     <t>HOALAN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH d­îc phÈm Hoa Lan</t>
-  </si>
-  <si>
-    <t>63D5 khu ®« thÞ míi §¹i Kim, Hoµng Mai, Hµ Néi</t>
+    <t>Công ty TNHH dược phẩm Hoa Lan</t>
+  </si>
+  <si>
+    <t>63D5 khu đô thị mới Đại Kim, Hoàng Mai, Hà Nội</t>
   </si>
   <si>
     <t>0101189270</t>
@@ -2995,10 +2995,10 @@
     <t>HOANGANHPHAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i vµ DÞch Vô VËn T¶i Hoµng Anh Ph¸t</t>
-  </si>
-  <si>
-    <t>Sè 2/97 CÇu C¸p, Ph­êng Lam S¬n, QuËn Lª Ch©n, TP. H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Thương Mại và Dịch Vụ Vận Tải Hoàng Anh Phát</t>
+  </si>
+  <si>
+    <t>Số 2/97 Cầu Cáp, Phường Lam Sơn, Quận Lê Chân, TP. Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0200924866</t>
@@ -3007,10 +3007,10 @@
     <t>HOANGLONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH DÞch Vô VËn T¶i BiÓn Hoµng Long</t>
-  </si>
-  <si>
-    <t>Sè 68 ®­êng §ång Cau, tæ d©n phè B¹ch §»ng 1, Ph­êng Thuû Nguyªn, TP. H¶i Phßng, VN</t>
+    <t>Công ty TNHH Dịch Vụ Vận Tải Biển Hoàng Long</t>
+  </si>
+  <si>
+    <t>Số 68 đường Đồng Cau, tổ dân phố Bạch Đằng 1, Phường Thuỷ Nguyên, TP. Hải Phòng, VN</t>
   </si>
   <si>
     <t>0202318444</t>
@@ -3019,10 +3019,10 @@
     <t>HOANGNGA</t>
   </si>
   <si>
-    <t>C«ng ty CP TM XD &amp; SX Hoµng Nga</t>
-  </si>
-  <si>
-    <t>P1104,24T1, Trung Hoµ, Nh©n ChÝnh, HN</t>
+    <t>Công ty CP TM XD &amp; SX Hoàng Nga</t>
+  </si>
+  <si>
+    <t>P1104,24T1, Trung Hoà, Nhân Chính, HN</t>
   </si>
   <si>
     <t>0101826258</t>
@@ -3031,10 +3031,10 @@
     <t>HOANGOCLANTHAIBINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i BiÓn Hoa Ngäc Lan Th¸i B×nh</t>
-  </si>
-  <si>
-    <t>Sè 129 Khu 6, Thi TrÊn Diªm §iÒm, HuyÖn Th¸i Thôy, TØnh Th¸i B×nh</t>
+    <t>Công ty TNHH Vận Tải Biển Hoa Ngọc Lan Thái Bình</t>
+  </si>
+  <si>
+    <t>Số 129 Khu 6, Thi Trấn Diêm Điềm, Huyện Thái Thụy, Tỉnh Thái Bình</t>
   </si>
   <si>
     <t>1001103056</t>
@@ -3043,10 +3043,10 @@
     <t>HOANGPHUONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i Kho¸ng S¶n Hoµng Ph­¬ng</t>
-  </si>
-  <si>
-    <t>Tæ d©n phè Th¾ng Lîi ( Nhµ «ng Ph¹m v¨n Th¨ng), Ph­êng Hoµ B×nh, TP. H¶i Phßng, VN</t>
+    <t>Công ty TNHH Thương Mại Khoáng Sản Hoàng Phương</t>
+  </si>
+  <si>
+    <t>Tổ dân phố Thắng Lợi ( Nhà ông Phạm văn Thăng), Phường Hoà Bình, TP. Hải Phòng, VN</t>
   </si>
   <si>
     <t>0201994425</t>
@@ -3055,10 +3055,10 @@
     <t>HOANGSON</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Hoµng S¬n</t>
-  </si>
-  <si>
-    <t>Sè 9 TriÖu Quèc §¹t - ph­êng §iÖn Biªn - TP. Thanh Hãa</t>
+    <t>Công ty TNHH Hoàng Sơn</t>
+  </si>
+  <si>
+    <t>Số 9 Triệu Quốc Đạt - phường Điện Biên - TP. Thanh Hóa</t>
   </si>
   <si>
     <t>2800136500001</t>
@@ -3067,10 +3067,10 @@
     <t>HOANGTIENDUNG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i vµ Th­¬ng M¹i Hoµng TiÕn Dòng</t>
-  </si>
-  <si>
-    <t>Sè 114 ®­êng Bïi ThÞ Tõ Nhiªn, Ph­êng §«ng H¶i, Thµnh Phè H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Vận Tải và Thương Mại Hoàng Tiến Dũng</t>
+  </si>
+  <si>
+    <t>Số 114 đường Bùi Thị Từ Nhiên, Phường Đông Hải, Thành Phố Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0201731313</t>
@@ -3079,10 +3079,10 @@
     <t>HOANGTRIEU</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn Hoµng TriÖu</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Th«n Phó An, ThÞ TrÊn C¸t Thµnh, HuyÖn Trùc Ninh, TØnh nam §Þnh, ViÖt Nam</t>
+    <t>Công ty cổ phần Hoàng Triệu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Thôn Phú An, Thị Trấn Cát Thành, Huyện Trực Ninh, Tỉnh nam Định, Việt Nam</t>
   </si>
   <si>
     <t>0600332871</t>
@@ -3091,10 +3091,10 @@
     <t>HOAPHAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TM Hoµ Ph¸t</t>
-  </si>
-  <si>
-    <t>119 Bïi ThÞ Xu©n, HN</t>
+    <t>Công ty TNHH TM Hoà Phát</t>
+  </si>
+  <si>
+    <t>119 Bùi Thị Xuân, HN</t>
   </si>
   <si>
     <t>0101541037</t>
@@ -3103,10 +3103,10 @@
     <t>HOINHAP</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Giao NhËn vËn t¶i Héi NhËp</t>
-  </si>
-  <si>
-    <t>LÇu 2 - Sè 70 Huúnh v¨n b¸ch - Ph­êng 15 - QuËn Phó NhuËn - TP. HCM</t>
+    <t>Công ty TNHH Giao Nhận vận tải Hội Nhập</t>
+  </si>
+  <si>
+    <t>Lầu 2 - Số 70 Huỳnh văn bách - Phường 15 - Quận Phú Nhuận - TP. HCM</t>
   </si>
   <si>
     <t>0306144009</t>
@@ -3148,10 +3148,10 @@
     <t>HOTUAN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH SX TMDV Hå TuÊn</t>
-  </si>
-  <si>
-    <t>Sè 323/7 ®­êng HT13, HiÖp Thµnh, Q12, Hå ChÝ Mnh</t>
+    <t>Công ty TNHH SX TMDV Hồ Tuấn</t>
+  </si>
+  <si>
+    <t>Số 323/7 đường HT13, Hiệp Thành, Q12, Hồ Chí Mnh</t>
   </si>
   <si>
     <t>0310421960</t>
@@ -3160,10 +3160,10 @@
     <t>HOYER</t>
   </si>
   <si>
-    <t>Hoyer Transport ViÖt Nam Co.,LTD</t>
-  </si>
-  <si>
-    <t>Sè 45 Vâ thÞ S¸u, Ph­êng §akao, QuËn1 TP Hå ChÝ Minh</t>
+    <t>Hoyer Transport Việt Nam Co.,LTD</t>
+  </si>
+  <si>
+    <t>Số 45 Võ thị Sáu, Phường Đakao, Quận1 TP Hồ Chí Minh</t>
   </si>
   <si>
     <t>0310241781</t>
@@ -3172,16 +3172,16 @@
     <t>HOYSAN VIETNAM</t>
   </si>
   <si>
-    <t>C«ng Ty TNHH  §¹i Lý VTB Hoysan ViÖt Nam</t>
+    <t>Công Ty TNHH  Đại Lý VTB Hoysan Việt Nam</t>
   </si>
   <si>
     <t>HP LOGS</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i HP LOGS</t>
-  </si>
-  <si>
-    <t>Sè 10A3/339 MiÕu Hai X·, Ph­êng Lª Ch©n, Thµnh Phè H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Thương Mại HP LOGS</t>
+  </si>
+  <si>
+    <t>Số 10A3/339 Miếu Hai Xã, Phường Lê Chân, Thành Phố Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0202201799</t>
@@ -3190,10 +3190,10 @@
     <t>HT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH H­¬ng Thuû - CN Hµ t©y</t>
-  </si>
-  <si>
-    <t>Lai X¸, Hoµi §óc, Hµ T©y</t>
+    <t>Công ty TNHH Hương Thuỷ - CN Hà tây</t>
+  </si>
+  <si>
+    <t>Lai Xá, Hoài Đúc, Hà Tây</t>
   </si>
   <si>
     <t>0101194471001</t>
@@ -3229,10 +3229,10 @@
     <t>HUBHP</t>
   </si>
   <si>
-    <t>Cty TNHH dÞch vô hµng h¶i HUB ViÖt Nam - CN t¹i HP</t>
-  </si>
-  <si>
-    <t>P506 tÇng 5 toµ nhµ TD Business Lª Hång Phong, Ng« QuyÒn, HP</t>
+    <t>Cty TNHH dịch vụ hàng hải HUB Việt Nam - CN tại HP</t>
+  </si>
+  <si>
+    <t>P506 tầng 5 toà nhà TD Business Lê Hồng Phong, Ngô Quyền, HP</t>
   </si>
   <si>
     <t>0103150102-001</t>
@@ -3241,10 +3241,10 @@
     <t>HUBLINE</t>
   </si>
   <si>
-    <t>CN Cty tr¸ch nhiÖm h÷u h¹n HUB LINE ViÖt nam t¹i HP</t>
-  </si>
-  <si>
-    <t>L« 96 khu nhµ ë NguyÔn Tr·i, NQ, HP</t>
+    <t>CN Cty trách nhiệm hữu hạn HUB LINE Việt nam tại HP</t>
+  </si>
+  <si>
+    <t>Lô 96 khu nhà ở Nguyễn Trãi, NQ, HP</t>
   </si>
   <si>
     <t>0302812329001</t>
@@ -3253,10 +3253,10 @@
     <t>HUBVN</t>
   </si>
   <si>
-    <t>Cty TNHH DÞch Vô Hµng H¶i Hub ViÖt Nam</t>
-  </si>
-  <si>
-    <t>A1, TÇng 3 Kh¸ch S¹n HN Horison, 40 C¸t Linh, Hµ Néi</t>
+    <t>Cty TNHH Dịch Vụ Hàng Hải Hub Việt Nam</t>
+  </si>
+  <si>
+    <t>A1, Tầng 3 Khách Sạn HN Horison, 40 Cát Linh, Hà Nội</t>
   </si>
   <si>
     <t>0103150102</t>
@@ -3274,10 +3274,10 @@
     <t>HUNGDAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH SX &amp; TM Hïng §¹t</t>
-  </si>
-  <si>
-    <t>93/167 T©y S¬n - §èng §a - Hµ Néi</t>
+    <t>Công ty TNHH SX &amp; TM Hùng Đạt</t>
+  </si>
+  <si>
+    <t>93/167 Tây Sơn - Đống Đa - Hà Nội</t>
   </si>
   <si>
     <t>0102574765</t>
@@ -3286,10 +3286,10 @@
     <t>HUNGHUNG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i vËn T¶i H­ng H­ng</t>
-  </si>
-  <si>
-    <t>Sè 223 Khu I - ThÞ TrÊn Diªm §iÒn - HuyÖn Th¸i Thôy - TØnh Th¸i B×nh</t>
+    <t>Công ty TNHH Thương Mại vận Tải Hưng Hưng</t>
+  </si>
+  <si>
+    <t>Số 223 Khu I - Thị Trấn Diêm Điền - Huyện Thái Thụy - Tỉnh Thái Bình</t>
   </si>
   <si>
     <t>1001003559</t>
@@ -3298,10 +3298,10 @@
     <t>HUNGLONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn Hïng Long</t>
-  </si>
-  <si>
-    <t>420 B¹ch §»ng, Ph­êng ThÞ Nai, TP. Quy Nh¬n, TØnh B×nh §Þnh</t>
+    <t>Công ty cổ phần Hùng Long</t>
+  </si>
+  <si>
+    <t>420 Bạch Đằng, Phường Thị Nai, TP. Quy Nhơn, Tỉnh Bình Định</t>
   </si>
   <si>
     <t>4100752836</t>
@@ -3310,10 +3310,10 @@
     <t>HUNGNGUYEN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i §Çu T­ vµ VËn T¶i H­ng Nguyªn</t>
-  </si>
-  <si>
-    <t>Sè 2/2/897 T©n §øc Th¾ng, Ph­êng Së DÇu, QuËn Hång Bµng, TP. H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Thương Mại Đầu Tư và Vận Tải Hưng Nguyên</t>
+  </si>
+  <si>
+    <t>Số 2/2/897 Tân Đức Thắng, Phường Sở Dầu, Quận Hồng Bàng, TP. Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0201769966</t>
@@ -3322,10 +3322,10 @@
     <t>HUYANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TM XNK C¬ KhÝ DV VËn T¶i Thanh Huy Anh</t>
-  </si>
-  <si>
-    <t>Sè 02 §­êng Hoµng H÷u Nam - Ph­êng Long Th¹nh Mü - Q.9 - TP.HCM</t>
+    <t>Công ty TNHH TM XNK Cơ Khí DV Vận Tải Thanh Huy Anh</t>
+  </si>
+  <si>
+    <t>Số 02 Đường Hoàng Hữu Nam - Phường Long Thạnh Mỹ - Q.9 - TP.HCM</t>
   </si>
   <si>
     <t>0313858540</t>
@@ -3340,10 +3340,10 @@
     <t>ICD</t>
   </si>
   <si>
-    <t>CN Cty CP Ph¸t triÓn hµng h¶i - Hµ Néi</t>
-  </si>
-  <si>
-    <t>Sè 1 ®µo Duy Anh, §èng §a, Hµ Néi</t>
+    <t>CN Cty CP Phát triển hàng hải - Hà Nội</t>
+  </si>
+  <si>
+    <t>Số 1 đào Duy Anh, Đống Đa, Hà Nội</t>
   </si>
   <si>
     <t>0200580975001</t>
@@ -3352,10 +3352,10 @@
     <t>ILSHIN TECH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH ILSHIN TECH ViÖt Nam</t>
-  </si>
-  <si>
-    <t>L« L5, KCN Trµng DuÖ, x· Hång Phong, HuyÖn An D­¬ng, TP. H¶i Phßng</t>
+    <t>Công ty TNHH ILSHIN TECH Việt Nam</t>
+  </si>
+  <si>
+    <t>Lô L5, KCN Tràng Duệ, xã Hồng Phong, Huyện An Dương, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201724644</t>
@@ -3379,10 +3379,10 @@
     <t>INJAE VINA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH INJAE VINA</t>
-  </si>
-  <si>
-    <t>KCN Phó Th¸i - ThÞ TrÊn Phó Th¸i - Huyeenk Kim Thµnh - TØnh h¶i D­¬ng</t>
+    <t>Công ty TNHH INJAE VINA</t>
+  </si>
+  <si>
+    <t>KCN Phú Thái - Thị Trấn Phú Thái - Huyeenk Kim Thành - Tỉnh hải Dương</t>
   </si>
   <si>
     <t>0800273951</t>
@@ -3391,10 +3391,10 @@
     <t>INLACOSAIGON</t>
   </si>
   <si>
-    <t>INLACO Sµi Gßn</t>
-  </si>
-  <si>
-    <t>36-38 NguyÔn Tr­êng Té - Ph­êng 12 - QuËn 4 - TP. Hå ChÝ Minh</t>
+    <t>INLACO Sài Gòn</t>
+  </si>
+  <si>
+    <t>36-38 Nguyễn Trường Tộ - Phường 12 - Quận 4 - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0300442760</t>
@@ -3403,10 +3403,10 @@
     <t>INTE</t>
   </si>
   <si>
-    <t>c«ng ty TNHH ®Çu t­ x©y dùng &amp; th­¬ng m¹ INTERDECOR</t>
-  </si>
-  <si>
-    <t>Sè 315 tæ 45 khu §Òn Lõ, Hoµng Mai, Hµ Néi</t>
+    <t>công ty TNHH đầu tư xây dựng &amp; thương mạ INTERDECOR</t>
+  </si>
+  <si>
+    <t>Số 315 tổ 45 khu Đền Lừ, Hoàng Mai, Hà Nội</t>
   </si>
   <si>
     <t>0100368083</t>
@@ -3436,10 +3436,10 @@
     <t>INTER-TREND</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Bao B× Toµn CÇu Inter - Trend</t>
-  </si>
-  <si>
-    <t>Sè 133 §ng sè 16,KDT,CN vµ DV Vship HP, X. LËp LÔ, H Thñy Nguyªn, HP</t>
+    <t>Công ty TNHH Bao Bì Toàn Cầu Inter - Trend</t>
+  </si>
+  <si>
+    <t>Số 133 Đng số 16,KDT,CN và DV Vship HP, X. Lập Lễ, H Thủy Nguyên, HP</t>
   </si>
   <si>
     <t>0201722164</t>
@@ -3457,7 +3457,7 @@
     <t>INTERSERCOMYDINH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn INTERSERCO Mü §×nh</t>
+    <t>Công ty cổ phần INTERSERCO Mỹ Đình</t>
   </si>
   <si>
     <t>0106286937</t>
@@ -3478,7 +3478,7 @@
     <t>Cty TNHH ISS- Gemadept</t>
   </si>
   <si>
-    <t>Phßng 301, Citilight Tower, 45 Vâ ThÞ S¸u, P §akao, Q1, TP Hå ChÝ Minh</t>
+    <t>Phòng 301, Citilight Tower, 45 Võ Thị Sáu, P Đakao, Q1, TP Hồ Chí Minh</t>
   </si>
   <si>
     <t>0305484958</t>
@@ -3487,10 +3487,10 @@
     <t>ISTAR</t>
   </si>
   <si>
-    <t>CN t¹i HP - C«ng ty TNHH VËn T¶i Giao NhËn vµ Th­¬ng M¹i Istar</t>
-  </si>
-  <si>
-    <t>Sè 58 Phan Béi Ch©u - P. Quang Trung - Q. Hång Bµng - TP. H¶i Phßng</t>
+    <t>CN tại HP - Công ty TNHH Vận Tải Giao Nhận và Thương Mại Istar</t>
+  </si>
+  <si>
+    <t>Số 58 Phan Bội Châu - P. Quang Trung - Q. Hồng Bàng - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0106349263001</t>
@@ -3547,10 +3547,10 @@
     <t>JARDINE(VIETNAM)</t>
   </si>
   <si>
-    <t>C«ng ty TNHH DÞch Vô hµn H¶i JARDINE ( ViÖt Nam)</t>
-  </si>
-  <si>
-    <t>Phßng 304, LÇu 3, 2 Bis 4-6, Lª Th¸nh T«n, Ph­êng BÕn NghÐ -HCM</t>
+    <t>Công ty TNHH Dịch Vụ hàn Hải JARDINE ( Việt Nam)</t>
+  </si>
+  <si>
+    <t>Phòng 304, Lầu 3, 2 Bis 4-6, Lê Thánh Tôn, Phường Bến Nghé -HCM</t>
   </si>
   <si>
     <t>0304147893</t>
@@ -3607,10 +3607,10 @@
     <t>K.HOA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH th­¬ng m¹i Kh¸nh Hoµ</t>
-  </si>
-  <si>
-    <t>74B TrÞnh Phong - Nha Trang</t>
+    <t>Công ty TNHH thương mại Khánh Hoà</t>
+  </si>
+  <si>
+    <t>74B Trịnh Phong - Nha Trang</t>
   </si>
   <si>
     <t>4200500448</t>
@@ -3649,10 +3649,10 @@
     <t>KCVN</t>
   </si>
   <si>
-    <t>Cty TNHH KCTC ViÖt Nam</t>
-  </si>
-  <si>
-    <t>473 §iÖn Biªn Phñ - P .25 - QuËn B×nh Th¹ch - TP. HCM</t>
+    <t>Cty TNHH KCTC Việt Nam</t>
+  </si>
+  <si>
+    <t>473 Điện Biên Phủ - P .25 - Quận Bình Thạch - TP. HCM</t>
   </si>
   <si>
     <t>0305713245</t>
@@ -3661,10 +3661,10 @@
     <t>KEANG</t>
   </si>
   <si>
-    <t>Cty TNHH mét thµnh viªn KEANG NAM VINA</t>
-  </si>
-  <si>
-    <t>101 Gi¶ng Vâ Lake, Ba §×nh, Hµ Néi</t>
+    <t>Cty TNHH một thành viên KEANG NAM VINA</t>
+  </si>
+  <si>
+    <t>101 Giảng Võ Lake, Ba Đình, Hà Nội</t>
   </si>
   <si>
     <t>0102314372</t>
@@ -3673,10 +3673,10 @@
     <t>KEIPHONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH XuÊt NhËp KhÈu Kei Phong</t>
-  </si>
-  <si>
-    <t>Tæ d©n phè 31, Ph­êng Hßa NghÜa, QuËn D­¬ng Kinh, TP. H¶i PHßng</t>
+    <t>Công ty TNHH Xuất Nhập Khẩu Kei Phong</t>
+  </si>
+  <si>
+    <t>Tổ dân phố 31, Phường Hòa Nghĩa, Quận Dương Kinh, TP. Hải PHòng</t>
   </si>
   <si>
     <t>0201773338</t>
@@ -3694,10 +3694,10 @@
     <t>KETOANTHUEHTT</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dÞch vô th­¬ng m¹i ®µo t¹o t­ vÊn kÕ to¸n thuÕ HT &amp;T</t>
-  </si>
-  <si>
-    <t>TÇng 6, Tßa nhµ LPsoos 98-100 T« HiÖu, P. Tr¹i Cau, Q. Lª Ch©n, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần dịch vụ thương mại đào tạo tư vấn kế toán thuế HT &amp;T</t>
+  </si>
+  <si>
+    <t>Tầng 6, Tòa nhà LPsoos 98-100 Tô Hiệu, P. Trại Cau, Q. Lê Chân, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201987192</t>
@@ -3712,10 +3712,10 @@
     <t>KHAITHACMO</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn ThiÕt BÞ Khai Th¸c Má</t>
-  </si>
-  <si>
-    <t>Sè 65 Phè An Tr¹ch, Ph­êng Quèc tö Gi¸m, QuËn §èng §a, Thµnh Phè Hµ Néi</t>
+    <t>Công ty Cổ Phần Thiết Bị Khai Thác Mỏ</t>
+  </si>
+  <si>
+    <t>Số 65 Phố An Trạch, Phường Quốc tử Giám, Quận Đống Đa, Thành Phố Hà Nội</t>
   </si>
   <si>
     <t>0106571187</t>
@@ -3724,19 +3724,19 @@
     <t>KHANHHOA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng m¹i Kh¸nh Hßa</t>
-  </si>
-  <si>
-    <t>74B Tring Phong - Ph­¬ng T©n LËp - Thµnh Phè Nha Trang - T. Kh¸nh Hßa</t>
+    <t>Công ty TNHH Thương mại Khánh Hòa</t>
+  </si>
+  <si>
+    <t>74B Tring Phong - Phương Tân Lập - Thành Phố Nha Trang - T. Khánh Hòa</t>
   </si>
   <si>
     <t>KHIDOTTHANGLONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH KhÝ §èt Th¨ng Long</t>
-  </si>
-  <si>
-    <t>Côm c«ng nghiÖp Gas L­u X¸, X· QuÊt §éng, HuyÖn Th­¬ng TÝn, TP. Hµ Néi, ViÖt Nam</t>
+    <t>Công ty TNHH Khí Đốt Thăng Long</t>
+  </si>
+  <si>
+    <t>Cụm công nghiệp Gas Lưu Xá, Xã Quất Động, Huyện Thương Tín, TP. Hà Nội, Việt Nam</t>
   </si>
   <si>
     <t>84-24-33765339</t>
@@ -3748,10 +3748,10 @@
     <t>KHOANGSAN I&amp;C</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Kho¸ng S¶n I&amp;C</t>
-  </si>
-  <si>
-    <t>Khèi B¾c Mü, Ph­êng Hoµng Mai, TØnh NghÖ An, ViÖt Nam</t>
+    <t>Công ty TNHH Khoáng Sản I&amp;C</t>
+  </si>
+  <si>
+    <t>Khối Bắc Mỹ, Phường Hoàng Mai, Tỉnh Nghệ An, Việt Nam</t>
   </si>
   <si>
     <t>2902194893</t>
@@ -3760,19 +3760,19 @@
     <t>KHUNG</t>
   </si>
   <si>
-    <t>Cty TNHH XNK Kh¸nh H­ng</t>
-  </si>
-  <si>
-    <t>40/115 §µo TÊn - Ba §×nh - Hµ Néi</t>
+    <t>Cty TNHH XNK Khánh Hưng</t>
+  </si>
+  <si>
+    <t>40/115 Đào Tấn - Ba Đình - Hà Nội</t>
   </si>
   <si>
     <t>KHUONMAUHOANGMINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §Çu T­ S¶n XuÊt Khu«n MÉu Hoµng Minh</t>
-  </si>
-  <si>
-    <t>Sè 138 Kªnh D­¬ng - Lª Ch©n - H¶i Phßng</t>
+    <t>Công ty TNHH Đầu Tư Sản Xuất Khuôn Mẫu Hoàng Minh</t>
+  </si>
+  <si>
+    <t>Số 138 Kênh Dương - Lê Chân - Hải Phòng</t>
   </si>
   <si>
     <t>0201646805</t>
@@ -3781,10 +3781,10 @@
     <t>KIMDINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH SX &amp; TM Kim §Ønh</t>
-  </si>
-  <si>
-    <t>6 ¢u C¬, Qu¶ng An, T©y Hå, Hµ Néi</t>
+    <t>Công ty TNHH SX &amp; TM Kim Đỉnh</t>
+  </si>
+  <si>
+    <t>6 Âu Cơ, Quảng An, Tây Hồ, Hà Nội</t>
   </si>
   <si>
     <t>0100231201</t>
@@ -3793,10 +3793,10 @@
     <t>KIMLONG</t>
   </si>
   <si>
-    <t>C«ng ty CP hµng h¶i vµ th­¬ng m¹i Kim Long</t>
-  </si>
-  <si>
-    <t>TÇng 3, sè 33 Phè Giang V¨n Minh, Ph­êng Kim M·, quËn Ba §×nh,HN</t>
+    <t>Công ty CP hàng hải và thương mại Kim Long</t>
+  </si>
+  <si>
+    <t>Tầng 3, số 33 Phố Giang Văn Minh, Phường Kim Mã, quận Ba Đình,HN</t>
   </si>
   <si>
     <t>0101658733</t>
@@ -3811,10 +3811,10 @@
     <t>KING MO</t>
   </si>
   <si>
-    <t>C«ng ty TNHH King Mo New Materials ViÖt Nam</t>
-  </si>
-  <si>
-    <t>KCN Tiªn S¬n - Ph­êng §ång Nguyªn - ThÞ X· Tõ S¬n - TØnh B¾c Ninh</t>
+    <t>Công ty TNHH King Mo New Materials Việt Nam</t>
+  </si>
+  <si>
+    <t>KCN Tiên Sơn - Phường Đồng Nguyên - Thị Xã Từ Sơn - Tỉnh Bắc Ninh</t>
   </si>
   <si>
     <t>2300324721</t>
@@ -3829,10 +3829,10 @@
     <t>KK HN</t>
   </si>
   <si>
-    <t>Cty CP Kim KhÝ Hµ Néi</t>
-  </si>
-  <si>
-    <t>20 T«n ThÊt Tïng, §èng §a, Hµ N«i</t>
+    <t>Cty CP Kim Khí Hà Nội</t>
+  </si>
+  <si>
+    <t>20 Tôn Thất Tùng, Đống Đa, Hà Nôi</t>
   </si>
   <si>
     <t>0100100368</t>
@@ -3841,10 +3841,10 @@
     <t>KKTLONG</t>
   </si>
   <si>
-    <t>Cty TNHH Nhµ n­íc 01 TV Kim KhÝ Th¨ng Long</t>
-  </si>
-  <si>
-    <t>Sµi §ång, Long Biªn, HN</t>
+    <t>Cty TNHH Nhà nước 01 TV Kim Khí Thăng Long</t>
+  </si>
+  <si>
+    <t>Sài Đồng, Long Biên, HN</t>
   </si>
   <si>
     <t>0100100618</t>
@@ -3853,10 +3853,10 @@
     <t>KLMQN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Kim Lo¹i Mµu Qu¶ng Ninh</t>
-  </si>
-  <si>
-    <t>Th«n T©n TiÕn, X· D­¬ng Huy, Thµnh Phè CÈm Ph¶, TØnh Qu¶ng Ninh</t>
+    <t>Công ty TNHH Kim Loại Màu Quảng Ninh</t>
+  </si>
+  <si>
+    <t>Thôn Tân Tiến, Xã Dương Huy, Thành Phố Cẩm Phả, Tỉnh Quảng Ninh</t>
   </si>
   <si>
     <t>5700686150</t>
@@ -3868,7 +3868,7 @@
     <t>Cty TNHH Khang Minh</t>
   </si>
   <si>
-    <t>Khèi 04 §«ng Anh, Hµ Néi</t>
+    <t>Khối 04 Đông Anh, Hà Nội</t>
   </si>
   <si>
     <t>0101116593</t>
@@ -3877,10 +3877,10 @@
     <t>KPB</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn KPB</t>
-  </si>
-  <si>
-    <t>Sè 13/120 Lª Lîi, P. Gia Viªn, QuËn Ng« QuyÒn, TP. H¶i Phßng, ViN</t>
+    <t>Công ty cổ phần KPB</t>
+  </si>
+  <si>
+    <t>Số 13/120 Lê Lợi, P. Gia Viên, Quận Ngô Quyền, TP. Hải Phòng, ViN</t>
   </si>
   <si>
     <t>0201627256</t>
@@ -3889,19 +3889,19 @@
     <t>KS VNS</t>
   </si>
   <si>
-    <t>C«ng ty CP kho¸ng s¶n vµ ®Çu t­ Vinashin</t>
-  </si>
-  <si>
-    <t>Sè 109 Qu¸n Th¸nh - Ba §×nh - HN</t>
+    <t>Công ty CP khoáng sản và đầu tư Vinashin</t>
+  </si>
+  <si>
+    <t>Số 109 Quán Thánh - Ba Đình - HN</t>
   </si>
   <si>
     <t>KSLEPHAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH L­u Tró vµ Kh¸ch S¹n Lª Ph¹m</t>
-  </si>
-  <si>
-    <t>Sè 4D Hå Sen, Ph­êng Tr¹i Cau, QuËn Lª Ch©n, Thµnh Phè H¶i Phßng</t>
+    <t>Công ty TNHH Lưu Trú và Khách Sạn Lê Phạm</t>
+  </si>
+  <si>
+    <t>Số 4D Hồ Sen, Phường Trại Cau, Quận Lê Chân, Thành Phố Hải Phòng</t>
   </si>
   <si>
     <t>0200145309</t>
@@ -3910,10 +3910,10 @@
     <t>KSPHIKIM</t>
   </si>
   <si>
-    <t>C«ng ty CP Kho¸ng Snar Phi Kim ViÖt Nam</t>
-  </si>
-  <si>
-    <t>L« 31M2 K§T Míi Yªn Hßa, P. Yªn Hßa, Q. CÇu GiÊy, TP. HN</t>
+    <t>Công ty CP Khoáng Snar Phi Kim Việt Nam</t>
+  </si>
+  <si>
+    <t>Lô 31M2 KĐT Mới Yên Hòa, P. Yên Hòa, Q. Cầu Giấy, TP. HN</t>
   </si>
   <si>
     <t>0106277989</t>
@@ -3922,10 +3922,10 @@
     <t>KSTANTHANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i Kho¸ng S¶n T©n Thµnh</t>
-  </si>
-  <si>
-    <t>LÇu 12B - 196 §­êng Hoµng DiÖu - Ph­êng 8 - QuËn 4 - TP. HCM</t>
+    <t>Công ty TNHH Thương Mại Khoáng Sản Tân Thành</t>
+  </si>
+  <si>
+    <t>Lầu 12B - 196 Đường Hoàng Diệu - Phường 8 - Quận 4 - TP. HCM</t>
   </si>
   <si>
     <t>0313588809</t>
@@ -3934,10 +3934,10 @@
     <t>KSTHAIBINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i Kho¸ng S¶n Th¸i B×nh</t>
-  </si>
-  <si>
-    <t>LÇu 7, Sè 198 §­êng Hoµng DiÖu, Ph­êng 9, QuËn 4, TP. HCM</t>
+    <t>Công ty TNHH Thương Mại Khoáng Sản Thái Bình</t>
+  </si>
+  <si>
+    <t>Lầu 7, Số 198 Đường Hoàng Diệu, Phường 9, Quận 4, TP. HCM</t>
   </si>
   <si>
     <t>0313757158</t>
@@ -3946,10 +3946,10 @@
     <t>KSTRUNGNGUYEN</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn kho¸ng s¶n Trung Nguyªn</t>
-  </si>
-  <si>
-    <t>Phßng 601 tÇng 6 tßa nhµ Lª Ph¹m, sè 98-100 T« HiÖu - P. Tr¹i Cau, Q. Lª Ch©n, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần khoáng sản Trung Nguyên</t>
+  </si>
+  <si>
+    <t>Phòng 601 tầng 6 tòa nhà Lê Phạm, số 98-100 Tô Hiệu - P. Trại Cau, Q. Lê Chân, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201799417</t>
@@ -3958,10 +3958,10 @@
     <t>KSVN</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn Nhùa Quèc TÕ KS ViÖt Nam</t>
-  </si>
-  <si>
-    <t>C3 - Côm CN Gi¸n KhÈu Ninh B×nh</t>
+    <t>Công ty Cổ Phần Nhựa Quốc Tế KS Việt Nam</t>
+  </si>
+  <si>
+    <t>C3 - Cụm CN Gián Khẩu Ninh Bình</t>
   </si>
   <si>
     <t>2700347191</t>
@@ -3979,10 +3979,10 @@
     <t>KUNNA</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn giao nhËn Quèc TÕ Kunna</t>
-  </si>
-  <si>
-    <t>Sè 508 ®­êng Lª Th¸nh T«ng -ph­êng Ng« QuyÒn - TP H¶i Phßng</t>
+    <t>Công ty cổ phần giao nhận Quốc Tế Kunna</t>
+  </si>
+  <si>
+    <t>Số 508 đường Lê Thánh Tông -phường Ngô Quyền - TP Hải Phòng</t>
   </si>
   <si>
     <t>0201288878</t>
@@ -3991,10 +3991,10 @@
     <t>KWANGJIN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Kwang Jin ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 2 Thi S¸ch, P. BÕn NghÐ, QuËn 1, TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH Kwang Jin Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 2 Thi Sách, P. Bến Nghé, Quận 1, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0313065527</t>
@@ -4021,10 +4021,10 @@
     <t>LACVIET</t>
   </si>
   <si>
-    <t>C«ng ty CP dÞch vô th­¬ng m¹i vµ vËn t¶i L¹c ViÖt</t>
-  </si>
-  <si>
-    <t>Sè 66 §­êng trÇn Quang Kh¶i - Ph­êng Quang Trung - Q.Hång Bµng - HP</t>
+    <t>Công ty CP dịch vụ thương mại và vận tải Lạc Việt</t>
+  </si>
+  <si>
+    <t>Số 66 Đường trần Quang Khải - Phường Quang Trung - Q.Hồng Bàng - HP</t>
   </si>
   <si>
     <t>0200888784</t>
@@ -4042,10 +4042,10 @@
     <t>LAMDONG-TKV</t>
   </si>
   <si>
-    <t>CN tËp ®oµn CN than -Kho¸ng s¶n VN - C«ng ty Nh«m L©m §ång - TKV</t>
-  </si>
-  <si>
-    <t>§­êng Phan §×nh Phïng, tæ 15, x· B¶o L©m, TØnh L©m §ång</t>
+    <t>CN tập đoàn CN than -Khoáng sản VN - Công ty Nhôm Lâm Đồng - TKV</t>
+  </si>
+  <si>
+    <t>Đường Phan Đình Phùng, tổ 15, xã Bảo Lâm, Tỉnh Lâm Đồng</t>
   </si>
   <si>
     <t>5700100256-070</t>
@@ -4054,10 +4054,10 @@
     <t>LANPHUONGDONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn DÞch Vô LÆn Ph­¬ng §«ng</t>
-  </si>
-  <si>
-    <t>99B M¹c §Ünh Chi, Ph­êng 4, TP. Vòng Tµu, TØnh Bµ RÞa - Vòng Tµu, ViÖt Nam</t>
+    <t>Công ty cổ phần Dịch Vụ Lặn Phương Đông</t>
+  </si>
+  <si>
+    <t>99B Mạc Đĩnh Chi, Phường 4, TP. Vũng Tàu, Tỉnh Bà Rịa - Vũng Tàu, Việt Nam</t>
   </si>
   <si>
     <t>3502361083</t>
@@ -4075,16 +4075,16 @@
     <t>LCUONG</t>
   </si>
   <si>
-    <t>C«ng Ty CP Th­¬ng M¹i XNK Loan C­êng</t>
+    <t>Công Ty CP Thương Mại XNK Loan Cường</t>
   </si>
   <si>
     <t>LEGENDSEA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Legendsea</t>
-  </si>
-  <si>
-    <t>TÇng 3, Toµ nhµ V¨n phßng Savina, Sè 1 §inh LÔ, P. Trµng TiÒn, Q. Hoµn KiÕm, HN</t>
+    <t>Công ty TNHH Legendsea</t>
+  </si>
+  <si>
+    <t>Tầng 3, Toà nhà Văn phòng Savina, Số 1 Đinh Lễ, P. Tràng Tiền, Q. Hoàn Kiếm, HN</t>
   </si>
   <si>
     <t>0109770409</t>
@@ -4093,10 +4093,10 @@
     <t>LELOI</t>
   </si>
   <si>
-    <t>Cty TNHH TM Lª Lîi</t>
-  </si>
-  <si>
-    <t>Trung Kinh, Lª Lîi, KiÕn X­¬ng, Th¸i B×nh</t>
+    <t>Cty TNHH TM Lê Lợi</t>
+  </si>
+  <si>
+    <t>Trung Kinh, Lê Lợi, Kiến Xương, Thái Bình</t>
   </si>
   <si>
     <t>1000351881</t>
@@ -4105,10 +4105,10 @@
     <t>LENGUYEN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH MTV Lª NguyÔn</t>
-  </si>
-  <si>
-    <t>Xãm 3 th«n V¨n Qu¸n, X· V¨n Khª, HuyÖn Mª Linh, Thµnh Phè Hµ Néi</t>
+    <t>Công ty TNHH MTV Lê Nguyễn</t>
+  </si>
+  <si>
+    <t>Xóm 3 thôn Văn Quán, Xã Văn Khê, Huyện Mê Linh, Thành Phố Hà Nội</t>
   </si>
   <si>
     <t>0109088718</t>
@@ -4117,10 +4117,10 @@
     <t>LEO VIETNAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §¹i lý Leo ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 29/27 T©n C¶ng, Ph­êng 25, QuËn B×nh Th¹nh, Thµnh Phè HCM</t>
+    <t>Công ty TNHH Đại lý Leo Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 29/27 Tân Cảng, Phường 25, Quận Bình Thạnh, Thành Phố HCM</t>
   </si>
   <si>
     <t>0317034015</t>
@@ -4129,10 +4129,10 @@
     <t>LG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Long Giang</t>
-  </si>
-  <si>
-    <t>Th«n ChÝ Trung, x· Nh­ Quúnh, TØnh H­ng Yªn, ViÖt Nam</t>
+    <t>Công ty TNHH Long Giang</t>
+  </si>
+  <si>
+    <t>Thôn Chí Trung, xã Như Quỳnh, Tỉnh Hưng Yên, Việt Nam</t>
   </si>
   <si>
     <t>0100365325</t>
@@ -4150,10 +4150,10 @@
     <t>LIENKET T&amp;TA</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn liªn kÕt T &amp; TA</t>
-  </si>
-  <si>
-    <t>MG3-11, Khu ®« thÞ Vinhome - Sè 1 BÕn §oan, P. Hång Gai, TP. H¹ Long, T.Qu¶ng Ninh</t>
+    <t>Công ty cổ phần liên kết T &amp; TA</t>
+  </si>
+  <si>
+    <t>MG3-11, Khu đô thị Vinhome - Số 1 Bến Đoan, P. Hồng Gai, TP. Hạ Long, T.Quảng Ninh</t>
   </si>
   <si>
     <t>5701962124</t>
@@ -4162,10 +4162,10 @@
     <t>LIENMINH</t>
   </si>
   <si>
-    <t>C«ng TY TNHH Qu¶n Lý TiÕp VËn Liªn Minh</t>
-  </si>
-  <si>
-    <t>157/44 ®­êng D2 - Ph­êng 25 - QuËn B×nh Th¹nh - TP. HCM</t>
+    <t>Công TY TNHH Quản Lý Tiếp Vận Liên Minh</t>
+  </si>
+  <si>
+    <t>157/44 đường D2 - Phường 25 - Quận Bình Thạnh - TP. HCM</t>
   </si>
   <si>
     <t>0301933602</t>
@@ -4174,7 +4174,7 @@
     <t>LIH</t>
   </si>
   <si>
-    <t>C«ng ty Lih Hsiang Industrial</t>
+    <t>Công ty Lih Hsiang Industrial</t>
   </si>
   <si>
     <t>LIME</t>
@@ -4186,10 +4186,10 @@
     <t>LIONAS METALS</t>
   </si>
   <si>
-    <t>C«ng ty TNHH LIONAS METALS</t>
-  </si>
-  <si>
-    <t>Tæ d©n phè Liªn S¬n - Ph­êng H¶i Th­îng - ThÞ X· Nghi S¬n - Thnah Hãa</t>
+    <t>Công ty TNHH LIONAS METALS</t>
+  </si>
+  <si>
+    <t>Tổ dân phố Liên Sơn - Phường Hải Thượng - Thị Xã Nghi Sơn - Thnah Hóa</t>
   </si>
   <si>
     <t>LISHEN</t>
@@ -4207,10 +4207,10 @@
     <t>LOGISTICS AC</t>
   </si>
   <si>
-    <t>C«ng ty CP th­¬ng m¹i vµ Logistic ¸ Ch©u</t>
-  </si>
-  <si>
-    <t>P309, t©ng 3, toµ nhµ DG, sè 15 TrÇn Phó, P L­¬ng Kh¸ch ThiÖn, NQ, HP</t>
+    <t>Công ty CP thương mại và Logistic á Châu</t>
+  </si>
+  <si>
+    <t>P309, tâng 3, toà nhà DG, số 15 Trần Phú, P Lương Khách Thiện, NQ, HP</t>
   </si>
   <si>
     <t>0201177448</t>
@@ -4219,10 +4219,10 @@
     <t>LOGISTICS ATOM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH S¶n XuÊt Th­¬ng M¹i vµ Logistics ATOM</t>
-  </si>
-  <si>
-    <t>Sè 39, dduwowngf 14, Khu phè 6, Ph­êng Ph­íc Long B, QuËn 9, TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH Sản Xuất Thương Mại và Logistics ATOM</t>
+  </si>
+  <si>
+    <t>Số 39, dduwowngf 14, Khu phố 6, Phường Phước Long B, Quận 9, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>3702534304</t>
@@ -4231,10 +4231,10 @@
     <t>LOGISTICS BACHDANG</t>
   </si>
   <si>
-    <t>C«ng Ty THNN Logistics B¹ch §»ng</t>
-  </si>
-  <si>
-    <t>Tæ d©n phè Sim BÊc, Ph­êng Hoµ B×nh, Thµnh Phè h¶i Phßng, ViÖt Nam</t>
+    <t>Công Ty THNN Logistics Bạch Đằng</t>
+  </si>
+  <si>
+    <t>Tổ dân phố Sim Bấc, Phường Hoà Bình, Thành Phố hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0202339606</t>
@@ -4243,10 +4243,10 @@
     <t>LOGISTICSNEWWAY</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn Logistics New Way</t>
-  </si>
-  <si>
-    <t>Sè 4 l« 2A Lª Hång Phong, Ph­êng §«ng Khª, QuËn Ng« QuyÒn - TP. H¶i Phßng</t>
+    <t>Công ty cổ phần Logistics New Way</t>
+  </si>
+  <si>
+    <t>Số 4 lô 2A Lê Hồng Phong, Phường Đông Khê, Quận Ngô Quyền - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201977740</t>
@@ -4255,10 +4255,10 @@
     <t>LOGISTICSVIETNAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TX Logistics ViÖt Nam</t>
-  </si>
-  <si>
-    <t>LÇu 3, Tßa nhµ Kicotrans, 46 B¹ch §»ng 2, ph­êng T©n S¬n Hoµ, TP HCM, VN</t>
+    <t>Công ty TNHH TX Logistics Việt Nam</t>
+  </si>
+  <si>
+    <t>Lầu 3, Tòa nhà Kicotrans, 46 Bạch Đằng 2, phường Tân Sơn Hoà, TP HCM, VN</t>
   </si>
   <si>
     <t>0313507849</t>
@@ -4267,10 +4267,10 @@
     <t>LOGIVAN VIET NAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH c«ng nghÖ Logivan ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 9 ngâ 189/2 Gi¶ng Vâ, Ph­êng C¸t Linh, QuËn §èng §a, Hµ Néi</t>
+    <t>Công ty TNHH công nghệ Logivan Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 9 ngõ 189/2 Giảng Võ, Phường Cát Linh, Quận Đống Đa, Hà Nội</t>
   </si>
   <si>
     <t>0108054755</t>
@@ -4279,10 +4279,10 @@
     <t>LONGPHUONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i Quèc TÕ Long Ph­¬ng Logs</t>
-  </si>
-  <si>
-    <t>P502, TÇng 5 sè 508 Lª Th¸nh T«ng, Ph­êng V¹n Mü, QuËn Ng« QuyÒn, H¶i Phßng</t>
+    <t>Công ty TNHH Thương Mại Quốc Tế Long Phương Logs</t>
+  </si>
+  <si>
+    <t>P502, Tầng 5 số 508 Lê Thánh Tông, Phường Vạn Mỹ, Quận Ngô Quyền, Hải Phòng</t>
   </si>
   <si>
     <t>0202233751</t>
@@ -4297,10 +4297,10 @@
     <t>LONGSON</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Long S¬n</t>
-  </si>
-  <si>
-    <t>Sè 29/3 Ph­êng Trung S¬n - ThÞ X· Tam §iÖp - TØnh Ninh B×nh</t>
+    <t>Công ty TNHH Long Sơn</t>
+  </si>
+  <si>
+    <t>Số 29/3 Phường Trung Sơn - Thị Xã Tam Điệp - Tỉnh Ninh Bình</t>
   </si>
   <si>
     <t>2700271520</t>
@@ -4309,10 +4309,10 @@
     <t>LONGTAN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i vµ Th­¬ng M¹i Long t©n</t>
-  </si>
-  <si>
-    <t>Sè 108 Ng« QuyÒn, Ph­êng M¸y Chai, QuËn Ng« QuyÒn , TP. H¶i Phßng</t>
+    <t>Công ty TNHH Vận Tải và Thương Mại Long tân</t>
+  </si>
+  <si>
+    <t>Số 108 Ngô Quyền, Phường Máy Chai, Quận Ngô Quyền , TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201749462</t>
@@ -4330,10 +4330,10 @@
     <t>LTRODA</t>
   </si>
   <si>
-    <t>C«ng ty CP s¶n xuÊt l­íi thÐp rä ®¸ ViÖt Nam</t>
-  </si>
-  <si>
-    <t>T©n Minh, Sãc S¬n, Hµ Néi</t>
+    <t>Công ty CP sản xuất lưới thép rọ đá Việt Nam</t>
+  </si>
+  <si>
+    <t>Tân Minh, Sóc Sơn, Hà Nội</t>
   </si>
   <si>
     <t>0101397016</t>
@@ -4342,10 +4342,10 @@
     <t>LTTNT</t>
   </si>
   <si>
-    <t>C«ng ty CP l­¬ng thùc Thanh NghÖ TÜnh</t>
-  </si>
-  <si>
-    <t>58 Lª Lîi, Thµnh Phè Vinh, NghÖ An</t>
+    <t>Công ty CP lương thực Thanh Nghệ Tĩnh</t>
+  </si>
+  <si>
+    <t>58 Lê Lợi, Thành Phố Vinh, Nghệ An</t>
   </si>
   <si>
     <t>2900523461</t>
@@ -4363,10 +4363,10 @@
     <t>LUYENDONGLAOCAI</t>
   </si>
   <si>
-    <t>Chi nh¸nh LuyÖn §ång Lµo Cai - VIMICO</t>
-  </si>
-  <si>
-    <t>Th«n T©n Hång, X· B¸t X¸t, TØnh Lµo Cai, ViÖt Nam</t>
+    <t>Chi nhánh Luyện Đồng Lào Cai - VIMICO</t>
+  </si>
+  <si>
+    <t>Thôn Tân Hồng, Xã Bát Xát, Tỉnh Lào Cai, Việt Nam</t>
   </si>
   <si>
     <t>0100103087-008</t>
@@ -4375,10 +4375,10 @@
     <t>LXUONG</t>
   </si>
   <si>
-    <t>Cty TNHH C¬ KhÝ Qu¶ng Long X­¬ng</t>
-  </si>
-  <si>
-    <t>Côm CN An §ång - AN L©m - Nam S¸ch - H¶i D­¬ng</t>
+    <t>Cty TNHH Cơ Khí Quảng Long Xương</t>
+  </si>
+  <si>
+    <t>Cụm CN An Đồng - AN Lâm - Nam Sách - Hải Dương</t>
   </si>
   <si>
     <t>0800749895</t>
@@ -4399,10 +4399,10 @@
     <t>M&amp;E MIEN NAM</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i dÞch vô M &amp; E MiÒn Nam</t>
-  </si>
-  <si>
-    <t>203/38/34 §­êng Trôc - P.13- QuËn B×nh Th¹nh - TP. Hå ChÝ Minh</t>
+    <t>Công ty cổ phần thương mại dịch vụ M &amp; E Miền Nam</t>
+  </si>
+  <si>
+    <t>203/38/34 Đường Trục - P.13- Quận Bình Thạnh - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0311818895</t>
@@ -4462,10 +4462,10 @@
     <t>MACS SHIPPING</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn hµng h¶i MACS</t>
-  </si>
-  <si>
-    <t>89 Pasteur, Ph­êng BÕn NghÐ, QuËn 1, Thµnh phè Hå ChÝ Minh, ViÖt Nam</t>
+    <t>Công ty cổ phần hàng hải MACS</t>
+  </si>
+  <si>
+    <t>89 Pasteur, Phường Bến Nghé, Quận 1, Thành phố Hồ Chí Minh, Việt Nam</t>
   </si>
   <si>
     <t>0302326311</t>
@@ -4474,10 +4474,10 @@
     <t>MAILAM</t>
   </si>
   <si>
-    <t>C«ng ty kho¸ng s¶n Mai Lam</t>
-  </si>
-  <si>
-    <t>Nhµ 07, hÎm 195, khu phè 3C, Ph­êng Th¹nh Léc, QuËn 12, TP. Hå ChÝ Minh</t>
+    <t>Công ty khoáng sản Mai Lam</t>
+  </si>
+  <si>
+    <t>Nhà 07, hẻm 195, khu phố 3C, Phường Thạnh Lộc, Quận 12, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0314186179</t>
@@ -4486,10 +4486,10 @@
     <t>MAIMAI</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn Th­¬ng M¹i Mai Mai</t>
-  </si>
-  <si>
-    <t>364/39B Thuy Hµ - Th¸i Thôy - Th¸i B×nh</t>
+    <t>Công ty Cổ Phần Thương Mại Mai Mai</t>
+  </si>
+  <si>
+    <t>364/39B Thuy Hà - Thái Thụy - Thái Bình</t>
   </si>
   <si>
     <t>1000423261</t>
@@ -4498,10 +4498,10 @@
     <t>MAIVU</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn Mai Vò</t>
-  </si>
-  <si>
-    <t>Sè nhµ 4 , ngâ 42 ®­êng NguyÔn v¨n Linh, Ph­êng D­ Hµng Kªnh, QuËn Lª Ch©n, TP.HP</t>
+    <t>Công ty cổ phần Mai Vũ</t>
+  </si>
+  <si>
+    <t>Số nhà 4 , ngõ 42 đường Nguyễn văn Linh, Phường Dư Hàng Kênh, Quận Lê Chân, TP.HP</t>
   </si>
   <si>
     <t>0200833464</t>
@@ -4516,10 +4516,10 @@
     <t>MANHPHAT</t>
   </si>
   <si>
-    <t>Cty TNHH TM M¹nh Ph¸t</t>
-  </si>
-  <si>
-    <t>L« B3, Khu TTVP Quèc Héi, ngâ 217, La Thµnh, HN</t>
+    <t>Cty TNHH TM Mạnh Phát</t>
+  </si>
+  <si>
+    <t>Lô B3, Khu TTVP Quốc Hội, ngõ 217, La Thành, HN</t>
   </si>
   <si>
     <t>0101213195</t>
@@ -4552,10 +4552,10 @@
     <t>MCO</t>
   </si>
   <si>
-    <t>Cty CP MCO ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 8 ngâ 121 Th¸i Hµ, §èng §a, Hµ Néi</t>
+    <t>Cty CP MCO Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 8 ngõ 121 Thái Hà, Đống Đa, Hà Nội</t>
   </si>
   <si>
     <t>0101413483</t>
@@ -4582,10 +4582,10 @@
     <t>MEGASTAR</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §¹i Lý vµ TiÕp VËn Megastar</t>
-  </si>
-  <si>
-    <t>B78/67C T«n ThÊt ThuyÕt, P. 16, QuËn 4, TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH Đại Lý và Tiếp Vận Megastar</t>
+  </si>
+  <si>
+    <t>B78/67C Tôn Thất Thuyết, P. 16, Quận 4, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0314355123</t>
@@ -4636,10 +4636,10 @@
     <t>MERIDIAN VN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §¹i Lý tµu biÓn  Meridian ViÖt Nam</t>
-  </si>
-  <si>
-    <t>63A Vâ V¨n TÇn, Ph­êng 6, QuËn 3, Tp Hcm, ViÖt Nam</t>
+    <t>Công ty TNHH Đại Lý tàu biển  Meridian Việt Nam</t>
+  </si>
+  <si>
+    <t>63A Võ Văn Tần, Phường 6, Quận 3, Tp Hcm, Việt Nam</t>
   </si>
   <si>
     <t>0313409601</t>
@@ -4666,10 +4666,10 @@
     <t>MINHCONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i dÞch vô Minh C«ng</t>
-  </si>
-  <si>
-    <t>Sè 204, Khu 7, ThÞ TrÊn Diªm §iÒn, Th¸i Thôy, Th¸i B×nh</t>
+    <t>Công ty cổ phần thương mại dịch vụ Minh Công</t>
+  </si>
+  <si>
+    <t>Số 204, Khu 7, Thị Trấn Diêm Điền, Thái Thụy, Thái Bình</t>
   </si>
   <si>
     <t>1000335618</t>
@@ -4678,10 +4678,10 @@
     <t>MINHHUY</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §Çu T­ Ph¸t TriÓn X©y Dùng vµ Th­¬ng M¹i Minh Huy</t>
-  </si>
-  <si>
-    <t>TÇng 6 tßa nhµ Lª Ph¹m, Sè 98-100 T« HiÖu, ph­êng Lª Ch©n, TP H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Đầu Tư Phát Triển Xây Dựng và Thương Mại Minh Huy</t>
+  </si>
+  <si>
+    <t>Tầng 6 tòa nhà Lê Phạm, Số 98-100 Tô Hiệu, phường Lê Chân, TP Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0202183194</t>
@@ -4690,10 +4690,10 @@
     <t>MINHLUONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn hµng h¶i Minh L­¬ng</t>
-  </si>
-  <si>
-    <t>Tæ 2 - Khu Hµng Kªnh 3 - D­ Hµng Kªnh - Lª Ch©n - H¶i Phßng</t>
+    <t>Công ty cổ phần hàng hải Minh Lương</t>
+  </si>
+  <si>
+    <t>Tổ 2 - Khu Hàng Kênh 3 - Dư Hàng Kênh - Lê Chân - Hải Phòng</t>
   </si>
   <si>
     <t>0201019321</t>
@@ -4702,10 +4702,10 @@
     <t>MINHPHATBACGIANG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH XuÊt NhËp KhÈu Minh Ph¸t B¾c Giang</t>
-  </si>
-  <si>
-    <t>Th«n ThiÒu, X· §ång L¹c, HuyÖn Yªn ThÕ, TØnh B¾c Giang</t>
+    <t>Công ty TNHH Xuất Nhập Khẩu Minh Phát Bắc Giang</t>
+  </si>
+  <si>
+    <t>Thôn Thiều, Xã Đồng Lạc, Huyện Yên Thế, Tỉnh Bắc Giang</t>
   </si>
   <si>
     <t>2400805468</t>
@@ -4714,10 +4714,10 @@
     <t>MINHPHONGHOPNHAT</t>
   </si>
   <si>
-    <t>Chi Nh¸nh Hµ Néi - C«ng ty TNHH Minh Phong Hîp NhÊt</t>
-  </si>
-  <si>
-    <t>P 1105, tÇng 11, toµ nhµ Ocean Park, Sè 1 §µo Duy Anh, Ph­êng Kim Liªn, TP Hµ N«i, VN</t>
+    <t>Chi Nhánh Hà Nội - Công ty TNHH Minh Phong Hợp Nhất</t>
+  </si>
+  <si>
+    <t>P 1105, tầng 11, toà nhà Ocean Park, Số 1 Đào Duy Anh, Phường Kim Liên, TP Hà Nôi, VN</t>
   </si>
   <si>
     <t>0310179156-001</t>
@@ -4726,16 +4726,16 @@
     <t>MINHPHU</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i Minh Phó</t>
+    <t>Công ty TNHH Vận Tải Minh Phú</t>
   </si>
   <si>
     <t>MINHPHUCHP</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Minh Phóc H¶i Phßng</t>
-  </si>
-  <si>
-    <t>Sè 478 Lª Th¸nh T«ng - P. V¹n Mü - Q. Ng« QuyÒn - TP. H¶i Phßng</t>
+    <t>Công ty TNHH Minh Phúc Hải Phòng</t>
+  </si>
+  <si>
+    <t>Số 478 Lê Thánh Tông - P. Vạn Mỹ - Q. Ngô Quyền - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201648249</t>
@@ -4747,7 +4747,7 @@
     <t>MIT SUI O.S.K VIET NAM</t>
   </si>
   <si>
-    <t>15 NguyÔn HuÖ - QuËn 1 - TP. Hå ChÝ Minh</t>
+    <t>15 Nguyễn Huệ - Quận 1 - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0304491818</t>
@@ -4765,10 +4765,10 @@
     <t>MJ LOGISTICS</t>
   </si>
   <si>
-    <t>C«ng ty TNHH MJ LOGISTICS ( Hµ Néi)</t>
-  </si>
-  <si>
-    <t>Hµ Néi</t>
+    <t>Công ty TNHH MJ LOGISTICS ( Hà Nội)</t>
+  </si>
+  <si>
+    <t>Hà Nội</t>
   </si>
   <si>
     <t>MKM TRADING</t>
@@ -4825,10 +4825,10 @@
     <t>MT HANOI</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i vµ vËn t¶i MT Hµ Néi</t>
-  </si>
-  <si>
-    <t>Sè 7C ngâ 38/58/17 ®­êng Xu©n La, Ph­êng Xu©n La, QuËn T©y Hå, TP. Hµ Néi</t>
+    <t>Công ty cổ phần thương mại và vận tải MT Hà Nội</t>
+  </si>
+  <si>
+    <t>Số 7C ngõ 38/58/17 đường Xuân La, Phường Xuân La, Quận Tây Hồ, TP. Hà Nội</t>
   </si>
   <si>
     <t>0108645028</t>
@@ -4837,16 +4837,16 @@
     <t>MYDINH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn Interserco Mü §×nh</t>
+    <t>Công ty cổ phần Interserco Mỹ Đình</t>
   </si>
   <si>
     <t>NAMANH</t>
   </si>
   <si>
-    <t>Cty TNHH ®Çu t­ thiÕt bÞ Nam Anh</t>
-  </si>
-  <si>
-    <t>Sè 08 T«n §¶n, Hµ Néi</t>
+    <t>Cty TNHH đầu tư thiết bị Nam Anh</t>
+  </si>
+  <si>
+    <t>Số 08 Tôn Đản, Hà Nội</t>
   </si>
   <si>
     <t>0102071352</t>
@@ -4855,10 +4855,10 @@
     <t>NAMBANGDUONG</t>
   </si>
   <si>
-    <t>C«ng ty CP Giao NhËn VT Nam B¨ng D­¬ng</t>
-  </si>
-  <si>
-    <t>53 T©n VÜnh - Ph­êng 4 - QuËn 4 - TP. Hå ChÝ Minh</t>
+    <t>Công ty CP Giao Nhận VT Nam Băng Dương</t>
+  </si>
+  <si>
+    <t>53 Tân Vĩnh - Phường 4 - Quận 4 - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0305696247</t>
@@ -4867,10 +4867,10 @@
     <t>NAMHANOI</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn giao nhËn vµ vËn t¶i Nam Hµ Néi</t>
-  </si>
-  <si>
-    <t>Sè 11, ngh¸ch 20, ngâ 100, ®­êng Hoµng Quèc ViÖt, P. NghÜa §«, CG, HN</t>
+    <t>Công ty cổ phần giao nhận và vận tải Nam Hà Nội</t>
+  </si>
+  <si>
+    <t>Số 11, nghách 20, ngõ 100, đường Hoàng Quốc Việt, P. Nghĩa Đô, CG, HN</t>
   </si>
   <si>
     <t>0104067785</t>
@@ -4879,10 +4879,10 @@
     <t>NAMLINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH D­îc PhÈm Hãa ChÊt Nam Linh</t>
-  </si>
-  <si>
-    <t>915/27/12 §­êng Lª v¨n L­¬ng, Êp 13, X· Ph­íc KiÓn, HuyÖn Nhµ BÌ, TP. HCM</t>
+    <t>Công ty TNHH Dược Phẩm Hóa Chất Nam Linh</t>
+  </si>
+  <si>
+    <t>915/27/12 Đường Lê văn Lương, ấp 13, Xã Phước Kiển, Huyện Nhà Bè, TP. HCM</t>
   </si>
   <si>
     <t>0303569980</t>
@@ -4891,10 +4891,10 @@
     <t>NAMPHAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TM &amp; SX Nam Ph¸t</t>
-  </si>
-  <si>
-    <t>Trung Hoµ, Nh©n ChÝnh, Thanh Xu©n, HN</t>
+    <t>Công ty TNHH TM &amp; SX Nam Phát</t>
+  </si>
+  <si>
+    <t>Trung Hoà, Nhân Chính, Thanh Xuân, HN</t>
   </si>
   <si>
     <t>0101806244</t>
@@ -4903,10 +4903,10 @@
     <t>NAMPHUONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn xuÊt nhËp khÈu vµ dÞch vô vËn t¶i Nam Ph­¬ng</t>
-  </si>
-  <si>
-    <t>Phßng 302, sè 337 ®­êng §µ n½ng, P. V¹n Mü, Q. Ng« QuyÒn, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần xuất nhập khẩu và dịch vụ vận tải Nam Phương</t>
+  </si>
+  <si>
+    <t>Phòng 302, số 337 đường Đà nẵng, P. Vạn Mỹ, Q. Ngô Quyền, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201114494</t>
@@ -4915,10 +4915,10 @@
     <t>NAMSON</t>
   </si>
   <si>
-    <t>Cty CP Ph¸t TriÓn C«ng NghiÖp tµu Thñy Nam S¬n</t>
-  </si>
-  <si>
-    <t>Sè 8 §µ N½ng - TT Nói §Ìo, H. Thñy Nguyªn, TP. Thanh Hãa</t>
+    <t>Cty CP Phát Triển Công Nghiệp tàu Thủy Nam Sơn</t>
+  </si>
+  <si>
+    <t>Số 8 Đà Nẵng - TT Núi Đèo, H. Thủy Nguyên, TP. Thanh Hóa</t>
   </si>
   <si>
     <t>0200725148</t>
@@ -4927,10 +4927,10 @@
     <t>NAMTRIEU</t>
   </si>
   <si>
-    <t>C«ng ty TNHH MTV Tæng Cty CNTT nam TriÖu</t>
-  </si>
-  <si>
-    <t>Tam H­ng - Thuû Nguyªn - H¶i Phßng</t>
+    <t>Công ty TNHH MTV Tổng Cty CNTT nam Triệu</t>
+  </si>
+  <si>
+    <t>Tam Hưng - Thuỷ Nguyên - Hải Phòng</t>
   </si>
   <si>
     <t>0200158227</t>
@@ -4966,10 +4966,10 @@
     <t>NDUONG</t>
   </si>
   <si>
-    <t>Cty CP TM &amp; DV Nam D­¬ng</t>
-  </si>
-  <si>
-    <t>14/87 TrÇn H­ng §¹o - H¶i D­¬ng</t>
+    <t>Cty CP TM &amp; DV Nam Dương</t>
+  </si>
+  <si>
+    <t>14/87 Trần Hưng Đạo - Hải Dương</t>
   </si>
   <si>
     <t>0800379676</t>
@@ -4987,10 +4987,10 @@
     <t>NEWSUN</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i vµ vËn t¶i biÓn New Sun</t>
-  </si>
-  <si>
-    <t>Sè 206 phè Lª Träng TÊn, Ph­êng Kh­¬ng Mai, QuËn Thanh Xu©n, TP. hµ Néi, ViÖt Nam</t>
+    <t>Công ty cổ phần thương mại và vận tải biển New Sun</t>
+  </si>
+  <si>
+    <t>Số 206 phố Lê Trọng Tấn, Phường Khương Mai, Quận Thanh Xuân, TP. hà Nội, Việt Nam</t>
   </si>
   <si>
     <t>0107287443</t>
@@ -4999,10 +4999,10 @@
     <t>NGOCANH</t>
   </si>
   <si>
-    <t>Cty TNHH TM Quèc tÕ Ngäc Anh</t>
-  </si>
-  <si>
-    <t>P 1304 nhµ C4, Mü §×nh, Tõ Liªm, Hµ Néi</t>
+    <t>Cty TNHH TM Quốc tế Ngọc Anh</t>
+  </si>
+  <si>
+    <t>P 1304 nhà C4, Mỹ Đình, Từ Liêm, Hà Nội</t>
   </si>
   <si>
     <t>0102182750</t>
@@ -5011,10 +5011,10 @@
     <t>NGOCLINH</t>
   </si>
   <si>
-    <t>DN T­ Nh©n TM Ngäc Linh</t>
-  </si>
-  <si>
-    <t>231 Lª Lîi,Ph­êng 3,QuËn Gß VÊp,TP HCM</t>
+    <t>DN Tư Nhân TM Ngọc Linh</t>
+  </si>
+  <si>
+    <t>231 Lê Lợi,Phường 3,Quận Gò Vấp,TP HCM</t>
   </si>
   <si>
     <t>0304137292</t>
@@ -5023,10 +5023,10 @@
     <t>NGOCSON</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §T TM Ngäc S¬n</t>
-  </si>
-  <si>
-    <t>52 Kim M·, Ba §×nh, Hµ Néi</t>
+    <t>Công ty TNHH ĐT TM Ngọc Sơn</t>
+  </si>
+  <si>
+    <t>52 Kim Mã, Ba Đình, Hà Nội</t>
   </si>
   <si>
     <t>0101836383</t>
@@ -5035,10 +5035,10 @@
     <t>NGOISAOVIET</t>
   </si>
   <si>
-    <t>C«ng ty TNHH H·ng tµu Ng«i Sao ViÖt</t>
-  </si>
-  <si>
-    <t>27-29 §­êng Ng« ThÞ B×, Ph­êng T©n H­ng, Thµnh Phè Hå ChÝ MInh, ViÖt Nam</t>
+    <t>Công ty TNHH Hãng tàu Ngôi Sao Việt</t>
+  </si>
+  <si>
+    <t>27-29 Đường Ngô Thị Bì, Phường Tân Hưng, Thành Phố Hồ Chí MInh, Việt Nam</t>
   </si>
   <si>
     <t>0318773530</t>
@@ -5047,10 +5047,10 @@
     <t>NGUYENDANGVN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH NguyÔn §¨ng ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 12 Ngâ 28/18 ®­êng t¨ng ThiÕt Gi¸p, P. Cæ NhuÕ, Q. B¾c Tõ Liªm, HN</t>
+    <t>Công ty TNHH Nguyễn Đăng Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 12 Ngõ 28/18 đường tăng Thiết Giáp, P. Cổ Nhuế, Q. Bắc Từ Liêm, HN</t>
   </si>
   <si>
     <t>0105188630</t>
@@ -5059,10 +5059,10 @@
     <t>NGUYENHOANG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i Quèc TÕ NguyÔn Hoµng</t>
-  </si>
-  <si>
-    <t>Th«n V¹n H¹nh - ThÞ TrÊn Phó Mü - H.T©n Thµnh - T. Bµ RÞa - Vòng Tµu</t>
+    <t>Công ty TNHH Thương Mại Quốc Tế Nguyễn Hoàng</t>
+  </si>
+  <si>
+    <t>Thôn Vạn Hạnh - Thị Trấn Phú Mỹ - H.Tân Thành - T. Bà Rịa - Vũng Tàu</t>
   </si>
   <si>
     <t>3502224295</t>
@@ -5071,10 +5071,10 @@
     <t>NGUYENPHUC</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng m¹i Nguyªn Phóc</t>
-  </si>
-  <si>
-    <t>An L­ - Thuû Nguyªn _ H¶i Phßng</t>
+    <t>Công ty TNHH Thương mại Nguyên Phúc</t>
+  </si>
+  <si>
+    <t>An Lư - Thuỷ Nguyên _ Hải Phòng</t>
   </si>
   <si>
     <t>0201135102</t>
@@ -5083,10 +5083,10 @@
     <t>NGUYENVANLAP</t>
   </si>
   <si>
-    <t>Hé kinh Doanh NguyÔn V¨n LËp</t>
-  </si>
-  <si>
-    <t>213 ®­êng 8/3 Khãm 4, Ph­êng 5, thµnh phè VÜnh Long</t>
+    <t>Hộ kinh Doanh Nguyễn Văn Lập</t>
+  </si>
+  <si>
+    <t>213 đường 8/3 Khóm 4, Phường 5, thành phố Vĩnh Long</t>
   </si>
   <si>
     <t>1500612838</t>
@@ -5095,10 +5095,10 @@
     <t>NGUYETMINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i vµ DÞch Vô Giao NhËn NguyÖt Minh</t>
-  </si>
-  <si>
-    <t>Sè 28/183 CÇu §Êt, Q. Ng« QuyÒn, TP. H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Thương Mại và Dịch Vụ Giao Nhận Nguyệt Minh</t>
+  </si>
+  <si>
+    <t>Số 28/183 Cầu Đất, Q. Ngô Quyền, TP. Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0200476276</t>
@@ -5107,10 +5107,10 @@
     <t>NHABE</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn cÊp n­íc Nhµ BÌ</t>
-  </si>
-  <si>
-    <t>Phó Mü H­ng - NguyÔn V¨n Linh - P. T©n Phong - Q.7 - TP. HCM</t>
+    <t>Công ty cổ phần cấp nước Nhà Bè</t>
+  </si>
+  <si>
+    <t>Phú Mỹ Hưng - Nguyễn Văn Linh - P. Tân Phong - Q.7 - TP. HCM</t>
   </si>
   <si>
     <t>0304789298</t>
@@ -5119,10 +5119,10 @@
     <t>NHANLUCVOSCO</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Mét Thµnh Viªn Cung øng Nh©n Lùc Vosco</t>
-  </si>
-  <si>
-    <t>Sè 215 L¹ch Tray, Ph­êng §»ng Giang, QuËn Ng« QuyÒn, Thµnh Phè H¶i Phßng</t>
+    <t>Công ty TNHH Một Thành Viên Cung ứng Nhân Lực Vosco</t>
+  </si>
+  <si>
+    <t>Số 215 Lạch Tray, Phường Đằng Giang, Quận Ngô Quyền, Thành Phố Hải Phòng</t>
   </si>
   <si>
     <t>0202113197</t>
@@ -5131,10 +5131,10 @@
     <t>NHATANH</t>
   </si>
   <si>
-    <t>Cty CP §Çu T­ TM &amp; XNK NhËt Anh</t>
-  </si>
-  <si>
-    <t>Trung Yªn - Trung Hoµ - CÇu GiÊy - Hµ Néi</t>
+    <t>Cty CP Đầu Tư TM &amp; XNK Nhật Anh</t>
+  </si>
+  <si>
+    <t>Trung Yên - Trung Hoà - Cầu Giấy - Hà Nội</t>
   </si>
   <si>
     <t>0102374371</t>
@@ -5143,10 +5143,10 @@
     <t>NHATMINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH « t« NhËt Minh</t>
-  </si>
-  <si>
-    <t>10B T¨ng B¹t Hæ, Hai Bµ Tr­ng, Hµ Néi</t>
+    <t>Công ty TNHH ô tô Nhật Minh</t>
+  </si>
+  <si>
+    <t>10B Tăng Bạt Hổ, Hai Bà Trưng, Hà Nội</t>
   </si>
   <si>
     <t>0102391352</t>
@@ -5155,19 +5155,19 @@
     <t>NHATTRI</t>
   </si>
   <si>
-    <t>C«ng ty TNHH DÞch Vô Tµu BiÓn NhÊt TrÝ</t>
-  </si>
-  <si>
-    <t>LÇu 2, 63BC Vâ V¨n TÇn, Ph­êng 6, QuËn 3, TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH Dịch Vụ Tàu Biển Nhất Trí</t>
+  </si>
+  <si>
+    <t>Lầu 2, 63BC Võ Văn Tần, Phường 6, Quận 3, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>NHIETDIENQUANGNINH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn NhiÖt §iÖn Qu¶ng Ninh</t>
-  </si>
-  <si>
-    <t>Tæ 33, Khu phè Hµ Kh¸nh 5, Ph­êng Cao Xanh, TØnh Qu¶ng Ninh, ViÖt Nam</t>
+    <t>Công ty cổ phần Nhiệt Điện Quảng Ninh</t>
+  </si>
+  <si>
+    <t>Tổ 33, Khu phố Hà Khánh 5, Phường Cao Xanh, Tỉnh Quảng Ninh, Việt Nam</t>
   </si>
   <si>
     <t>5700434869</t>
@@ -5176,10 +5176,10 @@
     <t>NHIETDIENUONGBI</t>
   </si>
   <si>
-    <t>C«ng ty NhiÖt §iÖn U«ng BÝ - Chi Nh¸nh Tæng C«ng Ty Ph¸t §iÖn 1</t>
-  </si>
-  <si>
-    <t>Khu phè Quang Trung 6, Ph­êng U«ng BÝ, TØnh Qu¶ng Ninh, ViÖt Nam</t>
+    <t>Công ty Nhiệt Điện Uông Bí - Chi Nhánh Tổng Công Ty Phát Điện 1</t>
+  </si>
+  <si>
+    <t>Khu phố Quang Trung 6, Phường Uông Bí, Tỉnh Quảng Ninh, Việt Nam</t>
   </si>
   <si>
     <t>5701662152-010</t>
@@ -5188,10 +5188,10 @@
     <t>NHOMDAKNONG</t>
   </si>
   <si>
-    <t>CN tËp ®oµn c«ng nghiÖp than - Kho¸ng s¶n ViÖt Nam - C«ng ty Nh«m §¾k N«ng - TKV</t>
-  </si>
-  <si>
-    <t>Th«n 11, x· Nh©n C¬, TØnh L©m §ång, ViÖt Nam</t>
+    <t>CN tập đoàn công nghiệp than - Khoáng sản Việt Nam - Công ty Nhôm Đắk Nông - TKV</t>
+  </si>
+  <si>
+    <t>Thôn 11, xã Nhân Cơ, Tỉnh Lâm Đồng, Việt Nam</t>
   </si>
   <si>
     <t>5700100256-066</t>
@@ -5200,10 +5200,10 @@
     <t>NHONTRACH</t>
   </si>
   <si>
-    <t>C«ng ty CP dÞch vô BÕn Thñy Néi §¹i Nh¬n Tr¹ch</t>
-  </si>
-  <si>
-    <t>Sè 91A §inh Tiªn Hoµng, P3, QuËn B×nh Th¹ch, HCM</t>
+    <t>Công ty CP dịch vụ Bến Thủy Nội Đại Nhơn Trạch</t>
+  </si>
+  <si>
+    <t>Số 91A Đinh Tiên Hoàng, P3, Quận Bình Thạch, HCM</t>
   </si>
   <si>
     <t>0312484589</t>
@@ -5212,10 +5212,10 @@
     <t>NHUKHOI</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TMGN vËn t¶i Nh­ Kh«i</t>
-  </si>
-  <si>
-    <t>B60/10 NguyÔn ThÇn HiÕn P18, Q4 HCM</t>
+    <t>Công ty TNHH TMGN vận tải Như Khôi</t>
+  </si>
+  <si>
+    <t>B60/10 Nguyễn Thần Hiến P18, Q4 HCM</t>
   </si>
   <si>
     <t>0303534120</t>
@@ -5224,10 +5224,10 @@
     <t>NINHBINH</t>
   </si>
   <si>
-    <t>CN Cty CP SX XNK Ninh B×nh t¹i HP</t>
-  </si>
-  <si>
-    <t>Sè 5 §iÖn Biªn Phñ, HP</t>
+    <t>CN Cty CP SX XNK Ninh Bình tại HP</t>
+  </si>
+  <si>
+    <t>Số 5 Điện Biên Phủ, HP</t>
   </si>
   <si>
     <t>2700224383001</t>
@@ -5236,10 +5236,10 @@
     <t>NINHHOA</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn XuÊt NhËp KhÈu Agris Ninh Hßa</t>
-  </si>
-  <si>
-    <t>Th«n Ph­íc L©m - X· T©n §Þnh, TØnh Kh¸nh Hoµ, ViÖt Nam</t>
+    <t>Công ty Cổ Phần Xuất Nhập Khẩu Agris Ninh Hòa</t>
+  </si>
+  <si>
+    <t>Thôn Phước Lâm - Xã Tân Định, Tỉnh Khánh Hoà, Việt Nam</t>
   </si>
   <si>
     <t>4200636590</t>
@@ -5248,10 +5248,10 @@
     <t>NLINH</t>
   </si>
   <si>
-    <t>Cty CP TM &amp; DÞch Vô XNK Ngäc Linh</t>
-  </si>
-  <si>
-    <t>1019 Ng« Gia Tù, §øc Giang, Long Biªn, Hµ Néi</t>
+    <t>Cty CP TM &amp; Dịch Vụ XNK Ngọc Linh</t>
+  </si>
+  <si>
+    <t>1019 Ngô Gia Tự, Đức Giang, Long Biên, Hà Nội</t>
   </si>
   <si>
     <t>0102190487</t>
@@ -5260,10 +5260,10 @@
     <t>NONGNGHIEPXANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH S¶n XuÊt - Cung øng VËt T­ N«ng NghiÖp Xanh</t>
-  </si>
-  <si>
-    <t>TÇng TrÖt, tßa nhµ Rosana - Sè 60 NguyÔn §×nh ChiÓu, P §akao, Q.1,HCM</t>
+    <t>Công ty TNHH Sản Xuất - Cung ứng Vật Tư Nông Nghiệp Xanh</t>
+  </si>
+  <si>
+    <t>Tầng Trệt, tòa nhà Rosana - Số 60 Nguyễn Đình Chiểu, P Đakao, Q.1,HCM</t>
   </si>
   <si>
     <t>0313408439</t>
@@ -5293,10 +5293,10 @@
     <t>NOVASTAR</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i DÞch Vô Novastar</t>
-  </si>
-  <si>
-    <t>Sè 21 §Æng Kim Në, Ph­êng C¸t Dµi, QuËn Lª Ch©n, TP. H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Thương Mại Dịch Vụ Novastar</t>
+  </si>
+  <si>
+    <t>Số 21 Đặng Kim Nở, Phường Cát Dài, Quận Lê Chân, TP. Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0202124304</t>
@@ -5314,10 +5314,10 @@
     <t>NUOCTRONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ®­êng n­íc trong</t>
-  </si>
-  <si>
-    <t>x· T©n Héi, HuyÖn T©n Ch©u, TØnh T©y Ninh</t>
+    <t>Công ty cổ phần đường nước trong</t>
+  </si>
+  <si>
+    <t>xã Tân Hội, Huyện Tân Châu, Tỉnh Tây Ninh</t>
   </si>
   <si>
     <t>3900243272005</t>
@@ -5377,10 +5377,10 @@
     <t>OGCM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Quèc TÕ Hoµn Vò H­ng OGCM</t>
-  </si>
-  <si>
-    <t>Sè 4H TrÇn H­ng §¹o - Hoµng V¨n Thô - Hång Bµng - H¶i Phßng</t>
+    <t>Công ty TNHH Quốc Tế Hoàn Vũ Hưng OGCM</t>
+  </si>
+  <si>
+    <t>Số 4H Trần Hưng Đạo - Hoàng Văn Thụ - Hồng Bàng - Hải Phòng</t>
   </si>
   <si>
     <t>0201108268</t>
@@ -5395,10 +5395,10 @@
     <t>OMEGA</t>
   </si>
   <si>
-    <t>Cty TNHH Giao NhËn Alpha To Omega</t>
-  </si>
-  <si>
-    <t>F4, T19, 27 Huúnh Thóc Kh¸ng - §èng §a -  Hµ Néi</t>
+    <t>Cty TNHH Giao Nhận Alpha To Omega</t>
+  </si>
+  <si>
+    <t>F4, T19, 27 Huỳnh Thúc Kháng - Đống Đa -  Hà Nội</t>
   </si>
   <si>
     <t>0102123106</t>
@@ -5407,10 +5407,10 @@
     <t>OPL</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i biÓn OPL</t>
-  </si>
-  <si>
-    <t>Km56, Quèc Lé 5, x· nam §ång, TP. H¶i D­¬ng, TØnh H¶i D­¬ng</t>
+    <t>Công ty cổ phần vận tải biển OPL</t>
+  </si>
+  <si>
+    <t>Km56, Quốc Lộ 5, xã nam Đồng, TP. Hải Dương, Tỉnh Hải Dương</t>
   </si>
   <si>
     <t>OSLO BULK</t>
@@ -5425,10 +5425,10 @@
     <t>OSSTEM INPLANT</t>
   </si>
   <si>
-    <t>C¤NG TY TNHH OSSTEM INPLANT VINA</t>
-  </si>
-  <si>
-    <t>TÇng 5, toµ nhµ VNPT, sè 1487 NguyÔn V¨n Linh, ph­êng T©n H­ng, TP HCM, VN</t>
+    <t>CÔNG TY TNHH OSSTEM INPLANT VINA</t>
+  </si>
+  <si>
+    <t>Tầng 5, toà nhà VNPT, số 1487 Nguyễn Văn Linh, phường Tân Hưng, TP HCM, VN</t>
   </si>
   <si>
     <t>0311109514</t>
@@ -5437,10 +5437,10 @@
     <t>OTOTT</t>
   </si>
   <si>
-    <t>Cty TNHH ¤ t« Tr­êng Thµnh</t>
-  </si>
-  <si>
-    <t>78 phè Lim, Tiªn Du, B¾c Ninh</t>
+    <t>Cty TNHH Ô tô Trường Thành</t>
+  </si>
+  <si>
+    <t>78 phố Lim, Tiên Du, Bắc Ninh</t>
   </si>
   <si>
     <t>2300224389</t>
@@ -5467,10 +5467,10 @@
     <t>PACIFIC LINES</t>
   </si>
   <si>
-    <t>C«ng ty TNHH PACIFIC LINES</t>
-  </si>
-  <si>
-    <t>45D/19 §­êng D5, Ph­êng Th¹ch Mü T©y, Thµnh Phè Hå ChÝ MInh, ViÖt Nam</t>
+    <t>Công ty TNHH PACIFIC LINES</t>
+  </si>
+  <si>
+    <t>45D/19 Đường D5, Phường Thạch Mỹ Tây, Thành Phố Hồ Chí MInh, Việt Nam</t>
   </si>
   <si>
     <t>0309912234</t>
@@ -5500,10 +5500,10 @@
     <t>PAINT VIETNAM</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn CITY PAINT ViÖt Nam</t>
-  </si>
-  <si>
-    <t>¤ sè 2, Khu C khu ®Êu gi¸ QuyÒn Sö Dông §Êt - P. Mü §×nh 2 - QuËn Nam Tõ Liªm - HN</t>
+    <t>Công ty Cổ Phần CITY PAINT Việt Nam</t>
+  </si>
+  <si>
+    <t>Ô số 2, Khu C khu đấu giá Quyền Sử Dụng Đất - P. Mỹ Đình 2 - Quận Nam Từ Liêm - HN</t>
   </si>
   <si>
     <t>0106954221</t>
@@ -5545,10 +5545,10 @@
     <t>PENASCOP</t>
   </si>
   <si>
-    <t>C«ng ty TNHH PENASCOP ViÖt Nam</t>
-  </si>
-  <si>
-    <t>3G Phæ Quang, Ph­êng 2, QuËn T©n B×nh, TP. HCM</t>
+    <t>Công ty TNHH PENASCOP Việt Nam</t>
+  </si>
+  <si>
+    <t>3G Phổ Quang, Phường 2, Quận Tân Bình, TP. HCM</t>
   </si>
   <si>
     <t>0313234976</t>
@@ -5557,10 +5557,10 @@
     <t>PHAMHAI</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i VËn T¶i Vµ XuÊt NhËp KhÈu Ph¹m H¶i</t>
-  </si>
-  <si>
-    <t>Sè 229 §µ N½ng, ph­êng CÇu Tre, QuËn Ng« QuyÒn, Thµnh Phè H¶i Phßng</t>
+    <t>Công ty TNHH Thương Mại Vận Tải Và Xuất Nhập Khẩu Phạm Hải</t>
+  </si>
+  <si>
+    <t>Số 229 Đà Nẵng, phường Cầu Tre, Quận Ngô Quyền, Thành Phố Hải Phòng</t>
   </si>
   <si>
     <t>0200944492</t>
@@ -5569,10 +5569,10 @@
     <t>PHAMTHANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Logistics Ph¹m Thµnh</t>
-  </si>
-  <si>
-    <t>Sè 5C/55 NguyÔn §øc C¶nh, Ph­êng An Biªn, QuËn Lª Ch©n, Thµnh Phè H¶i Phßng, VN</t>
+    <t>Công ty TNHH Logistics Phạm Thành</t>
+  </si>
+  <si>
+    <t>Số 5C/55 Nguyễn Đức Cảnh, Phường An Biên, Quận Lê Chân, Thành Phố Hải Phòng, VN</t>
   </si>
   <si>
     <t>0201765168</t>
@@ -5581,10 +5581,10 @@
     <t>PHANRANG</t>
   </si>
   <si>
-    <t>C«ng ty CP ®­êng Biªn Hßa - Phan Rang</t>
-  </si>
-  <si>
-    <t>160 B¸c ¸i - §« Vinh - TP. Phan Rang - Th¸p Chµm - TØnh Ninh ThuËn</t>
+    <t>Công ty CP đường Biên Hòa - Phan Rang</t>
+  </si>
+  <si>
+    <t>160 Bác ái - Đô Vinh - TP. Phan Rang - Tháp Chàm - Tỉnh Ninh Thuận</t>
   </si>
   <si>
     <t>4500138596</t>
@@ -5602,10 +5602,10 @@
     <t>PHILONG</t>
   </si>
   <si>
-    <t>Cty CP Quèc tÕ Phi Long</t>
-  </si>
-  <si>
-    <t>187 Nghi Tµm, T©y Hå, HN</t>
+    <t>Cty CP Quốc tế Phi Long</t>
+  </si>
+  <si>
+    <t>187 Nghi Tàm, Tây Hồ, HN</t>
   </si>
   <si>
     <t>0102454700</t>
@@ -5614,10 +5614,10 @@
     <t>PHIMA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i BiÓn vµ §Çu T­ Phi M·</t>
-  </si>
-  <si>
-    <t>LÇ 1 Cao èc M-H sè 728-730 Vâ V¨n KiÖt - Ph­êng 1 - QuËn 5 - TP. HCM</t>
+    <t>Công ty TNHH Vận Tải Biển và Đầu Tư Phi Mã</t>
+  </si>
+  <si>
+    <t>Lầ 1 Cao ốc M-H số 728-730 Võ Văn Kiệt - Phường 1 - Quận 5 - TP. HCM</t>
   </si>
   <si>
     <t>0312191409</t>
@@ -5635,10 +5635,10 @@
     <t>PHUAN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH vËn T¶i Phó An</t>
-  </si>
-  <si>
-    <t>Th«n Phó Thä - ThÞ TrÊn C¸t Thµnh - HuyÖn Trùc ninh - TØnh Nam §Þnh</t>
+    <t>Công ty TNHH vận Tải Phú An</t>
+  </si>
+  <si>
+    <t>Thôn Phú Thọ - Thị Trấn Cát Thành - Huyện Trực ninh - Tỉnh Nam Định</t>
   </si>
   <si>
     <t>0601111219</t>
@@ -5647,10 +5647,10 @@
     <t>PHUCAN</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn §Çu T­ C«ng NghÖ Phóc An</t>
-  </si>
-  <si>
-    <t>D56 - 361 T©n Xu©n - Xu©n §Ønh - Tõ Liªm - Hµ Néi</t>
+    <t>Công ty Cổ Phần Đầu Tư Công Nghệ Phúc An</t>
+  </si>
+  <si>
+    <t>D56 - 361 Tân Xuân - Xuân Đỉnh - Từ Liêm - Hà Nội</t>
   </si>
   <si>
     <t>0104218018</t>
@@ -5662,7 +5662,7 @@
     <t>Cty TNHH TM Phó Nam</t>
   </si>
   <si>
-    <t>Sè 8/104 §øc Giang, Long Biªn, Hµ Néi</t>
+    <t>Số 8/104 Đức Giang, Long Biên, Hà Nội</t>
   </si>
   <si>
     <t>0101065892</t>
@@ -5671,19 +5671,19 @@
     <t>PHUONGANPHAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Ph­¬ng An Ph¸t</t>
-  </si>
-  <si>
-    <t>25A4 Nam Ph¸p 1 - P. §»ng Giang - Q. Ng« QuyÒn - TP. H¶i Phßng</t>
+    <t>Công ty TNHH Phương An Phát</t>
+  </si>
+  <si>
+    <t>25A4 Nam Pháp 1 - P. Đằng Giang - Q. Ngô Quyền - TP. Hải Phòng</t>
   </si>
   <si>
     <t>PHUSON</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Phó S¬n</t>
-  </si>
-  <si>
-    <t>310 Bµ TriÖu, §«ng Thä, Thanh Ho¸</t>
+    <t>Công ty TNHH Phú Sơn</t>
+  </si>
+  <si>
+    <t>310 Bà Triệu, Đông Thọ, Thanh Hoá</t>
   </si>
   <si>
     <t>2800790470</t>
@@ -5692,10 +5692,10 @@
     <t>PIL VN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH PIL ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 161 - 163 ®­êng Ký Con, ph­êng BÕn Thµnh, TP Hå ChÝ Minh, VN</t>
+    <t>Công ty TNHH PIL Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 161 - 163 đường Ký Con, phường Bến Thành, TP Hồ Chí Minh, VN</t>
   </si>
   <si>
     <t>0303449450</t>
@@ -5725,10 +5725,10 @@
     <t>PNAM</t>
   </si>
   <si>
-    <t>Cty CP tËp ®oµn TM Ph­¬ng Nam</t>
-  </si>
-  <si>
-    <t>P 104 tËp thÓ viÖn M¸ Lenin, Ba ®×nh, Hµ Néi</t>
+    <t>Cty CP tập đoàn TM Phương Nam</t>
+  </si>
+  <si>
+    <t>P 104 tập thể viện Má Lenin, Ba đình, Hà Nội</t>
   </si>
   <si>
     <t>0102278068</t>
@@ -5737,10 +5737,10 @@
     <t>POSCO SS- VINA</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn thÐp Posco Yamato Vina</t>
-  </si>
-  <si>
-    <t>§­êng N1 - KCN Phó Mü 2, Ph­êng Phó Mü, TP Hå ChÝ Minh, VN</t>
+    <t>Công ty cổ phần thép Posco Yamato Vina</t>
+  </si>
+  <si>
+    <t>Đường N1 - KCN Phú Mỹ 2, Phường Phú Mỹ, TP Hồ Chí Minh, VN</t>
   </si>
   <si>
     <t>3501620257</t>
@@ -5806,10 +5806,10 @@
     <t>PTH</t>
   </si>
   <si>
-    <t>C¬ Së Kinh Doanh Than §¸ Ph¹m ThÞ H­êng</t>
-  </si>
-  <si>
-    <t>43/9A, B×nh §­êng 2, An B×nh, DÜ An, B×nh D­¬ng</t>
+    <t>Cơ Sở Kinh Doanh Than Đá Phạm Thị Hường</t>
+  </si>
+  <si>
+    <t>43/9A, Bình Đường 2, An Bình, Dĩ An, Bình Dương</t>
   </si>
   <si>
     <t>3700801586</t>
@@ -5824,10 +5824,10 @@
     <t>QCTH</t>
   </si>
   <si>
-    <t>C«ng ty TB &amp; Qu¶ng C¸o TruyÒn H×nh</t>
-  </si>
-  <si>
-    <t>65 L¹c Trung, HN</t>
+    <t>Công ty TB &amp; Quảng Cáo Truyền Hình</t>
+  </si>
+  <si>
+    <t>65 Lạc Trung, HN</t>
   </si>
   <si>
     <t>0100110006005</t>
@@ -5836,10 +5836,10 @@
     <t>QINGSAN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH XuÊt NhËp KhÈu QINGSAN</t>
-  </si>
-  <si>
-    <t>Xãm Chanh - X· S¬n Hïng - HuyÖn Thanh S¬n - TØnh Phó Thä</t>
+    <t>Công ty TNHH Xuất Nhập Khẩu QINGSAN</t>
+  </si>
+  <si>
+    <t>Xóm Chanh - Xã Sơn Hùng - Huyện Thanh Sơn - Tỉnh Phú Thọ</t>
   </si>
   <si>
     <t>2600920411</t>
@@ -5848,10 +5848,10 @@
     <t>QLTAU AMANN</t>
   </si>
   <si>
-    <t>V¨n Phßng §¹i DiÖn C«ng Ty TNHH Qu¶n Lý Tµu AMANN t¹i ViÖt Nam</t>
-  </si>
-  <si>
-    <t>TÇng 9, Tßa nhµ Mobifone , Khu Phó H¶i, P.Anh Dòng, Q.D­¬ng Kinh, TP.H¶i Phßng, VN</t>
+    <t>Văn Phòng Đại Diện Công Ty TNHH Quản Lý Tàu AMANN tại Việt Nam</t>
+  </si>
+  <si>
+    <t>Tầng 9, Tòa nhà Mobifone , Khu Phú Hải, P.Anh Dũng, Q.Dương Kinh, TP.Hải Phòng, VN</t>
   </si>
   <si>
     <t>0202253589</t>
@@ -5860,10 +5860,10 @@
     <t>QPHAT</t>
   </si>
   <si>
-    <t>Cty TNHH Qu¶ng Ph¸t</t>
-  </si>
-  <si>
-    <t>Th«n Trung Thµnh II, x· Minh TiÕn, Lôc Yªn, tØnh Yªn B¸i</t>
+    <t>Cty TNHH Quảng Phát</t>
+  </si>
+  <si>
+    <t>Thôn Trung Thành II, xã Minh Tiến, Lục Yên, tỉnh Yên Bái</t>
   </si>
   <si>
     <t>5200216728</t>
@@ -5872,10 +5872,10 @@
     <t>QTR</t>
   </si>
   <si>
-    <t>Cty TNHH §Çu t­ TM Quúnh Trang</t>
-  </si>
-  <si>
-    <t>29/60 Hoµng Mai - Hµ Néi</t>
+    <t>Cty TNHH Đầu tư TM Quỳnh Trang</t>
+  </si>
+  <si>
+    <t>29/60 Hoàng Mai - Hà Nội</t>
   </si>
   <si>
     <t>0102112168</t>
@@ -5884,10 +5884,10 @@
     <t>QUANGHUNG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Barwil VËn T¶i Quang H­ng</t>
-  </si>
-  <si>
-    <t>148 Kh¸nh Héi - Ph­êng 6 - QuËn 4</t>
+    <t>Công ty TNHH Barwil Vận Tải Quang Hưng</t>
+  </si>
+  <si>
+    <t>148 Khánh Hội - Phường 6 - Quận 4</t>
   </si>
   <si>
     <t>0303673276</t>
@@ -5896,10 +5896,10 @@
     <t>QUANHAIAN</t>
   </si>
   <si>
-    <t>Phßng tµi chÝnh kÕ ho¹ch QuËn H¶i An</t>
-  </si>
-  <si>
-    <t>Trô së UBND QuËn h¶i An, Khu 5 h¹ Lòng, P. §»ng H¶i, Q. H¶i An, HP</t>
+    <t>Phòng tài chính kế hoạch Quận Hải An</t>
+  </si>
+  <si>
+    <t>Trụ sở UBND Quận hải An, Khu 5 hạ Lũng, P. Đằng Hải, Q. Hải An, HP</t>
   </si>
   <si>
     <t>0200970118</t>
@@ -5917,10 +5917,10 @@
     <t>QUOCTE ITC</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i vµ vËn t¶i quèc tÕ ITC</t>
-  </si>
-  <si>
-    <t>Sè 209 L« N12, Khu ®« thÞ míi, Ph­êng §»ng H¶i, QuËn h¶i An, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần thương mại và vận tải quốc tế ITC</t>
+  </si>
+  <si>
+    <t>Số 209 Lô N12, Khu đô thị mới, Phường Đằng Hải, Quận hải An, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201141219</t>
@@ -5929,10 +5929,10 @@
     <t>QUOCTE KA</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i Quèc TÕ KA</t>
-  </si>
-  <si>
-    <t>Sè 95 Lý Nam §Õ, P. Cöa §«ng, Q. Hoµn KiÕm, TP. Hµ Néi</t>
+    <t>Công ty cổ phần vận tải Quốc Tế KA</t>
+  </si>
+  <si>
+    <t>Số 95 Lý Nam Đế, P. Cửa Đông, Q. Hoàn Kiếm, TP. Hà Nội</t>
   </si>
   <si>
     <t>0102921056</t>
@@ -5941,10 +5941,10 @@
     <t>QUOCTEHALINH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dÞch vô vµ th­¬ng m¹i quèc tÕ Hµ Linh</t>
-  </si>
-  <si>
-    <t>Sè 4 ngâ 99/54 Phè §Þnh C«ng H¹, Ph­êng §Þnh C«ng, QuËn Hoµng Mai, TP. Hµ Néi</t>
+    <t>Công ty cổ phần dịch vụ và thương mại quốc tế Hà Linh</t>
+  </si>
+  <si>
+    <t>Số 4 ngõ 99/54 Phố Định Công Hạ, Phường Định Công, Quận Hoàng Mai, TP. Hà Nội</t>
   </si>
   <si>
     <t>0107502203</t>
@@ -5953,10 +5953,10 @@
     <t>QUOCTEQHP</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TiÕp vËn Quèc tÕ QHP</t>
-  </si>
-  <si>
-    <t>Phßng 702, TÇng 7 Tßa nhµ LP, sè 508 Lª Th¸nh T«ng, Ph­êng Ng« QuyÒn, HP, VN</t>
+    <t>Công ty TNHH Tiếp vận Quốc tế QHP</t>
+  </si>
+  <si>
+    <t>Phòng 702, Tầng 7 Tòa nhà LP, số 508 Lê Thánh Tông, Phường Ngô Quyền, HP, VN</t>
   </si>
   <si>
     <t>0202108239</t>
@@ -5965,10 +5965,10 @@
     <t>QUYNHTR</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Quúnh Trang</t>
-  </si>
-  <si>
-    <t>L¹i Xu©n - Thñy Nguyªn - H¶i Phßng</t>
+    <t>Công ty TNHH Quỳnh Trang</t>
+  </si>
+  <si>
+    <t>Lại Xuân - Thủy Nguyên - Hải Phòng</t>
   </si>
   <si>
     <t>0200905528</t>
@@ -5977,10 +5977,10 @@
     <t>QUYSANG</t>
   </si>
   <si>
-    <t>CN c«ng ty cæ phÇn th­¬ng m¹i vËn t¶i biÓn Quý Sang</t>
-  </si>
-  <si>
-    <t>Sè 292 Khu 5 - thÞ TrÊn Diªm §iÒm - HuyÖn Th¸i Thuþ - TØnh Th¸i B×nh</t>
+    <t>CN công ty cổ phần thương mại vận tải biển Quý Sang</t>
+  </si>
+  <si>
+    <t>Số 292 Khu 5 - thị Trấn Diêm Điềm - Huyện Thái Thuỵ - Tỉnh Thái Bình</t>
   </si>
   <si>
     <t>1000398424001</t>
@@ -6049,10 +6049,10 @@
     <t>RUOU HN</t>
   </si>
   <si>
-    <t>C«ng ty CP Cån R­îu Hµ Néi</t>
-  </si>
-  <si>
-    <t>94 Lß §óc - Thµnh Phè Hµ Néi</t>
+    <t>Công ty CP Cồn Rượu Hà Nội</t>
+  </si>
+  <si>
+    <t>94 Lò Đúc - Thành Phố Hà Nội</t>
   </si>
   <si>
     <t>0100102245</t>
@@ -6064,7 +6064,7 @@
     <t>S.Alam Refined Sugar Industries</t>
   </si>
   <si>
-    <t>I Sanga, Charpather Gh©t Cittagong, Bµnladesh</t>
+    <t>I Sanga, Charpather Ghât Cittagong, Bànladesh</t>
   </si>
   <si>
     <t>S.SHIP</t>
@@ -6079,19 +6079,19 @@
     <t>S5 ASIA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH S5 ASIA</t>
-  </si>
-  <si>
-    <t>Phßng 502-503, lÇu 5, sè 45, ®­êng Vâ ThÞ S¸u, Ph­êng §a Kao, Q1, HCM</t>
+    <t>Công ty TNHH S5 ASIA</t>
+  </si>
+  <si>
+    <t>Phòng 502-503, lầu 5, số 45, đường Võ Thị Sáu, Phường Đa Kao, Q1, HCM</t>
   </si>
   <si>
     <t>S5 VIET NAM</t>
   </si>
   <si>
-    <t>Chi nh¸nh c«ng ty TNHH S5 ViÖt Nam t¹i H¶i Phßng</t>
-  </si>
-  <si>
-    <t>TÇng 10, sè 2/16D ®­êng Lª Hång Phong, Ph­êng H¶i An, TP H¶i Phßng, VN</t>
+    <t>Chi nhánh công ty TNHH S5 Việt Nam tại Hải Phòng</t>
+  </si>
+  <si>
+    <t>Tầng 10, số 2/16D đường Lê Hồng Phong, Phường Hải An, TP Hải Phòng, VN</t>
   </si>
   <si>
     <t>0313918863-001</t>
@@ -6109,10 +6109,10 @@
     <t>SAIKO</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng m¹i vµ Giao NhËn Quèc TÕ Saiko</t>
-  </si>
-  <si>
-    <t>Phngf 201, Tßa Nhµ Lª Ph¹m, Sè 508 Lª Th¸nh T«ng, P. v¹n Mü, NQ, HP</t>
+    <t>Công ty TNHH Thương mại và Giao Nhận Quốc Tế Saiko</t>
+  </si>
+  <si>
+    <t>Phngf 201, Tòa Nhà Lê Phạm, Số 508 Lê Thánh Tông, P. vạn Mỹ, NQ, HP</t>
   </si>
   <si>
     <t>0201763925</t>
@@ -6127,10 +6127,10 @@
     <t>SAOBAC</t>
   </si>
   <si>
-    <t>C«ng Ty CP TM Vµ VËn T¶i Sao B¾c</t>
-  </si>
-  <si>
-    <t>Sè 11 - Ngâ 463 - §éi CÊn - VÜnh Phóc - Ba §×nh - Hµ Néi</t>
+    <t>Công Ty CP TM Và Vận Tải Sao Bắc</t>
+  </si>
+  <si>
+    <t>Số 11 - Ngõ 463 - Đội Cấn - Vĩnh Phúc - Ba Đình - Hà Nội</t>
   </si>
   <si>
     <t>0102699073</t>
@@ -6139,10 +6139,10 @@
     <t>SAOSANG</t>
   </si>
   <si>
-    <t>Cty TNHH Giao nhËn Sao S¸ng</t>
-  </si>
-  <si>
-    <t>LÇu 2, sè 1 Phæ Quang, T©n B×nh, Hå ChÝ Minh</t>
+    <t>Cty TNHH Giao nhận Sao Sáng</t>
+  </si>
+  <si>
+    <t>Lầu 2, số 1 Phổ Quang, Tân Bình, Hồ Chí Minh</t>
   </si>
   <si>
     <t>0302922201</t>
@@ -6151,10 +6151,10 @@
     <t>SAOTOP</t>
   </si>
   <si>
-    <t>C«ng ty TNHH MTV th­¬ng m¹i dÞch vô Sao Top</t>
-  </si>
-  <si>
-    <t>923B/3 B×nh Thung - khu phè B×nh Thung 2 - P. B×nh An - TX DÜ An - BD</t>
+    <t>Công ty TNHH MTV thương mại dịch vụ Sao Top</t>
+  </si>
+  <si>
+    <t>923B/3 Bình Thung - khu phố Bình Thung 2 - P. Bình An - TX Dĩ An - BD</t>
   </si>
   <si>
     <t>SEA</t>
@@ -6169,10 +6169,10 @@
     <t>SEABANK</t>
   </si>
   <si>
-    <t>Ng©n hµng TMCP §«ng Nam ¸ - CN H¶i An</t>
-  </si>
-  <si>
-    <t>Thöa 17 - Khu B1 - L« 7b Lª Hång Phong - Ng« QuyÒn - H¶i Phßng</t>
+    <t>Ngân hàng TMCP Đông Nam á - CN Hải An</t>
+  </si>
+  <si>
+    <t>Thửa 17 - Khu B1 - Lô 7b Lê Hồng Phong - Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0200253985052</t>
@@ -6208,10 +6208,10 @@
     <t>SELLANGAS</t>
   </si>
   <si>
-    <t>C¤NG TY TNHH SELLAN GAS</t>
-  </si>
-  <si>
-    <t>TÇng 4, Tßa nhµ  Ocean Park,Sè 1 §µo Duy Anh,Ph­êng Ph­¬ng Mai, QuËn §èng §a, HN</t>
+    <t>CÔNG TY TNHH SELLAN GAS</t>
+  </si>
+  <si>
+    <t>Tầng 4, Tòa nhà  Ocean Park,Số 1 Đào Duy Anh,Phường Phương Mai, Quận Đống Đa, HN</t>
   </si>
   <si>
     <t>0200887195</t>
@@ -6220,10 +6220,10 @@
     <t>SENVANG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dÇu khÝ vµ bÊt ®éng s¶n sen vµng</t>
-  </si>
-  <si>
-    <t>Sè 67 Phã §øc ChÝnh, Ph­êng Trøc b¹ch, QuËn Ba §×nh, Thµnh Phè Hµ Néi, ViÖt Nam</t>
+    <t>Công ty cổ phần dầu khí và bất động sản sen vàng</t>
+  </si>
+  <si>
+    <t>Số 67 Phó Đức Chính, Phường Trức bạch, Quận Ba Đình, Thành Phố Hà Nội, Việt Nam</t>
   </si>
   <si>
     <t>0108209906</t>
@@ -6283,7 +6283,7 @@
     <t>SHARAF SHIPPING AGENCY LLC</t>
   </si>
   <si>
-    <t>3RD FLOOR SHARAF BUILDING, AL M¢N ROAD, PO Bâ 576, DUBAI</t>
+    <t>3RD FLOOR SHARAF BUILDING, AL MÂN ROAD, PO Bõ 576, DUBAI</t>
   </si>
   <si>
     <t>SHEN ZHONG</t>
@@ -6310,10 +6310,10 @@
     <t>SHINHAN VN</t>
   </si>
   <si>
-    <t>Ng©n hµng TNHH MTV SHINHAN ViÖt Nam - CN H¶i Phßng</t>
-  </si>
-  <si>
-    <t>Thöa 19 - L« B7 - §­êng Lª Hång Phong - P. §«ng Khª - Q. Ng« QuyÒn HP</t>
+    <t>Ngân hàng TNHH MTV SHINHAN Việt Nam - CN Hải Phòng</t>
+  </si>
+  <si>
+    <t>Thửa 19 - Lô B7 - Đường Lê Hồng Phong - P. Đông Khê - Q. Ngô Quyền HP</t>
   </si>
   <si>
     <t>0309103635013</t>
@@ -6334,10 +6334,10 @@
     <t>SI AM</t>
   </si>
   <si>
-    <t>Cty TNHH ViÖt Si Am</t>
-  </si>
-  <si>
-    <t>357C/8 Néi Ho¸ 1, x· B×nh An, huyÖn DÜ An, B×nh D­¬ng</t>
+    <t>Cty TNHH Việt Si Am</t>
+  </si>
+  <si>
+    <t>357C/8 Nội Hoá 1, xã Bình An, huyện Dĩ An, Bình Dương</t>
   </si>
   <si>
     <t>3700783746</t>
@@ -6379,7 +6379,7 @@
     <t>SIVA BULK DMCC</t>
   </si>
   <si>
-    <t>Ên §é</t>
+    <t>ấn Độ</t>
   </si>
   <si>
     <t>SJS LOGICS</t>
@@ -6391,10 +6391,10 @@
     <t>SKY LOGISTICS</t>
   </si>
   <si>
-    <t>Công ty TNHH Green Sky Logistics ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 17, ngâ 529, §­êng 72m PDP Trung B×nh, P. D­¬ng Néi, Hµ §«ng, Hµ Néi</t>
+    <t>Cụng ty TNHH Green Sky Logistics Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 17, ngõ 529, Đường 72m PDP Trung Bình, P. Dương Nội, Hà Đông, Hà Nội</t>
   </si>
   <si>
     <t>SKYLINE.LTD</t>
@@ -6415,10 +6415,10 @@
     <t>SNM</t>
   </si>
   <si>
-    <t>Cty TNHH giao nhËn VT &amp;TM S.N.M</t>
-  </si>
-  <si>
-    <t>51 §B, TrÇn H­ng §¹o, HP</t>
+    <t>Cty TNHH giao nhận VT &amp;TM S.N.M</t>
+  </si>
+  <si>
+    <t>51 ĐB, Trần Hưng Đạo, HP</t>
   </si>
   <si>
     <t>0200668637</t>
@@ -6433,10 +6433,10 @@
     <t>SONA</t>
   </si>
   <si>
-    <t>Cty cung øng nh©n lùc Quèc tÕ &amp; th­¬ng m¹i ( SONA)</t>
-  </si>
-  <si>
-    <t>34 §¹i Cå ViÖt, HN</t>
+    <t>Cty cung ứng nhân lực Quốc tế &amp; thương mại ( SONA)</t>
+  </si>
+  <si>
+    <t>34 Đại Cồ Việt, HN</t>
   </si>
   <si>
     <t>01001104151</t>
@@ -6454,10 +6454,10 @@
     <t>SONHAIPHONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn s¬n H¶i Phßng</t>
-  </si>
-  <si>
-    <t>12 L¹ch tray - Ng« QuyÒn - H¶i Phßng</t>
+    <t>Công ty cổ phần sơn Hải Phòng</t>
+  </si>
+  <si>
+    <t>12 Lạch tray - Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0200575580</t>
@@ -6466,10 +6466,10 @@
     <t>SONHOA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH S¶n XuÊt vµ Th­¬ng M¹i V«i S¬n Hßa</t>
-  </si>
-  <si>
-    <t>10/1 Quèc Lé 1A, Khu phè 3, Ph­êng HiÖp B×nh Ph­íc, Thµnh Phè Thñ §øc, TP. Hå ChÝ h</t>
+    <t>Công ty TNHH Sản Xuất và Thương Mại Vôi Sơn Hòa</t>
+  </si>
+  <si>
+    <t>10/1 Quốc Lộ 1A, Khu phố 3, Phường Hiệp Bình Phước, Thành Phố Thủ Đức, TP. Hồ Chí h</t>
   </si>
   <si>
     <t>0317149337</t>
@@ -6478,10 +6478,10 @@
     <t>SOTAICHINH</t>
   </si>
   <si>
-    <t>Së tµi chÝnh H¶i Phßng</t>
-  </si>
-  <si>
-    <t>Sè 10/15 A ®­êng Lª Hång Phong - Ph­êng §»ng L©m - QuËn h¶i An - H¶i Phßng</t>
+    <t>Sở tài chính Hải Phòng</t>
+  </si>
+  <si>
+    <t>Số 10/15 A đường Lê Hồng Phong - Phường Đằng Lâm - Quận hải An - Hải Phòng</t>
   </si>
   <si>
     <t>0200923421</t>
@@ -6496,10 +6496,10 @@
     <t>SSE</t>
   </si>
   <si>
-    <t>Cty SX thÐp óc SSE</t>
-  </si>
-  <si>
-    <t>Km 9 VËt C¸ch, Qu¸n Toan, Hång Bµng, HP</t>
+    <t>Cty SX thép úc SSE</t>
+  </si>
+  <si>
+    <t>Km 9 Vật Cách, Quán Toan, Hồng Bàng, HP</t>
   </si>
   <si>
     <t>0200373471</t>
@@ -6529,10 +6529,10 @@
     <t>SUPERVICTORY</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Super Victory</t>
-  </si>
-  <si>
-    <t>Km 5 ®­êng Ph¹m V¨n §ång, P. Anh Dòng, Q. D­¬ng Kinh, TP. H¶i Phßng</t>
+    <t>Công ty TNHH Super Victory</t>
+  </si>
+  <si>
+    <t>Km 5 đường Phạm Văn Đồng, P. Anh Dũng, Q. Dương Kinh, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201631929</t>
@@ -6556,10 +6556,10 @@
     <t>SXHAICHAU</t>
   </si>
   <si>
-    <t>C«ng ty TNHH S¶n XuÊt H¶i Ch©u</t>
-  </si>
-  <si>
-    <t>Khu phè 3 §«ng, ThÞ TrÊn Yªn L¹c, HuyÖn Yªn L¹c, TØnh VÜnh Phóc</t>
+    <t>Công ty TNHH Sản Xuất Hải Châu</t>
+  </si>
+  <si>
+    <t>Khu phố 3 Đông, Thị Trấn Yên Lạc, Huyện Yên Lạc, Tỉnh Vĩnh Phúc</t>
   </si>
   <si>
     <t>2500259702</t>
@@ -6586,19 +6586,19 @@
     <t>T LOC</t>
   </si>
   <si>
-    <t>C«ng ty CP TM vËn t¶i biÓn Tr­êng Léc</t>
-  </si>
-  <si>
-    <t>Khu  2 - Diªm §iÒn - Th¸i Thuþ - Th¸i B×nh</t>
+    <t>Công ty CP TM vận tải biển Trường Lộc</t>
+  </si>
+  <si>
+    <t>Khu  2 - Diêm Điền - Thái Thuỵ - Thái Bình</t>
   </si>
   <si>
     <t>T.HUYEN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Thanh HuyÒn</t>
-  </si>
-  <si>
-    <t>208 NguyÔn L­¬ng B»ng - §µ N½ng</t>
+    <t>Công ty TNHH Thanh Huyền</t>
+  </si>
+  <si>
+    <t>208 Nguyễn Lương Bằng - Đà Nẵng</t>
   </si>
   <si>
     <t>0400445229</t>
@@ -6628,10 +6628,10 @@
     <t>TAMBAC</t>
   </si>
   <si>
-    <t>Hîp T¸c X· VËn t¶i Thuû Tam B¹c</t>
-  </si>
-  <si>
-    <t>12 C Lý Tù Träng - Ph­êng Minh Khai - QuËn Hång bµng - TP. H¶i Phßng</t>
+    <t>Hợp Tác Xã Vận tải Thuỷ Tam Bạc</t>
+  </si>
+  <si>
+    <t>12 C Lý Tự Trọng - Phường Minh Khai - Quận Hồng bàng - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200144256</t>
@@ -6640,10 +6640,10 @@
     <t>TAMLONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i vµ tiÕp vËn Tam Long</t>
-  </si>
-  <si>
-    <t>TÇng 2, Tßa nhµ BiÓn §«ng, Sè 150 Chïa VÏ, §«ng h¶i 1, H¶i An, H¶i Phßng</t>
+    <t>Công ty cổ phần vận tải và tiếp vận Tam Long</t>
+  </si>
+  <si>
+    <t>Tầng 2, Tòa nhà Biển Đông, Số 150 Chùa Vẽ, Đông hải 1, Hải An, Hải Phòng</t>
   </si>
   <si>
     <t>0201648305</t>
@@ -6652,10 +6652,10 @@
     <t>TAMNGUYEN</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i vµ ®Çu t­ x©y dùng Tam Nguyªn</t>
-  </si>
-  <si>
-    <t>Sè 10 ng¸ch 11 ngâ 79 TrÇn Cung, Ph­êng NghÜa T©n, QuËn CÇu GiÊy, TP Hµ Néi</t>
+    <t>Công ty cổ phần thương mại và đầu tư xây dựng Tam Nguyên</t>
+  </si>
+  <si>
+    <t>Số 10 ngách 11 ngõ 79 Trần Cung, Phường Nghĩa Tân, Quận Cầu Giấy, TP Hà Nội</t>
   </si>
   <si>
     <t>0104643051</t>
@@ -6664,10 +6664,10 @@
     <t>TAMTHAO</t>
   </si>
   <si>
-    <t>Cty TNHH S¶n XuÊt vµ Th­¬ng m¹i T¸m Thao</t>
-  </si>
-  <si>
-    <t>2/1 Quèc Lé 1APhuwowng HiÖp B×nh Ph­íc, QuËn Thñ §øc, TP. Hå ChÝ Minh</t>
+    <t>Cty TNHH Sản Xuất và Thương mại Tám Thao</t>
+  </si>
+  <si>
+    <t>2/1 Quốc Lộ 1APhuwowng Hiệp Bình Phước, Quận Thủ Đức, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0304682876</t>
@@ -6676,10 +6676,10 @@
     <t>TAN PHU</t>
   </si>
   <si>
-    <t>DNTN vËt liÖu x©y dùng TÊn Phó</t>
-  </si>
-  <si>
-    <t>99/29, Ph¹m §¨ng Gi¶ng, B×nh H­ng Hµ, B×nh T©n, HCM</t>
+    <t>DNTN vật liệu xây dựng Tấn Phú</t>
+  </si>
+  <si>
+    <t>99/29, Phạm Đăng Giảng, Bình Hưng Hà, Bình Tân, HCM</t>
   </si>
   <si>
     <t>0305247393</t>
@@ -6688,10 +6688,10 @@
     <t>TANBINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH T©n B×nh</t>
-  </si>
-  <si>
-    <t>Sè 56 NguyÔn V¨n Linh, Ph­êng Lª Ch©n, TP H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Tân Bình</t>
+  </si>
+  <si>
+    <t>Số 56 Nguyễn Văn Linh, Phường Lê Chân, TP Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0200288642</t>
@@ -6700,10 +6700,10 @@
     <t>TANCUONG</t>
   </si>
   <si>
-    <t>C«ng ty CP TM T©n C­êng</t>
-  </si>
-  <si>
-    <t>Sè 1B tæ 58 Thµnh C«ng, Ba §×nh,HN</t>
+    <t>Công ty CP TM Tân Cường</t>
+  </si>
+  <si>
+    <t>Số 1B tổ 58 Thành Công, Ba Đình,HN</t>
   </si>
   <si>
     <t>0102381026</t>
@@ -6712,10 +6712,10 @@
     <t>TANHA</t>
   </si>
   <si>
-    <t>Cty TNHH T©n Hµ</t>
-  </si>
-  <si>
-    <t>33 D C¸t Linh, §èng §a,HN</t>
+    <t>Cty TNHH Tân Hà</t>
+  </si>
+  <si>
+    <t>33 D Cát Linh, Đống Đa,HN</t>
   </si>
   <si>
     <t>0100366946</t>
@@ -6724,16 +6724,16 @@
     <t>TANHIEP</t>
   </si>
   <si>
-    <t>C«ng ty nguyªn liÖu giÊy T©n HiÖp</t>
+    <t>Công ty nguyên liệu giấy Tân Hiệp</t>
   </si>
   <si>
     <t>TANTHANH</t>
   </si>
   <si>
-    <t>Cty TM &amp; DV T©n Thµnh</t>
-  </si>
-  <si>
-    <t>785 Ng« Gia Tù, Long Biªn, HN</t>
+    <t>Cty TM &amp; DV Tân Thành</t>
+  </si>
+  <si>
+    <t>785 Ngô Gia Tự, Long Biên, HN</t>
   </si>
   <si>
     <t>0101086067</t>
@@ -6742,10 +6742,10 @@
     <t>TANVIETPHAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Ph¸t TriÓn §Çu T­ Th­¬ng M¹i T©n ViÖt Ph¸t</t>
-  </si>
-  <si>
-    <t>Sè 10 B226 tæ 3, Ph­êng Thµnh T«, QuËn H¶i An, TP. H¶i Phßng</t>
+    <t>Công ty TNHH Phát Triển Đầu Tư Thương Mại Tân Việt Phát</t>
+  </si>
+  <si>
+    <t>Số 10 B226 tổ 3, Phường Thành Tô, Quận Hải An, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201782082</t>
@@ -6754,10 +6754,10 @@
     <t>TATUCO</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn x©y dùng vµ ®Çu t­ th­¬ng m¹i TATUCO</t>
-  </si>
-  <si>
-    <t>Sè 27, ng¸ch 8, ngâ Gèc §Ò, phè Minh Khai, QuËn Hai Bµ Tr­ng, TP. Hµ Néi</t>
+    <t>Công ty cổ phần xây dựng và đầu tư thương mại TATUCO</t>
+  </si>
+  <si>
+    <t>Số 27, ngách 8, ngõ Gốc Đề, phố Minh Khai, Quận Hai Bà Trưng, TP. Hà Nội</t>
   </si>
   <si>
     <t>0106065769</t>
@@ -6766,10 +6766,10 @@
     <t>TAUBIENSAIGON</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i &amp; §¹i Lý Tµu BiÓn Sµi Gßn</t>
-  </si>
-  <si>
-    <t>Toµ nhµ The Treor, Sè 39-39B BÕn V©n §ån, Ph­êng Xãm ChiÕu, Thµnh Phè Hå ChÝ Minh</t>
+    <t>Công ty TNHH Vận Tải &amp; Đại Lý Tàu Biển Sài Gòn</t>
+  </si>
+  <si>
+    <t>Toà nhà The Treor, Số 39-39B Bến Vân Đồn, Phường Xóm Chiếu, Thành Phố Hồ Chí Minh</t>
   </si>
   <si>
     <t>0319379174</t>
@@ -6784,10 +6784,10 @@
     <t>TAUTHUYDONGBAC</t>
   </si>
   <si>
-    <t>C«ng Ty Cæ PhÇn C«ng NghiÖp Tµu Thñy §«ng B¾c</t>
-  </si>
-  <si>
-    <t>C¶ng Km6, Phuwowgnf Quang Hanh, Thµnh Phè CÈm Ph¶, TØnh Qu¶ng Ninh</t>
+    <t>Công Ty Cổ Phần Công Nghiệp Tàu Thủy Đông Bắc</t>
+  </si>
+  <si>
+    <t>Cảng Km6, Phuwowgnf Quang Hanh, Thành Phố Cẩm Phả, Tỉnh Quảng Ninh</t>
   </si>
   <si>
     <t>5700780594</t>
@@ -6796,10 +6796,10 @@
     <t>TAYNINH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn BUORBON T©y Ninh</t>
-  </si>
-  <si>
-    <t>X· T©n H­ng, HuyÖn T©n Ch©u, TØnh T©y Ninh</t>
+    <t>Công ty cổ phần BUORBON Tây Ninh</t>
+  </si>
+  <si>
+    <t>Xã Tân Hưng, Huyện Tân Châu, Tỉnh Tây Ninh</t>
   </si>
   <si>
     <t>3900244389</t>
@@ -6808,10 +6808,10 @@
     <t>TBCL</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §¹i Lý Tµu BiÓn Ch©u Lôc</t>
-  </si>
-  <si>
-    <t>LÇu 19 - Tßa Nhµ Ree Tower - Sè 9 §oµn V¨n B¬ - P.12 - Q.4 - TP. HCM</t>
+    <t>Công ty TNHH Đại Lý Tàu Biển Châu Lục</t>
+  </si>
+  <si>
+    <t>Lầu 19 - Tòa Nhà Ree Tower - Số 9 Đoàn Văn Bơ - P.12 - Q.4 - TP. HCM</t>
   </si>
   <si>
     <t>0302597086</t>
@@ -6820,10 +6820,10 @@
     <t>TBDUONG</t>
   </si>
   <si>
-    <t>C«ng ty CP Gi¶i ph¸p tiÕp vËn ch©u ¸ Th¸i B×nh D­¬ng</t>
-  </si>
-  <si>
-    <t>Sè 763 Lª Th¸nh T«ng - P. B¹ch §»ng - TP. H¹ Long - TØnh Qu¶ng Ninh</t>
+    <t>Công ty CP Giải pháp tiếp vận châu á Thái Bình Dương</t>
+  </si>
+  <si>
+    <t>Số 763 Lê Thánh Tông - P. Bạch Đằng - TP. Hạ Long - Tỉnh Quảng Ninh</t>
   </si>
   <si>
     <t>5701541140</t>
@@ -6832,10 +6832,10 @@
     <t>TBINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH ThÐp Thanh B×nh</t>
-  </si>
-  <si>
-    <t>109-53 §øc Giang, Long Biªn, Hµ Néi</t>
+    <t>Công ty TNHH Thép Thanh Bình</t>
+  </si>
+  <si>
+    <t>109-53 Đức Giang, Long Biên, Hà Nội</t>
   </si>
   <si>
     <t>0100595569</t>
@@ -6844,10 +6844,10 @@
     <t>TBPT</t>
   </si>
   <si>
-    <t>C«ng ty CP thiÕt bÞ phô tïng</t>
-  </si>
-  <si>
-    <t>444 Hoµng Hoa Th¸m, Hµ Néi</t>
+    <t>Công ty CP thiết bị phụ tùng</t>
+  </si>
+  <si>
+    <t>444 Hoàng Hoa Thám, Hà Nội</t>
   </si>
   <si>
     <t>0101401537</t>
@@ -6856,10 +6856,10 @@
     <t>TBYTHAIPHONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn thiÕt bÞ y tÕ H¶i Phßng</t>
-  </si>
-  <si>
-    <t>33 Kú §ång - P. Quang Trung - Q. Hång bµng - TP. H¶i Phßng</t>
+    <t>Công ty cổ phần thiết bị y tế Hải Phòng</t>
+  </si>
+  <si>
+    <t>33 Kỳ Đồng - P. Quang Trung - Q. Hồng bàng - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200574629</t>
@@ -6868,10 +6868,10 @@
     <t>TCMN</t>
   </si>
   <si>
-    <t>Cty CP XNK thñ c«ng mü nghÖ</t>
-  </si>
-  <si>
-    <t>31-33 Ng« QuyÒn, Hµ N«i</t>
+    <t>Cty CP XNK thủ công mỹ nghệ</t>
+  </si>
+  <si>
+    <t>31-33 Ngô Quyền, Hà Nôi</t>
   </si>
   <si>
     <t>0100107356</t>
@@ -6880,10 +6880,10 @@
     <t>TCONG</t>
   </si>
   <si>
-    <t>Cty TNHH c¬ khÝ Thµnh C«ng</t>
-  </si>
-  <si>
-    <t>C«ng nghiÖp I, Nguyªn Khª, §«ng Anh, HN</t>
+    <t>Cty TNHH cơ khí Thành Công</t>
+  </si>
+  <si>
+    <t>Công nghiệp I, Nguyên Khê, Đông Anh, HN</t>
   </si>
   <si>
     <t>0100831174</t>
@@ -6892,10 +6892,10 @@
     <t>TDNANG</t>
   </si>
   <si>
-    <t>C«ng ty CP ThÐp §µ N½ng</t>
-  </si>
-  <si>
-    <t>KCN Liªn ChiÓu - Q.Liªn ChiÓu - TP §µ N½ng</t>
+    <t>Công ty CP Thép Đà Nẵng</t>
+  </si>
+  <si>
+    <t>KCN Liên Chiểu - Q.Liên Chiểu - TP Đà Nẵng</t>
   </si>
   <si>
     <t>0400101549</t>
@@ -6904,10 +6904,10 @@
     <t>TDT</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn TDT</t>
-  </si>
-  <si>
-    <t>54/9 L­¬ng §×nh Cña - Kim Liªn - §èng §a - HN</t>
+    <t>Công ty Cổ Phần TDT</t>
+  </si>
+  <si>
+    <t>54/9 Lương Đình Của - Kim Liên - Đống Đa - HN</t>
   </si>
   <si>
     <t>0101889120</t>
@@ -6916,10 +6916,10 @@
     <t>TDUNG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Thµnh Dòng</t>
-  </si>
-  <si>
-    <t>Th«n Ng­ Uyªn - X· Long Xuyªn - Kinh M«n - H¶i D­¬ng</t>
+    <t>Công ty TNHH Thành Dũng</t>
+  </si>
+  <si>
+    <t>Thôn Ngư Uyên - Xã Long Xuyên - Kinh Môn - Hải Dương</t>
   </si>
   <si>
     <t>0800288901</t>
@@ -6928,10 +6928,10 @@
     <t>THAIBINHDUONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH MTV VËn T¶i Hµng AHir Th¸i B×nh D­¬ng</t>
-  </si>
-  <si>
-    <t>6 Lª Th¸nh T«n, Ph­êng Sµi Gßn, TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH MTV Vận Tải Hàng AHir Thái Bình Dương</t>
+  </si>
+  <si>
+    <t>6 Lê Thánh Tôn, Phường Sài Gòn, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0310490604</t>
@@ -6940,10 +6940,10 @@
     <t>THAIHA</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i vµ vËn t¶i Th¸i Hµ</t>
-  </si>
-  <si>
-    <t>ThÞ TrÊn Minh T©n - HuyÖn Kinh M«n - TØnh H¶i D­¬ng</t>
+    <t>Công ty cổ phần thương mại và vận tải Thái Hà</t>
+  </si>
+  <si>
+    <t>Thị Trấn Minh Tân - Huyện Kinh Môn - Tỉnh Hải Dương</t>
   </si>
   <si>
     <t>0800282138</t>
@@ -6961,10 +6961,10 @@
     <t>THANGLOG</t>
   </si>
   <si>
-    <t>C«ng Ty VËn T¶i BiÓn Th¨ng Long</t>
-  </si>
-  <si>
-    <t>338 L¹ch Tray - H¶i Phßng - VN</t>
+    <t>Công Ty Vận Tải Biển Thăng Long</t>
+  </si>
+  <si>
+    <t>338 Lạch Tray - Hải Phòng - VN</t>
   </si>
   <si>
     <t>0200123506-004</t>
@@ -6973,10 +6973,10 @@
     <t>THANGLOI</t>
   </si>
   <si>
-    <t>Cty TNHH Th­¬ng M¹i DÞch Vô Th¾ng Lîi</t>
-  </si>
-  <si>
-    <t>4/6 §o¹n X¸ - V¹n Mü - Ng« QuyÒn - H¶i Phßng</t>
+    <t>Cty TNHH Thương Mại Dịch Vụ Thắng Lợi</t>
+  </si>
+  <si>
+    <t>4/6 Đoạn Xá - Vạn Mỹ - Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0200638463</t>
@@ -6985,10 +6985,10 @@
     <t>THANHDAT</t>
   </si>
   <si>
-    <t>Cty TNHH ¤ T« Thµnh §¹t</t>
-  </si>
-  <si>
-    <t>TÇng 1, 78H Hai Bµ Tr­ng - Tiªn Du - B¾c Ninh</t>
+    <t>Cty TNHH Ô Tô Thành Đạt</t>
+  </si>
+  <si>
+    <t>Tầng 1, 78H Hai Bà Trưng - Tiên Du - Bắc Ninh</t>
   </si>
   <si>
     <t>2300345538</t>
@@ -6997,10 +6997,10 @@
     <t>THANHDONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i biÓn Thµnh §«ng</t>
-  </si>
-  <si>
-    <t>Sè 16 l« 9 §­êng ThÕ L÷, P. Hång Bµng, TP. h¶i Phßng</t>
+    <t>Công ty cổ phần vận tải biển Thành Đông</t>
+  </si>
+  <si>
+    <t>Số 16 lô 9 Đường Thế Lữ, P. Hồng Bàng, TP. hải Phòng</t>
   </si>
   <si>
     <t>0202244915</t>
@@ -7009,10 +7009,10 @@
     <t>THANHLAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TM Thanh L©m</t>
-  </si>
-  <si>
-    <t>Côm d©n c­ An Trang - An §ång - An D­¬ng - H¶i Phßng</t>
+    <t>Công ty TNHH TM Thanh Lâm</t>
+  </si>
+  <si>
+    <t>Cụm dân cư An Trang - An Đồng - An Dương - Hải Phòng</t>
   </si>
   <si>
     <t>0200875714</t>
@@ -7021,10 +7021,10 @@
     <t>THANHMY</t>
   </si>
   <si>
-    <t>C«ng ty CP T©n Thµnh Mü</t>
-  </si>
-  <si>
-    <t>KCN phó Mü I - T©n Thµnh - TØnh Bµ RÞa - Vòng Tµu</t>
+    <t>Công ty CP Tân Thành Mỹ</t>
+  </si>
+  <si>
+    <t>KCN phú Mỹ I - Tân Thành - Tỉnh Bà Rịa - Vũng Tàu</t>
   </si>
   <si>
     <t>3500757072</t>
@@ -7033,10 +7033,10 @@
     <t>THANHNAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i An Thµnh Nam</t>
-  </si>
-  <si>
-    <t>Th«n 5 Yªn §Þnh, X· H¶i HËu, TØnh Ninh B×nh, ViÖt Nam</t>
+    <t>Công ty TNHH Vận Tải An Thành Nam</t>
+  </si>
+  <si>
+    <t>Thôn 5 Yên Định, Xã Hải Hậu, Tỉnh Ninh Bình, Việt Nam</t>
   </si>
   <si>
     <t>0601075842</t>
@@ -7045,10 +7045,10 @@
     <t>THANHPHAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i - S¶n XuÊt Minh Th¹nh Ph¸t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Êp T©n Minh, X· Minh Th¹nh, HuyÖn DÇu TiÒng, TØnh B×nh D­¬ng, ViÖt Nam</t>
+    <t>Công ty TNHH Thương Mại - Sản Xuất Minh Thạnh Phát</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ấp Tân Minh, Xã Minh Thạnh, Huyện Dầu Tiềng, Tỉnh Bình Dương, Việt Nam</t>
   </si>
   <si>
     <t>3702490047</t>
@@ -7057,10 +7057,10 @@
     <t>THANHPHONG</t>
   </si>
   <si>
-    <t>Hé kinh doanh c¬ së v«i Thanh Phong</t>
-  </si>
-  <si>
-    <t>Sè 36, quèc lé 22B, khu phè Tr­êng ¢n, ph­êng Long Hoa, TØnh T©y Ninh, VN</t>
+    <t>Hộ kinh doanh cơ sở vôi Thanh Phong</t>
+  </si>
+  <si>
+    <t>Số 36, quốc lộ 22B, khu phố Trường Ân, phường Long Hoa, Tỉnh Tây Ninh, VN</t>
   </si>
   <si>
     <t>072071001561</t>
@@ -7069,10 +7069,10 @@
     <t>THANHTRUNG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Kinh Doanh Vµ VËn T¶i Thµnh Trung</t>
-  </si>
-  <si>
-    <t>Sè 20/588 Thiªn L«i, Ph­êng VÜnh NiÖm, QuËn Lª Ch©n, Thµnh Phè H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Kinh Doanh Và Vận Tải Thành Trung</t>
+  </si>
+  <si>
+    <t>Số 20/588 Thiên Lôi, Phường Vĩnh Niệm, Quận Lê Chân, Thành Phố Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0201877538</t>
@@ -7081,10 +7081,10 @@
     <t>THC</t>
   </si>
   <si>
-    <t>Cty CP TM T©n Hoµng CÇu</t>
-  </si>
-  <si>
-    <t>Sè 6, NhuÖ Giang, Hµ §«ng, Hµ Néi</t>
+    <t>Cty CP TM Tân Hoàng Cầu</t>
+  </si>
+  <si>
+    <t>Số 6, Nhuệ Giang, Hà Đông, Hà Nội</t>
   </si>
   <si>
     <t>0500571682</t>
@@ -7102,10 +7102,10 @@
     <t>THIEN Y</t>
   </si>
   <si>
-    <t>C«ng ty TNHH DÞch Vô VËn T¶i Hµng H¶i Thiªn ý</t>
-  </si>
-  <si>
-    <t>28 §Æng Thai Mai, Ph­êng 7, QuËn Phó NhuËn, TP.HCM</t>
+    <t>Công ty TNHH Dịch Vụ Vận Tải Hàng Hải Thiên ý</t>
+  </si>
+  <si>
+    <t>28 Đặng Thai Mai, Phường 7, Quận Phú Nhuận, TP.HCM</t>
   </si>
   <si>
     <t>0301458812</t>
@@ -7114,10 +7114,10 @@
     <t>THIENDUC</t>
   </si>
   <si>
-    <t>Cty TNHH XNK sao Thiªn §­c</t>
-  </si>
-  <si>
-    <t>Sè 40 - Ngâ 115 - §µo TÊn - Ba §×nh - HN</t>
+    <t>Cty TNHH XNK sao Thiên Đưc</t>
+  </si>
+  <si>
+    <t>Số 40 - Ngõ 115 - Đào Tấn - Ba Đình - HN</t>
   </si>
   <si>
     <t>0103339147</t>
@@ -7126,10 +7126,10 @@
     <t>THIENLONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i ®Çu t­ ThiÖn Long</t>
-  </si>
-  <si>
-    <t>286/3 NguyÔn V¨n C«ng, Ph­êng 3, QuËn Gß VÊp, TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH Thương Mại đầu tư Thiện Long</t>
+  </si>
+  <si>
+    <t>286/3 Nguyễn Văn Công, Phường 3, Quận Gò Vấp, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0311455578</t>
@@ -7138,10 +7138,10 @@
     <t>THIENLUONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn Th­¬ng M¹i Vµ VËt LiÖu X©y Dùng Thiªn L­¬ng</t>
-  </si>
-  <si>
-    <t>Khu CN Nam §×nh Vò, Ph­êng §«ng H¶i 2, QuËn H¶i An, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần Thương Mại Và Vật Liệu Xây Dựng Thiên Lương</t>
+  </si>
+  <si>
+    <t>Khu CN Nam Đình Vũ, Phường Đông Hải 2, Quận Hải An, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201159174</t>
@@ -7150,10 +7150,10 @@
     <t>THLONG</t>
   </si>
   <si>
-    <t>Cty VËn T¶i BiÓn Th¨ng Long</t>
-  </si>
-  <si>
-    <t>338 L¹ch Tray - Ng« QuyÒn - H¶i Phßng</t>
+    <t>Cty Vận Tải Biển Thăng Long</t>
+  </si>
+  <si>
+    <t>338 Lạch Tray - Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0200123506</t>
@@ -7162,10 +7162,10 @@
     <t>THOIDAIMOI</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i biÓn vµ th­¬ng m¹i thêi ®¹i míi</t>
-  </si>
-  <si>
-    <t>69 ®­êng 27, khu phã 2, Ph­êng T©n Phong, QuËn 7, Thµnh phè Hå ChÝ Minh, ViÖt Nam</t>
+    <t>Công ty cổ phần vận tải biển và thương mại thời đại mới</t>
+  </si>
+  <si>
+    <t>69 đường 27, khu phó 2, Phường Tân Phong, Quận 7, Thành phố Hồ Chí Minh, Việt Nam</t>
   </si>
   <si>
     <t>0314137044</t>
@@ -7174,10 +7174,10 @@
     <t>THONGMINHTCL</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §iÖn Tö Th«ng Minh TCL ( ViÖt Nam)</t>
-  </si>
-  <si>
-    <t>Sè 26 Vship II-A, §­êng sè 32, Khu CN ViÖt Nam - Singapore II -A ph­êng VÜnh T©n, TP HCM, ViÖt Nam</t>
+    <t>Công ty TNHH Điện Tử Thông Minh TCL ( Việt Nam)</t>
+  </si>
+  <si>
+    <t>Số 26 Vship II-A, Đường số 32, Khu CN Việt Nam - Singapore II -A phường Vĩnh Tân, TP HCM, Việt Nam</t>
   </si>
   <si>
     <t>3702670794</t>
@@ -7186,19 +7186,19 @@
     <t>THPTLECHAN</t>
   </si>
   <si>
-    <t>Tr­êng THPT Lª Ch©n</t>
-  </si>
-  <si>
-    <t>Khu 5 - VÜnh NiÖm - Lª Ch©n - H¶i Phßng</t>
+    <t>Trường THPT Lê Chân</t>
+  </si>
+  <si>
+    <t>Khu 5 - Vĩnh Niệm - Lê Chân - Hải Phòng</t>
   </si>
   <si>
     <t>THU DUC</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn x©y l¾p c¬ ®iÖn Thñ §øc</t>
-  </si>
-  <si>
-    <t>Êp Phó Th¹nh - X· Müa Xu©n - HuyÖn T©n Thµnh - TØnh Bµ RÞa - Vòng Tµu</t>
+    <t>Công ty cổ phần xây lắp cơ điện Thủ Đức</t>
+  </si>
+  <si>
+    <t>ấp Phú Thạnh - Xã Mỹa Xuân - Huyện Tân Thành - Tỉnh Bà Rịa - Vũng Tàu</t>
   </si>
   <si>
     <t>3502088469</t>
@@ -7207,10 +7207,10 @@
     <t>THUANHAI</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dÞch vô vËn t¶i ThuËn H¶i</t>
-  </si>
-  <si>
-    <t>73 Huúnh Kh­¬ng An - Ph­êng 3 - TP. Vòng Tµu - TØnh bµ RÞa - Vòng Tµu</t>
+    <t>Công ty cổ phần dịch vụ vận tải Thuận Hải</t>
+  </si>
+  <si>
+    <t>73 Huỳnh Khương An - Phường 3 - TP. Vũng Tàu - Tỉnh bà Rịa - Vũng Tàu</t>
   </si>
   <si>
     <t>3502326522</t>
@@ -7219,19 +7219,19 @@
     <t>THUANPHAT</t>
   </si>
   <si>
-    <t>C«ng ty CP vµ th­¬ng m¹i ThuËn Ph¸t</t>
-  </si>
-  <si>
-    <t>ThÞ TrÊn C¸t Thµnh, Trùc Ninh, Nam §Þnh</t>
+    <t>Công ty CP và thương mại Thuận Phát</t>
+  </si>
+  <si>
+    <t>Thị Trấn Cát Thành, Trực Ninh, Nam Định</t>
   </si>
   <si>
     <t>THUANPHONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH T©n ThuËn Phong</t>
-  </si>
-  <si>
-    <t>Km sè 8 Quèc Lé 5 - X· Nam S¬n, HuyÖn An D­¬ng, H¶i Phßng</t>
+    <t>Công ty TNHH Tân Thuận Phong</t>
+  </si>
+  <si>
+    <t>Km số 8 Quốc Lộ 5 - Xã Nam Sơn, Huyện An Dương, Hải Phòng</t>
   </si>
   <si>
     <t>0200429212</t>
@@ -7240,10 +7240,10 @@
     <t>THUETAU BIENVN</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i vµ thuª tµu biÓn ViÖt Nam</t>
-  </si>
-  <si>
-    <t>428 NGuyÔn TÊt Thµnh - Ph­êng 18 - QuËn 4 - TP. HCM</t>
+    <t>Công ty cổ phần vận tải và thuê tàu biển Việt Nam</t>
+  </si>
+  <si>
+    <t>428 NGuyễn Tất Thành - Phường 18 - Quận 4 - TP. HCM</t>
   </si>
   <si>
     <t>0300448709</t>
@@ -7252,10 +7252,10 @@
     <t>THUONGMAI</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dÞch vô vËn t¶i vµ th­¬ng m¹i</t>
-  </si>
-  <si>
-    <t>Phßng 427-430 tßa nhµ Thµnh §¹t 1, sè 3 Lª Th¸nh T«ng, Ph­êng M¸y T¬, Ng« QuyÒn,HP</t>
+    <t>Công ty cổ phần dịch vụ vận tải và thương mại</t>
+  </si>
+  <si>
+    <t>Phòng 427-430 tòa nhà Thành Đạt 1, số 3 Lê Thánh Tông, Phường Máy Tơ, Ngô Quyền,HP</t>
   </si>
   <si>
     <t>0200387594</t>
@@ -7264,10 +7264,10 @@
     <t>THUONGMAINAMANH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn x©y dùng vµ dÞch vô th­¬ng m¹i Nam Anh</t>
-  </si>
-  <si>
-    <t>Sè 179 ®­êng Lª Hoµn, khèi Yªn Vinh, ph­êng H­ng Phóc, TP. Vinh, NghÖ An</t>
+    <t>Công ty cổ phần xây dựng và dịch vụ thương mại Nam Anh</t>
+  </si>
+  <si>
+    <t>Số 179 đường Lê Hoàn, khối Yên Vinh, phường Hưng Phúc, TP. Vinh, Nghệ An</t>
   </si>
   <si>
     <t>2901362312</t>
@@ -7276,10 +7276,10 @@
     <t>THUONGMAIVINACOMIN</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn du lÞch vµ th­¬ng m¹i - Vinacomin</t>
-  </si>
-  <si>
-    <t>TÇng 8, Tµ nhµ ViÖt ¸, Phè Duy T©n, Ph­êng DÞch Väng HËu, QuËn CÇu GiÊy, Hµ Néi</t>
+    <t>Công ty cổ phần du lịch và thương mại - Vinacomin</t>
+  </si>
+  <si>
+    <t>Tầng 8, Tà nhà Việt á, Phố Duy Tân, Phường Dịch Vọng Hậu, Quận Cầu Giấy, Hà Nội</t>
   </si>
   <si>
     <t>0100101298</t>
@@ -7288,10 +7288,10 @@
     <t>THUYENVIEN SCC</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Cung øng thuyÒn viªn SCC</t>
-  </si>
-  <si>
-    <t>36 NguyÔn ThÞ Minh Khai, Ph­êng §a Kao, QuËn 1, Thµnh Phè Hå ChÝ MInh, ViÖt Nam</t>
+    <t>Công ty TNHH Cung ứng thuyền viên SCC</t>
+  </si>
+  <si>
+    <t>36 Nguyễn Thị Minh Khai, Phường Đa Kao, Quận 1, Thành Phố Hồ Chí MInh, Việt Nam</t>
   </si>
   <si>
     <t>0315174176</t>
@@ -7300,10 +7300,10 @@
     <t>THUYSANHN</t>
   </si>
   <si>
-    <t>CN Cty CP XNK Thñy S¶n Hµ Néi - XN Giao nhËn thñy s¸n XK H¶i Phßng</t>
-  </si>
-  <si>
-    <t>Lª Lai - Ng« QuyÒn - h¶i Phßng</t>
+    <t>CN Cty CP XNK Thủy Sản Hà Nội - XN Giao nhận thủy sán XK Hải Phòng</t>
+  </si>
+  <si>
+    <t>Lê Lai - Ngô Quyền - hải Phòng</t>
   </si>
   <si>
     <t>0100102848002</t>
@@ -7318,10 +7318,10 @@
     <t>TICO</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn TICO ViÖt Nam</t>
-  </si>
-  <si>
-    <t>TÇng 6, sè 61 phè Ngôy Nh­ Kontum, Ph­êng Thanh Xu©n, TP. Hµ Néi, VN</t>
+    <t>Công ty cổ phần TICO Việt Nam</t>
+  </si>
+  <si>
+    <t>Tầng 6, số 61 phố Ngụy Như Kontum, Phường Thanh Xuân, TP. Hà Nội, VN</t>
   </si>
   <si>
     <t>0106303156</t>
@@ -7330,10 +7330,10 @@
     <t>TIENDAIPHAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i TiÕn §¹i Ph¸t</t>
-  </si>
-  <si>
-    <t>Sè 20/136 Bïi ThÞ Tõ Nhiªn, P. §©ong H¶i 1, QuËn H¶i An,TP. H¶i Phong</t>
+    <t>Công ty TNHH Vận Tải Tiến Đại Phát</t>
+  </si>
+  <si>
+    <t>Số 20/136 Bùi Thị Từ Nhiên, P. Đâong Hải 1, Quận Hải An,TP. Hải Phong</t>
   </si>
   <si>
     <t>0201734057</t>
@@ -7342,10 +7342,10 @@
     <t>TIENHUNG</t>
   </si>
   <si>
-    <t>Cty CP TM XNK TiÕn H­ng</t>
-  </si>
-  <si>
-    <t>Uy Nç, §«ng Anh, Hµ Néi</t>
+    <t>Cty CP TM XNK Tiến Hưng</t>
+  </si>
+  <si>
+    <t>Uy Nỗ, Đông Anh, Hà Nội</t>
   </si>
   <si>
     <t>0101570214</t>
@@ -7354,16 +7354,16 @@
     <t>TIENPHONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TiÕp vËn vµ TM Tien Phong</t>
+    <t>Công ty TNHH Tiếp vận và TM Tien Phong</t>
   </si>
   <si>
     <t>TIENTHANH</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn Gç NhËp KhÈu TiÕn Thµnh</t>
-  </si>
-  <si>
-    <t>Th«n 6 quèc lé 47, X· Qu¶ng Phó, Thµnh Phè Thanh Hãa, TØnh Thanh Hãa, ViÖt Nam</t>
+    <t>Công ty Cổ Phần Gỗ Nhập Khẩu Tiến Thành</t>
+  </si>
+  <si>
+    <t>Thôn 6 quốc lộ 47, Xã Quảng Phú, Thành Phố Thanh Hóa, Tỉnh Thanh Hóa, Việt Nam</t>
   </si>
   <si>
     <t>2802491187</t>
@@ -7372,10 +7372,10 @@
     <t>TIEPVAN T&amp;T</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TiÕp VËn T &amp; T</t>
-  </si>
-  <si>
-    <t>Sè 2/2B/417 §»ng h¶i, Ph­êng H¶i An, TP. H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Tiếp Vận T &amp; T</t>
+  </si>
+  <si>
+    <t>Số 2/2B/417 Đằng hải, Phường Hải An, TP. Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0202193259</t>
@@ -7384,10 +7384,10 @@
     <t>TKN</t>
   </si>
   <si>
-    <t>CN Long An - Cty CP G¹ch Khèi T©n Kû Nguyªn</t>
-  </si>
-  <si>
-    <t>X· L­¬ng B×nh - HuyÖn BÕn Løc - TØnh Long An</t>
+    <t>CN Long An - Cty CP Gạch Khối Tân Kỷ Nguyên</t>
+  </si>
+  <si>
+    <t>Xã Lương Bình - Huyện Bến Lức - Tỉnh Long An</t>
   </si>
   <si>
     <t>0305799651-001</t>
@@ -7396,10 +7396,10 @@
     <t>TLONG</t>
   </si>
   <si>
-    <t>Cty TNHH TM Th¨ng Long Hµ Néi</t>
-  </si>
-  <si>
-    <t>36 Mai H¾c §Õ, Hµ Néi</t>
+    <t>Cty TNHH TM Thăng Long Hà Nội</t>
+  </si>
+  <si>
+    <t>36 Mai Hắc Đế, Hà Nội</t>
   </si>
   <si>
     <t>0101352093</t>
@@ -7408,10 +7408,10 @@
     <t>TLVVIETNAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TLV ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 34/97 Mª Linh - P. An Biªn - Q. Lª Ch©n - TP. H¶i Phßng</t>
+    <t>Công ty TNHH TLV Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 34/97 Mê Linh - P. An Biên - Q. Lê Chân - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201720431</t>
@@ -7420,10 +7420,10 @@
     <t>TMEVERSTEP</t>
   </si>
   <si>
-    <t>C«ng ty TNHH ViÖt Nam LogicstÝc vµ th­¬ng m¹i Everstep</t>
-  </si>
-  <si>
-    <t>Sè 3 ®­êng Lª Th¸nh T«ng, ph­êng M¸y T¬, Q Ng« QuyÒn, TP H¶i Phßng VN</t>
+    <t>Công ty TNHH Việt Nam Logicstíc và thương mại Everstep</t>
+  </si>
+  <si>
+    <t>Số 3 đường Lê Thánh Tông, phường Máy Tơ, Q Ngô Quyền, TP Hải Phòng VN</t>
   </si>
   <si>
     <t>0202083880</t>
@@ -7432,10 +7432,10 @@
     <t>TMHA</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i Hoµng Anh</t>
-  </si>
-  <si>
-    <t>H¹ §o¹n 2 - §«ng H¶i - H¶i An -H¶i Phßng</t>
+    <t>Công ty cổ phần thương mại Hoàng Anh</t>
+  </si>
+  <si>
+    <t>Hạ Đoạn 2 - Đông Hải - Hải An -Hải Phòng</t>
   </si>
   <si>
     <t>0200585123</t>
@@ -7444,10 +7444,10 @@
     <t>TMHAIPHONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn thÐp vµ th­¬ng m¹i H¶i Phßng</t>
-  </si>
-  <si>
-    <t>Sè 1091 T«n §øc Th¾ng, Së DÇu, Hång Bµng, H¶i Phßng</t>
+    <t>Công ty cổ phần thép và thương mại Hải Phòng</t>
+  </si>
+  <si>
+    <t>Số 1091 Tôn Đức Thắng, Sở Dầu, Hồng Bàng, Hải Phòng</t>
   </si>
   <si>
     <t>0201813118</t>
@@ -7456,10 +7456,10 @@
     <t>TMHH</t>
   </si>
   <si>
-    <t>Cty CP Th­¬ng m¹i H­¬ng Hoµn</t>
-  </si>
-  <si>
-    <t>Sè 141 L¸n BÌ, Lª Ch©n, HP</t>
+    <t>Cty CP Thương mại Hương Hoàn</t>
+  </si>
+  <si>
+    <t>Số 141 Lán Bè, Lê Chân, HP</t>
   </si>
   <si>
     <t>0200739912</t>
@@ -7468,10 +7468,10 @@
     <t>TMNGOCANH</t>
   </si>
   <si>
-    <t>C«ng ty CP ThiÕt KÕ X©y Dùng Th­¬ng M¹i Ngäc Anh</t>
-  </si>
-  <si>
-    <t>Sè 10/19/267 Hµng Kªnh, P. Hµng Kªnh, Q. Lª Ch©n, TP. H¶i Phßng</t>
+    <t>Công ty CP Thiết Kế Xây Dựng Thương Mại Ngọc Anh</t>
+  </si>
+  <si>
+    <t>Số 10/19/267 Hàng Kênh, P. Hàng Kênh, Q. Lê Chân, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201747426</t>
@@ -7480,10 +7480,10 @@
     <t>TMPHUDAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i vµ Th­¬ng M¹i Phó §¹t</t>
-  </si>
-  <si>
-    <t>Th«n Phó An, ThÞ TrÊn C¸t Thµnh, HuyÖn Trùc Ninh, TØnh Nam §Þnh</t>
+    <t>Công ty TNHH Vận Tải và Thương Mại Phú Đạt</t>
+  </si>
+  <si>
+    <t>Thôn Phú An, Thị Trấn Cát Thành, Huyện Trực Ninh, Tỉnh Nam Định</t>
   </si>
   <si>
     <t>0600334653</t>
@@ -7492,25 +7492,25 @@
     <t>TMQUOCTE</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i vµ th­¬ng m¹i Quèc TÕ</t>
+    <t>Công ty cổ phần vận tải và thương mại Quốc Tế</t>
   </si>
   <si>
     <t>TMSNM</t>
   </si>
   <si>
-    <t>Cty TNHH Giao NhËn VT &amp; TM S.N.M</t>
-  </si>
-  <si>
-    <t>51 §­êng Bao TrÇn H­ng §¹o, H¶i Phßng</t>
+    <t>Cty TNHH Giao Nhận VT &amp; TM S.N.M</t>
+  </si>
+  <si>
+    <t>51 Đường Bao Trần Hưng Đạo, Hải Phòng</t>
   </si>
   <si>
     <t>TMVH</t>
   </si>
   <si>
-    <t>Cty CP TM ViÖt Hµn</t>
-  </si>
-  <si>
-    <t>Sè 19D36 §æng Quèc B×nh, Ng« QuyÒn, HP</t>
+    <t>Cty CP TM Việt Hàn</t>
+  </si>
+  <si>
+    <t>Số 19D36 Đổng Quốc Bình, Ngô Quyền, HP</t>
   </si>
   <si>
     <t>0200761555</t>
@@ -7519,10 +7519,10 @@
     <t>TMVIETDUC</t>
   </si>
   <si>
-    <t>Hîp t¸c x· xÝ nghiÖp th­¬ng m¹i ViÖt §øc</t>
-  </si>
-  <si>
-    <t>116 L¹ch Tray - Ng« QuyÒn - HP</t>
+    <t>Hợp tác xã xí nghiệp thương mại Việt Đức</t>
+  </si>
+  <si>
+    <t>116 Lạch Tray - Ngô Quyền - HP</t>
   </si>
   <si>
     <t>0200403743</t>
@@ -7531,10 +7531,10 @@
     <t>TMVINA</t>
   </si>
   <si>
-    <t>C«ng Ty CP Nh©n Lùc Vµ Th­¬ng M¹i Vinaconex</t>
-  </si>
-  <si>
-    <t>TÇng 1 - 17 T6 Trung Hoµ Nh©n ChÝnh - Thanh Xu©n - HN</t>
+    <t>Công Ty CP Nhân Lực Và Thương Mại Vinaconex</t>
+  </si>
+  <si>
+    <t>Tầng 1 - 17 T6 Trung Hoà Nhân Chính - Thanh Xuân - HN</t>
   </si>
   <si>
     <t>0102234864</t>
@@ -7543,10 +7543,10 @@
     <t>TNHAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH s¶n xuÊt v«i TMDV Thèng NhÊt</t>
-  </si>
-  <si>
-    <t>87/995 ®­êng Lª §øc Thä, P17, Q Gß VÊp, HCM</t>
+    <t>Công ty TNHH sản xuất vôi TMDV Thống Nhất</t>
+  </si>
+  <si>
+    <t>87/995 đường Lê Đức Thọ, P17, Q Gò Vấp, HCM</t>
   </si>
   <si>
     <t>0302217760</t>
@@ -7555,10 +7555,10 @@
     <t>TNHHHAINAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH H¶i Nam</t>
-  </si>
-  <si>
-    <t>Tæ 65 khu 5, ph­êng B¹ch §»ng, TP. H¹ Long, TØnh Qu¶ng Ninh</t>
+    <t>Công ty TNHH Hải Nam</t>
+  </si>
+  <si>
+    <t>Tổ 65 khu 5, phường Bạch Đằng, TP. Hạ Long, Tỉnh Quảng Ninh</t>
   </si>
   <si>
     <t>5700427766</t>
@@ -7567,10 +7567,10 @@
     <t>TNHHPHUONGNAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Ph­¬ng Nam</t>
-  </si>
-  <si>
-    <t>Xãm An Th¾ng  - X· An L­ - HuyÖn Thñy Nguyªn - TP,. H¶i Phßng</t>
+    <t>Công ty TNHH Phương Nam</t>
+  </si>
+  <si>
+    <t>Xóm An Thắng  - Xã An Lư - Huyện Thủy Nguyên - TP,. Hải Phòng</t>
   </si>
   <si>
     <t>0200157590</t>
@@ -7579,10 +7579,10 @@
     <t>TNHHTIENPHONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TiÕn Phong</t>
-  </si>
-  <si>
-    <t>Sè 314, Khu 6, TT Diªm §iÒm, Th¸i Thôy, Th¸i B×nh</t>
+    <t>Công ty TNHH Tiến Phong</t>
+  </si>
+  <si>
+    <t>Số 314, Khu 6, TT Diêm Điềm, Thái Thụy, Thái Bình</t>
   </si>
   <si>
     <t>1000504217</t>
@@ -7591,10 +7591,10 @@
     <t>TOANAN</t>
   </si>
   <si>
-    <t>Cty CP §Çu T­ Tßan An</t>
-  </si>
-  <si>
-    <t>Sè 12G NguyÔn Quang BÝch, P.13, Q.T©n B×nh, TP Hå ChÝ Minh</t>
+    <t>Cty CP Đầu Tư Tòan An</t>
+  </si>
+  <si>
+    <t>Số 12G Nguyễn Quang Bích, P.13, Q.Tân Bình, TP Hồ Chí Minh</t>
   </si>
   <si>
     <t>0304245844</t>
@@ -7603,10 +7603,10 @@
     <t>TOANTHANG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §Çu T­ Ngo¹i Th­¬ng Toµn Th¾ng</t>
-  </si>
-  <si>
-    <t>156/46C §­êng NguyÔn Thi ThËp, Khu phè 4A, Ph­êng B×nh ThuËn, QuËn 7, TPHCM, VN</t>
+    <t>Công ty TNHH Đầu Tư Ngoại Thương Toàn Thắng</t>
+  </si>
+  <si>
+    <t>156/46C Đường Nguyễn Thi Thập, Khu phố 4A, Phường Bình Thuận, Quận 7, TPHCM, VN</t>
   </si>
   <si>
     <t>0314638019</t>
@@ -7615,10 +7615,10 @@
     <t>TOCONTAP</t>
   </si>
   <si>
-    <t>C«ng ty CP xuÊt nhËp khÈu T¹p PhÈm (TOCOTAP)</t>
-  </si>
-  <si>
-    <t>36 Bµ TriÖu, Hµ Néi</t>
+    <t>Công ty CP xuất nhập khẩu Tạp Phẩm (TOCOTAP)</t>
+  </si>
+  <si>
+    <t>36 Bà Triệu, Hà Nội</t>
   </si>
   <si>
     <t>0100106747</t>
@@ -7627,10 +7627,10 @@
     <t>TONGHOP</t>
   </si>
   <si>
-    <t>CN Cty CP XNK Tæng hîp II t¹i HN</t>
-  </si>
-  <si>
-    <t>16 Ngâ HuÕ, Hai Bµ Tr­ng, HN</t>
+    <t>CN Cty CP XNK Tổng hợp II tại HN</t>
+  </si>
+  <si>
+    <t>16 Ngõ Huế, Hai Bà Trưng, HN</t>
   </si>
   <si>
     <t>0301184833009</t>
@@ -7663,10 +7663,10 @@
     <t>TPHONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TiÕp vËn va th­¬ng M¹i Tiªn Phong</t>
-  </si>
-  <si>
-    <t>12A l« 26D KDT míi Ng· 5 S©n Bay C¸t Bi, P. §«ng Khª - Ng« QuyÒn - HP</t>
+    <t>Công ty TNHH Tiếp vận va thương Mại Tiên Phong</t>
+  </si>
+  <si>
+    <t>12A lô 26D KDT mới Ngã 5 Sân Bay Cát Bi, P. Đông Khê - Ngô Quyền - HP</t>
   </si>
   <si>
     <t>0201299453</t>
@@ -7675,10 +7675,10 @@
     <t>TQUANG</t>
   </si>
   <si>
-    <t>Cty TNHH SX &amp; KD XNK Tuyªn Quang</t>
-  </si>
-  <si>
-    <t>Khèi 2C, thÞ trÊn §«ng Anh, HN</t>
+    <t>Cty TNHH SX &amp; KD XNK Tuyên Quang</t>
+  </si>
+  <si>
+    <t>Khối 2C, thị trấn Đông Anh, HN</t>
   </si>
   <si>
     <t>0101376619</t>
@@ -7687,10 +7687,10 @@
     <t>TRACO</t>
   </si>
   <si>
-    <t>C«ng ty Cæ phÇn vËn t¶i 1 Traco</t>
-  </si>
-  <si>
-    <t>Sè 271 Lª Th¸nh T«ng, P M¸y Chai, Q Ng« QuyÒn, H¶i Phßng</t>
+    <t>Công ty Cổ phần vận tải 1 Traco</t>
+  </si>
+  <si>
+    <t>Số 271 Lê Thánh Tông, P Máy Chai, Q Ngô Quyền, Hải Phòng</t>
   </si>
   <si>
     <t>0200380768</t>
@@ -7723,10 +7723,10 @@
     <t>TRANQUY GROUP</t>
   </si>
   <si>
-    <t>C«ng ty TNHH X©y Dùng TrÇn Quý Group</t>
-  </si>
-  <si>
-    <t>Sè 16, §­êng TriÖu Phóc LÞch, tæ 7, Ph­êng T©n Hßa, TP Hßa B×nh,t. Hßa B×nh, VN</t>
+    <t>Công ty TNHH Xây Dựng Trần Quý Group</t>
+  </si>
+  <si>
+    <t>Số 16, Đường Triệu Phúc Lịch, tổ 7, Phường Tân Hòa, TP Hòa Bình,t. Hòa Bình, VN</t>
   </si>
   <si>
     <t>5400538306</t>
@@ -7744,10 +7744,10 @@
     <t>TREE MARINE</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TREE MARINE</t>
-  </si>
-  <si>
-    <t>LÇu 17 tßa nhµ Petroland, 12 T©n Trµo, Ph­êng T©n Phó, QuËn 7, TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH TREE MARINE</t>
+  </si>
+  <si>
+    <t>Lầu 17 tòa nhà Petroland, 12 Tân Trào, Phường Tân Phú, Quận 7, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0315496670</t>
@@ -7756,10 +7756,10 @@
     <t>TRICONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TrÝ C«ng</t>
-  </si>
-  <si>
-    <t>P229, tÇng 2, kh¸ch s¹n DÇu khÝ - 442 §µ N½ng - §«ng H¶i - HP</t>
+    <t>Công ty TNHH Trí Công</t>
+  </si>
+  <si>
+    <t>P229, tầng 2, khách sạn Dầu khí - 442 Đà Nẵng - Đông Hải - HP</t>
   </si>
   <si>
     <t>5700592382</t>
@@ -7777,10 +7777,10 @@
     <t>TRIHIEU</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn th­¬ng m¹i vµ dÞch vô tæng hîp An TrÝ HiÕu</t>
-  </si>
-  <si>
-    <t>Sè 1 NguyÔn Th­îng HiÒn - Ph­êng NguyÔn DU - QuËn hai Bµ Tr­ng - HN</t>
+    <t>Công ty cổ phần thương mại và dịch vụ tổng hợp An Trí Hiếu</t>
+  </si>
+  <si>
+    <t>Số 1 Nguyễn Thượng Hiền - Phường Nguyễn DU - Quận hai Bà Trưng - HN</t>
   </si>
   <si>
     <t>0106549833</t>
@@ -7798,10 +7798,10 @@
     <t>TRLOC</t>
   </si>
   <si>
-    <t>C«ng ty CP TM VTB Tr­êng Léc</t>
-  </si>
-  <si>
-    <t>Khu 2 - Diªm §iÒm - Th¸i Thuþ - Th¸i B×nh</t>
+    <t>Công ty CP TM VTB Trường Lộc</t>
+  </si>
+  <si>
+    <t>Khu 2 - Diêm Điềm - Thái Thuỵ - Thái Bình</t>
   </si>
   <si>
     <t>1000418060</t>
@@ -7813,10 +7813,10 @@
     <t>TRUONGAN</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ®Çu t­ vµ ph¸t triÓn vËn t¶i Tr­êng An</t>
-  </si>
-  <si>
-    <t>Tæ d©n phè Th¾ng Lîi, ph­êng Hoµ B×nh, Thµnh Phè H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty cổ phần đầu tư và phát triển vận tải Trường An</t>
+  </si>
+  <si>
+    <t>Tổ dân phố Thắng Lợi, phường Hoà Bình, Thành Phố Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0202034185</t>
@@ -7825,10 +7825,10 @@
     <t>TRUONGMINH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn quèc tÕ Tr­êng Minh</t>
-  </si>
-  <si>
-    <t>Phßng 906, th¸p B - TP Plaza - L« 20A Lª Hång Phong - P. §«ng Khª NQ</t>
+    <t>Công ty cổ phần quốc tế Trường Minh</t>
+  </si>
+  <si>
+    <t>Phòng 906, tháp B - TP Plaza - Lô 20A Lê Hồng Phong - P. Đông Khê NQ</t>
   </si>
   <si>
     <t>0201173059</t>
@@ -7837,10 +7837,10 @@
     <t>TRUONGNGUYEN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i Kinh Doanh XuÊt NhËp KhÈu Tr­êng Nguyªn</t>
-  </si>
-  <si>
-    <t>57 B¹ch §»ng, tæ d©n phè Bach §»ng 1, ph­êng Thñy Nguyªn, TP H¶i Phßng, VN</t>
+    <t>Công ty TNHH Vận Tải Kinh Doanh Xuất Nhập Khẩu Trường Nguyên</t>
+  </si>
+  <si>
+    <t>57 Bạch Đằng, tổ dân phố Bach Đằng 1, phường Thủy Nguyên, TP Hải Phòng, VN</t>
   </si>
   <si>
     <t>0200826749</t>
@@ -7849,10 +7849,10 @@
     <t>TRUONGPHAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i Kho¸ng S¶n T©n Tr­êng Ph¸t</t>
-  </si>
-  <si>
-    <t>LÇu 12B - 196 Hoµng DiÖu - Ph­êng 8 - QuËn 4 - TP. Hå ChÝh</t>
+    <t>Công ty TNHH Thương Mại Khoáng Sản Tân Trường Phát</t>
+  </si>
+  <si>
+    <t>Lầu 12B - 196 Hoàng Diệu - Phường 8 - Quận 4 - TP. Hồ Chíh</t>
   </si>
   <si>
     <t>0311979941</t>
@@ -7861,10 +7861,10 @@
     <t>TSBAN</t>
   </si>
   <si>
-    <t>Cty CP Thuû S¶n B×nh An</t>
-  </si>
-  <si>
-    <t>L« 217 KCN Trµ Nãc II, TP CÇn Th¬</t>
+    <t>Cty CP Thuỷ Sản Bình An</t>
+  </si>
+  <si>
+    <t>Lô 217 KCN Trà Nóc II, TP Cần Thơ</t>
   </si>
   <si>
     <t>1800604806</t>
@@ -7873,10 +7873,10 @@
     <t>TSHANOI</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TuyÕn Container TS Hµ Néi</t>
-  </si>
-  <si>
-    <t>11 Vâ ThÞ S¸u, M¸y T¬, Ng« QuyÒn, h¶i Phßng</t>
+    <t>Công ty TNHH Tuyến Container TS Hà Nội</t>
+  </si>
+  <si>
+    <t>11 Võ Thị Sáu, Máy Tơ, Ngô Quyền, hải Phòng</t>
   </si>
   <si>
     <t>0201747264</t>
@@ -7885,10 +7885,10 @@
     <t>TSON</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i BiÓn Thiªn S¬n</t>
-  </si>
-  <si>
-    <t>111 Chïa hµng - Lª Ch©n - H¶i Phßng</t>
+    <t>Công ty TNHH Vận Tải Biển Thiên Sơn</t>
+  </si>
+  <si>
+    <t>111 Chùa hàng - Lê Chân - Hải Phòng</t>
   </si>
   <si>
     <t>0200620956</t>
@@ -7897,10 +7897,10 @@
     <t>TSQUANGNINH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn XNK Thñy S¶n Qu¶ng Ninh</t>
-  </si>
-  <si>
-    <t>35 BÕn Tµu - TP. H¹ Long - Qu¶ng Ninh</t>
+    <t>Công ty cổ phần XNK Thủy Sản Quảng Ninh</t>
+  </si>
+  <si>
+    <t>35 Bến Tàu - TP. Hạ Long - Quảng Ninh</t>
   </si>
   <si>
     <t>5700100714</t>
@@ -7909,10 +7909,10 @@
     <t>TTBN</t>
   </si>
   <si>
-    <t>Cty TNHH vËn t¶i biÓn vµ thuª tµu BiÓn Nam</t>
-  </si>
-  <si>
-    <t>Hoµng DiÖu - Ph­êng 12 - QuËn 4 - TP. HCM</t>
+    <t>Cty TNHH vận tải biển và thuê tàu Biển Nam</t>
+  </si>
+  <si>
+    <t>Hoàng Diệu - Phường 12 - Quận 4 - TP. HCM</t>
   </si>
   <si>
     <t>0305047771</t>
@@ -7921,10 +7921,10 @@
     <t>TTC</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i DÞch Vô vµ S¶n XuÊt T.T.C</t>
-  </si>
-  <si>
-    <t>78/38 TuÖ TÜnh - Nha Trang - Kh¸nh Hoµ</t>
+    <t>Công ty TNHH Thương Mại Dịch Vụ và Sản Xuất T.T.C</t>
+  </si>
+  <si>
+    <t>78/38 Tuệ Tĩnh - Nha Trang - Khánh Hoà</t>
   </si>
   <si>
     <t>4200707604</t>
@@ -7933,19 +7933,19 @@
     <t>TTCBIENHOA</t>
   </si>
   <si>
-    <t>C«ng Ty Cæ PhÇn Thµnh Thµnh C«ng - Biªn Hoµ</t>
-  </si>
-  <si>
-    <t>X· T©n H­ng - HuyÖn T©n Ch©u - TØnh T©y Ninh</t>
+    <t>Công Ty Cổ Phần Thành Thành Công - Biên Hoà</t>
+  </si>
+  <si>
+    <t>Xã Tân Hưng - Huyện Tân Châu - Tỉnh Tây Ninh</t>
   </si>
   <si>
     <t>TTDANANG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i vµ thuª tµu §µ N½ng</t>
-  </si>
-  <si>
-    <t>113 Hoµng V¨n Thô , P. Ph­íc Nninh, Q. H¶i Ch©u, TP. §µ N½ng, VN</t>
+    <t>Công ty cổ phần vận tải và thuê tàu Đà Nẵng</t>
+  </si>
+  <si>
+    <t>113 Hoàng Văn Thụ , P. Phước Nninh, Q. Hải Châu, TP. Đà Nẵng, VN</t>
   </si>
   <si>
     <t>0400453269</t>
@@ -7954,10 +7954,10 @@
     <t>TTHANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH m¸y vµ thiÕt bÞ Thiªn Thanh</t>
-  </si>
-  <si>
-    <t>73C Ph­¬ng mai, Hµ Néi</t>
+    <t>Công ty TNHH máy và thiết bị Thiên Thanh</t>
+  </si>
+  <si>
+    <t>73C Phương mai, Hà Nội</t>
   </si>
   <si>
     <t>0101491241</t>
@@ -7966,10 +7966,10 @@
     <t>TTTHINH</t>
   </si>
   <si>
-    <t>Cty CP §Çu t­ TM T©n T©y ThÞnh</t>
-  </si>
-  <si>
-    <t>69/151 NguyÔn §øc C¶nh, Hoµng Mai, HN</t>
+    <t>Cty CP Đầu tư TM Tân Tây Thịnh</t>
+  </si>
+  <si>
+    <t>69/151 Nguyễn Đức Cảnh, Hoàng Mai, HN</t>
   </si>
   <si>
     <t>0102343454</t>
@@ -7978,19 +7978,19 @@
     <t>TTVT2</t>
   </si>
   <si>
-    <t>Trung t©m viÔn th«ng 2</t>
-  </si>
-  <si>
-    <t>Sè 4 L¹ch Tray - Ng« QuyÒn - HP</t>
+    <t>Trung tâm viễn thông 2</t>
+  </si>
+  <si>
+    <t>Số 4 Lạch Tray - Ngô Quyền - HP</t>
   </si>
   <si>
     <t>TUANLONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i BiÓn TuÊn Long</t>
-  </si>
-  <si>
-    <t>sè 337 §µ N½ng - Ph­êng V¹n Mü - QuËn Ng« QuyÒn - TP. H¶i Phßng</t>
+    <t>Công ty TNHH Vận Tải Biển Tuấn Long</t>
+  </si>
+  <si>
+    <t>số 337 Đà Nẵng - Phường Vạn Mỹ - Quận Ngô Quyền - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201783939</t>
@@ -7999,10 +7999,10 @@
     <t>TUANTU</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i TuÊn Tó</t>
-  </si>
-  <si>
-    <t>ThÞ Tø §ång Gia, X· Kim Thµnh, Thµnh Phè H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Thương Mại Tuấn Tú</t>
+  </si>
+  <si>
+    <t>Thị Tứ Đồng Gia, Xã Kim Thành, Thành Phố Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0800375826</t>
@@ -8011,10 +8011,10 @@
     <t>TUELAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Kinh Doanh Th­¬ng M¹i TuÖ L©m</t>
-  </si>
-  <si>
-    <t>Tæ 43C, Côm 5, Ph­êng §«ng Khª, QuËn NG« QuyÒn, TP. H¶i Phßng , VN</t>
+    <t>Công ty TNHH Kinh Doanh Thương Mại Tuệ Lâm</t>
+  </si>
+  <si>
+    <t>Tổ 43C, Cụm 5, Phường Đông Khê, Quận NGô Quyền, TP. Hải Phòng , VN</t>
   </si>
   <si>
     <t>0202028985</t>
@@ -8023,10 +8023,10 @@
     <t>TVBINHAN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng m¹i vµ DV TiÕp vËn B×nh An</t>
-  </si>
-  <si>
-    <t>Sè 189 A phè chî Lòng, tæ 15, Ph­êng §»ng h¶i, QuËn h¶i An, TP. HP</t>
+    <t>Công ty TNHH Thương mại và DV Tiếp vận Bình An</t>
+  </si>
+  <si>
+    <t>Số 189 A phố chợ Lũng, tổ 15, Phường Đằng hải, Quận hải An, TP. HP</t>
   </si>
   <si>
     <t>0201870035</t>
@@ -8035,10 +8035,10 @@
     <t>TVGMD</t>
   </si>
   <si>
-    <t>C«ng Ty TNHH Mét Thµnh Viªn TiÕp VËn Gemadept</t>
-  </si>
-  <si>
-    <t>§­êng sè 8 - KCN Sãng ThÇn - HuyÖn DÜ An - TØnh B×nh D­¬ng</t>
+    <t>Công Ty TNHH Một Thành Viên Tiếp Vận Gemadept</t>
+  </si>
+  <si>
+    <t>Đường số 8 - KCN Sóng Thần - Huyện Dĩ An - Tỉnh Bình Dương</t>
   </si>
   <si>
     <t>3700882169</t>
@@ -8047,10 +8047,10 @@
     <t>TVT</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ®Çu t­ x©y dùng vµ th­¬ng m¹i - TVT</t>
-  </si>
-  <si>
-    <t>Tæ 31 Khu Hoµ l¹c - Ph­êng CÈm B×nh - TP. CÈm Ph¶ - TØnh Qu¶ng Ninh</t>
+    <t>Công ty cổ phần đầu tư xây dựng và thương mại - TVT</t>
+  </si>
+  <si>
+    <t>Tổ 31 Khu Hoà lạc - Phường Cẩm Bình - TP. Cẩm Phả - Tỉnh Quảng Ninh</t>
   </si>
   <si>
     <t>5700654744</t>
@@ -8059,7 +8059,7 @@
     <t>UBND NGOQUYEN</t>
   </si>
   <si>
-    <t>Uû ban nh©n d©n quËn Ng« QuyÒn - Phßng TC kÕ Ho¹ch</t>
+    <t>Uỷ ban nhân dân quận Ngô Quyền - Phòng TC kế Hoạch</t>
   </si>
   <si>
     <t>ULTRABULK</t>
@@ -8128,16 +8128,16 @@
     <t>VAN</t>
   </si>
   <si>
-    <t>An H÷u V¨n</t>
+    <t>An Hữu Văn</t>
   </si>
   <si>
     <t>VANLOC</t>
   </si>
   <si>
-    <t>C«ng ty TNHH V¹n Léc</t>
-  </si>
-  <si>
-    <t>139 Khèi 1B, thÞ trÊn §«ng Anh, Hµ Néi</t>
+    <t>Công ty TNHH Vạn Lộc</t>
+  </si>
+  <si>
+    <t>139 Khối 1B, thị trấn Đông Anh, Hà Nội</t>
   </si>
   <si>
     <t>0100766126</t>
@@ -8146,10 +8146,10 @@
     <t>VANNIEN</t>
   </si>
   <si>
-    <t>C«ng ty CP V¹n Niªn</t>
-  </si>
-  <si>
-    <t>Sè 3 Lª Th¸nh T«ng, H¶i Phßng</t>
+    <t>Công ty CP Vạn Niên</t>
+  </si>
+  <si>
+    <t>Số 3 Lê Thánh Tông, Hải Phòng</t>
   </si>
   <si>
     <t>0200419581</t>
@@ -8158,10 +8158,10 @@
     <t>VANTAIANHAI</t>
   </si>
   <si>
-    <t>C«ng ty TNHH DÞch Vô Vµ Th­¬ng M¹i VËn T¶i An H¶i</t>
-  </si>
-  <si>
-    <t>Sè 110 L« 17 më réng, Trung hµnh 5, Ph­êng §»ng L©m, QuËn haie An, Thµnh Phè HP</t>
+    <t>Công ty TNHH Dịch Vụ Và Thương Mại Vận Tải An Hải</t>
+  </si>
+  <si>
+    <t>Số 110 Lô 17 mở rộng, Trung hành 5, Phường Đằng Lâm, Quận haie An, Thành Phố HP</t>
   </si>
   <si>
     <t>0200964322</t>
@@ -8170,10 +8170,10 @@
     <t>VANTAIBACVIET</t>
   </si>
   <si>
-    <t>C«ng ty TNHH DÞch Vô Th­¬ng M¹i Vµ VËn T¶i B¾c ViÖt</t>
-  </si>
-  <si>
-    <t>Sè 112 ®­êng Ng« QuyÒn, Ph­êng M¸y Chai, QuËn NG« QuyÒn, TP. H¶i Phßng</t>
+    <t>Công ty TNHH Dịch Vụ Thương Mại Và Vận Tải Bắc Việt</t>
+  </si>
+  <si>
+    <t>Số 112 đường Ngô Quyền, Phường Máy Chai, Quận NGô Quyền, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201649926</t>
@@ -8182,10 +8182,10 @@
     <t>VANTAIHAIMINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i Vµ VËn T¶i H¶i Minh</t>
-  </si>
-  <si>
-    <t>Sè nhµ 335, ®­êng NguyÔn §øc C¶nh, TT Diªm §iÒm, H. Th¸i Thôy, T. Th¸i B×nh, VN</t>
+    <t>Công ty TNHH Thương Mại Và Vận Tải Hải Minh</t>
+  </si>
+  <si>
+    <t>Số nhà 335, đường Nguyễn Đức Cảnh, TT Diêm Điềm, H. Thái Thụy, T. Thái Bình, VN</t>
   </si>
   <si>
     <t>1001235006</t>
@@ -8194,10 +8194,10 @@
     <t>VANTAINHATMINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §Çu T­ Th­¬ng M¹i VËn T¶i NhËt Minh</t>
-  </si>
-  <si>
-    <t>Sè 414 Lª Th¸nh T«ng, P. M¸y Chai, Q. Ng« QuyÒn, TP. H¶i Phßng</t>
+    <t>Công ty TNHH Đầu Tư Thương Mại Vận Tải Nhật Minh</t>
+  </si>
+  <si>
+    <t>Số 414 Lê Thánh Tông, P. Máy Chai, Q. Ngô Quyền, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200962124</t>
@@ -8206,10 +8206,10 @@
     <t>VANTAINHATVIET</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i NhËt ViÖt</t>
-  </si>
-  <si>
-    <t>151 NguyÔn V¨n Thñ, Ph­êng §a Kao, QuËn 1, Thµnh Phè Hå CHÝ Minh, ViÖt Nam</t>
+    <t>Công ty cổ phần vận tải Nhật Việt</t>
+  </si>
+  <si>
+    <t>151 Nguyễn Văn Thủ, Phường Đa Kao, Quận 1, Thành Phố Hồ CHí Minh, Việt Nam</t>
   </si>
   <si>
     <t>0308515724</t>
@@ -8218,10 +8218,10 @@
     <t>VANTAITHUY-VINACOMIN</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i thñy - Vinacomin</t>
-  </si>
-  <si>
-    <t>108 Lª Th¸nh T«ng, P. Hång Gai, TP. h¹ Long, T. Qu¶ng Ninh</t>
+    <t>Công ty cổ phần vận tải thủy - Vinacomin</t>
+  </si>
+  <si>
+    <t>108 Lê Thánh Tông, P. Hồng Gai, TP. hạ Long, T. Quảng Ninh</t>
   </si>
   <si>
     <t>5700647458</t>
@@ -8230,10 +8230,10 @@
     <t>VATCACH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Logistics Interserco - VËt C¸ch</t>
-  </si>
-  <si>
-    <t>Toµ nhµ Lª Ph¹m, 98-100 T« HiÖu, Ph­êng Lª Ch©n, TP. H¶i Phßng</t>
+    <t>Công ty TNHH Logistics Interserco - Vật Cách</t>
+  </si>
+  <si>
+    <t>Toà nhà Lê Phạm, 98-100 Tô Hiệu, Phường Lê Chân, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0202086962</t>
@@ -8242,10 +8242,10 @@
     <t>VATTUHP</t>
   </si>
   <si>
-    <t>C«ng ty CP ThÐp &amp; vËt t­ H¶i Phßng</t>
-  </si>
-  <si>
-    <t>Km 92 ®­êng 5 míi, Hïng V­¬ng, HB, HP</t>
+    <t>Công ty CP Thép &amp; vật tư Hải Phòng</t>
+  </si>
+  <si>
+    <t>Km 92 đường 5 mới, Hùng Vương, HB, HP</t>
   </si>
   <si>
     <t>0200421693</t>
@@ -8254,10 +8254,10 @@
     <t>VAXUCO MIEN BAC</t>
   </si>
   <si>
-    <t>C«ng ty TNHH MTV dÞch vô kho vËn Vaxuco MiÒn B¾c</t>
-  </si>
-  <si>
-    <t>Sè 1 TrÇn H­ng §¹o - Ph­êng §«ng H¶i - H¶i An - H¶i Phßng</t>
+    <t>Công ty TNHH MTV dịch vụ kho vận Vaxuco Miền Bắc</t>
+  </si>
+  <si>
+    <t>Số 1 Trần Hưng Đạo - Phường Đông Hải - Hải An - Hải Phòng</t>
   </si>
   <si>
     <t>0201257460</t>
@@ -8266,10 +8266,10 @@
     <t>VEDAN VIETNAM</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn h÷ h¹n VEDAN ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Quèc lé 51, Êp 1A, X· Ph­íc Th¸i, TØnh §ång Nai, ViÖt Nam</t>
+    <t>Công ty cổ phần hữ hạn VEDAN Việt Nam</t>
+  </si>
+  <si>
+    <t>Quốc lộ 51, ấp 1A, Xã Phước Thái, Tỉnh Đồng Nai, Việt Nam</t>
   </si>
   <si>
     <t>3600239719</t>
@@ -8287,19 +8287,19 @@
     <t>VHAN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH vËn t¶i biÓn vµ th­¬ng m¹i ViÖt Hµn</t>
-  </si>
-  <si>
-    <t>Sè 18 ®¹i lé x« viÕt NghÖ TÜnh - Xãm 10 - X· Nghi Phó - TP. Vinh NgÖn</t>
+    <t>Công ty TNHH vận tải biển và thương mại Việt Hàn</t>
+  </si>
+  <si>
+    <t>Số 18 đại lộ xô viết Nghệ Tĩnh - Xóm 10 - Xã Nghi Phú - TP. Vinh Ngện</t>
   </si>
   <si>
     <t>VICMAC</t>
   </si>
   <si>
-    <t>CN c«ng ty cæ phÇn vËn t¶i biÓn vµ xuÊt khÈu lao ®éng - TT thuuÒn viªn Vicmac</t>
-  </si>
-  <si>
-    <t>Sè 338 L¹ch tray, Ph­êng §»ng Giang, QuËn Ng« QuyÒn, TP. H¶i Phßng</t>
+    <t>CN công ty cổ phần vận tải biển và xuất khẩu lao động - TT thuuền viên Vicmac</t>
+  </si>
+  <si>
+    <t>Số 338 Lạch tray, Phường Đằng Giang, Quận Ngô Quyền, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200123506-005</t>
@@ -8308,10 +8308,10 @@
     <t>VIETDONG</t>
   </si>
   <si>
-    <t>C«ng ty ViÖt §«ng</t>
-  </si>
-  <si>
-    <t>Yªn Viªn, Gia L©m, Hµ Néi</t>
+    <t>Công ty Việt Đông</t>
+  </si>
+  <si>
+    <t>Yên Viên, Gia Lâm, Hà Nội</t>
   </si>
   <si>
     <t>0100908589</t>
@@ -8320,10 +8320,10 @@
     <t>VIETHAI</t>
   </si>
   <si>
-    <t>C«ng ty TNHH ViÖt H¶i</t>
-  </si>
-  <si>
-    <t>Sè 10/97 Mª Linh - Ph­êng An Biªn - QuËn Lª Ch©n - TP. H¶i Phßng</t>
+    <t>Công ty TNHH Việt Hải</t>
+  </si>
+  <si>
+    <t>Số 10/97 Mê Linh - Phường An Biên - Quận Lê Chân - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200122277</t>
@@ -8332,10 +8332,10 @@
     <t>VIETHAN</t>
   </si>
   <si>
-    <t>Cty CP XD &amp; TM tæng hîp ViÖt Hµn</t>
-  </si>
-  <si>
-    <t>360 B¹ch §»ng, Hoµn KiÕm, HN</t>
+    <t>Cty CP XD &amp; TM tổng hợp Việt Hàn</t>
+  </si>
+  <si>
+    <t>360 Bạch Đằng, Hoàn Kiếm, HN</t>
   </si>
   <si>
     <t>0101903311</t>
@@ -8344,10 +8344,10 @@
     <t>VIETHOANG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i ViÖt Hoµng</t>
-  </si>
-  <si>
-    <t>Sè 44 Ph¹m Tö Nghi, P. NghÜa X¸, Q. Lª Ch©n, TP. H¶i Phßng</t>
+    <t>Công ty TNHH Thương Mại Việt Hoàng</t>
+  </si>
+  <si>
+    <t>Số 44 Phạm Tử Nghi, P. Nghĩa Xá, Q. Lê Chân, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200644026</t>
@@ -8356,10 +8356,10 @@
     <t>VIETNAM</t>
   </si>
   <si>
-    <t>Cty TNHH HD ViÖt Nam</t>
-  </si>
-  <si>
-    <t>A 25/100 Hoµng CÇu, §èng §a, HN</t>
+    <t>Cty TNHH HD Việt Nam</t>
+  </si>
+  <si>
+    <t>A 25/100 Hoàng Cầu, Đống Đa, HN</t>
   </si>
   <si>
     <t>0101537866</t>
@@ -8368,10 +8368,10 @@
     <t>VIETNAM CMT</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ViÖt Nam CMT</t>
-  </si>
-  <si>
-    <t>TÇng 6 tßa nhµ Lª Ph¹m, sè 95-100 T« HiÖu, P. Tr¹i Cau, Q. Lª Ch©n, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần Việt Nam CMT</t>
+  </si>
+  <si>
+    <t>Tầng 6 tòa nhà Lê Phạm, số 95-100 Tô Hiệu, P. Trại Cau, Q. Lê Chân, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201019554</t>
@@ -8380,10 +8380,10 @@
     <t>VIETPHAT</t>
   </si>
   <si>
-    <t>Cty CP TM &amp; DL ViÖt Ph¸p</t>
-  </si>
-  <si>
-    <t>Thanh L­¬ng - Hai Bµ Tr­ng - Hµ Néi</t>
+    <t>Cty CP TM &amp; DL Việt Pháp</t>
+  </si>
+  <si>
+    <t>Thanh Lương - Hai Bà Trưng - Hà Nội</t>
   </si>
   <si>
     <t>0102956838</t>
@@ -8392,10 +8392,10 @@
     <t>VIETRANS</t>
   </si>
   <si>
-    <t>VIETRANS H¶i Phßng</t>
-  </si>
-  <si>
-    <t>Sè 08 Hoµng DiÖu, HP</t>
+    <t>VIETRANS Hải Phòng</t>
+  </si>
+  <si>
+    <t>Số 08 Hoàng Diệu, HP</t>
   </si>
   <si>
     <t>0200128737</t>
@@ -8404,10 +8404,10 @@
     <t>VIETTHUAN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i ViÖt ThuËn</t>
-  </si>
-  <si>
-    <t>Sè 412, ®­êng Quang Trung, Ph­êng  U«ng BÝ, TØnh Qu¶ng Ninh, ViÖt Nam</t>
+    <t>Công ty TNHH Vận Tải Việt Thuận</t>
+  </si>
+  <si>
+    <t>Số 412, đường Quang Trung, Phường  Uông Bí, Tỉnh Quảng Ninh, Việt Nam</t>
   </si>
   <si>
     <t>5700562451</t>
@@ -8416,10 +8416,10 @@
     <t>VIMC</t>
   </si>
   <si>
-    <t>C«ng ty vËn t¶i biÓn VIMC</t>
-  </si>
-  <si>
-    <t>Sè 1 §µo Duy Anh, ph­êng Ph­¬ng Mai, quËn §èng §a, thµnh phè Hµ Néi</t>
+    <t>Công ty vận tải biển VIMC</t>
+  </si>
+  <si>
+    <t>Số 1 Đào Duy Anh, phường Phương Mai, quận Đống Đa, thành phố Hà Nội</t>
   </si>
   <si>
     <t>0100104595-001</t>
@@ -8428,10 +8428,10 @@
     <t>VINA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §Çu T­ vµ S¶n XuÊt VINA</t>
-  </si>
-  <si>
-    <t>Xãm 7 - X· Thñy S¬n - HuyÖn Thñy Nguyªn - TP. H¶i Phßng</t>
+    <t>Công ty TNHH Đầu Tư và Sản Xuất VINA</t>
+  </si>
+  <si>
+    <t>Xóm 7 - Xã Thủy Sơn - Huyện Thủy Nguyên - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201651040</t>
@@ -8440,10 +8440,10 @@
     <t>VINACOMIN</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn ®Çu t­ th­¬ng m¹i vµ dÞch vô Vinacomin</t>
-  </si>
-  <si>
-    <t>Sè 1 Phan §×nh Giãt, P. Ph­¬ng LiÖt, Q. Hoang Mai, TP. Hµ Néi</t>
+    <t>Công ty cổ phần đầu tư thương mại và dịch vụ Vinacomin</t>
+  </si>
+  <si>
+    <t>Số 1 Phan Đình Giót, P. Phương Liệt, Q. Hoang Mai, TP. Hà Nội</t>
   </si>
   <si>
     <t>0200170658</t>
@@ -8452,10 +8452,10 @@
     <t>VINALUMBER</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Vina Lumber Products</t>
-  </si>
-  <si>
-    <t>20/16 Phan Huy ¤n, Ph­êng 19, QuËn B×nh Th¹nh, Thµnh Phè Hå ChÝ Minh, ViÖt Nam</t>
+    <t>Công ty TNHH Vina Lumber Products</t>
+  </si>
+  <si>
+    <t>20/16 Phan Huy Ôn, Phường 19, Quận Bình Thạnh, Thành Phố Hồ Chí Minh, Việt Nam</t>
   </si>
   <si>
     <t>0315831819</t>
@@ -8464,10 +8464,10 @@
     <t>VINASHIP</t>
   </si>
   <si>
-    <t>Cty Cæ PhÇn vËn t¶i biÓn VINASHIP</t>
-  </si>
-  <si>
-    <t>Sè 14 Vâ Nguyªn Gi¸p, ph­êng An Biªn, TP H¶i Phßng, ViÖt Nam</t>
+    <t>Cty Cổ Phần vận tải biển VINASHIP</t>
+  </si>
+  <si>
+    <t>Số 14 Võ Nguyên Giáp, phường An Biên, TP Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0200119965</t>
@@ -8476,10 +8476,10 @@
     <t>VINAUS</t>
   </si>
   <si>
-    <t>Cty LDSX thÐp VINAUSTEEL</t>
-  </si>
-  <si>
-    <t>Km9 VËt C¸ch, Qu¸n Toan, Hång Bµng, HP</t>
+    <t>Cty LDSX thép VINAUSTEEL</t>
+  </si>
+  <si>
+    <t>Km9 Vật Cách, Quán Toan, Hồng Bàng, HP</t>
   </si>
   <si>
     <t>0200108811001</t>
@@ -8488,19 +8488,19 @@
     <t>VINHPHU</t>
   </si>
   <si>
-    <t>Cty CP vËt t­ tæng hîp VÜnh Phó</t>
-  </si>
-  <si>
-    <t>2316 Hïng V­¬ng - ViÖt Tr× - Phó Thä</t>
+    <t>Cty CP vật tư tổng hợp Vĩnh Phú</t>
+  </si>
+  <si>
+    <t>2316 Hùng Vương - Việt Trì - Phú Thọ</t>
   </si>
   <si>
     <t>VINHPHUOC</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VÜnh Ph­íc</t>
-  </si>
-  <si>
-    <t>Sè 3 Lª Th¸nh T«ng - QuËn Ng« QuyÒn - TP. H¶i Phßng</t>
+    <t>Công ty TNHH Vĩnh Phước</t>
+  </si>
+  <si>
+    <t>Số 3 Lê Thánh Tông - Quận Ngô Quyền - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0200410331</t>
@@ -8509,10 +8509,10 @@
     <t>VINHSINH</t>
   </si>
   <si>
-    <t>Cty TNHH VÜnh Sinh</t>
-  </si>
-  <si>
-    <t>160 §×nh §«ng, Lª Ch©n, HP</t>
+    <t>Cty TNHH Vĩnh Sinh</t>
+  </si>
+  <si>
+    <t>160 Đình Đông, Lê Chân, HP</t>
   </si>
   <si>
     <t>0200436160</t>
@@ -8521,10 +8521,10 @@
     <t>VINHTUY</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn VËn T¶i VÜnh Tuy</t>
-  </si>
-  <si>
-    <t>Sè 3/27, phè VÜnh Tuy, P. VÜnh Tuy,  TP Hµ Néi, ViÖt Nam</t>
+    <t>Công ty Cổ Phần Vận Tải Vĩnh Tuy</t>
+  </si>
+  <si>
+    <t>Số 3/27, phố Vĩnh Tuy, P. Vĩnh Tuy,  TP Hà Nội, Việt Nam</t>
   </si>
   <si>
     <t>0101201383</t>
@@ -8545,10 +8545,10 @@
     <t>VISSAI</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TËp ®oµn Hoµng Ph¸t Vissai</t>
-  </si>
-  <si>
-    <t>Ninh B×nh</t>
+    <t>Công ty TNHH Tập đoàn Hoàng Phát Vissai</t>
+  </si>
+  <si>
+    <t>Ninh Bình</t>
   </si>
   <si>
     <t>VKCORPORATION</t>
@@ -8560,10 +8560,10 @@
     <t>VLCN</t>
   </si>
   <si>
-    <t>Cty TNHH X©y l¾p vµ vËt liÖu C«ng NghiÖp</t>
-  </si>
-  <si>
-    <t>Sè 2B1 §Çm TrÊu, Hai Bµ Tr­ng, Hµ Néi</t>
+    <t>Cty TNHH Xây lắp và vật liệu Công Nghiệp</t>
+  </si>
+  <si>
+    <t>Số 2B1 Đầm Trấu, Hai Bà Trưng, Hà Nội</t>
   </si>
   <si>
     <t>0101285979</t>
@@ -8572,10 +8572,10 @@
     <t>VLHNAMTRIEU</t>
   </si>
   <si>
-    <t>C«ng ty TNHH C«ng NghÖ VËt LiÖu Hµn Nam TriÖu</t>
-  </si>
-  <si>
-    <t>Sè 8/282 §µ N½ng - V¹n Mü - Ng« QuyÒn, H¶i Phßng</t>
+    <t>Công ty TNHH Công Nghệ Vật Liệu Hàn Nam Triệu</t>
+  </si>
+  <si>
+    <t>Số 8/282 Đà Nẵng - Vạn Mỹ - Ngô Quyền, Hải Phòng</t>
   </si>
   <si>
     <t>0201706885</t>
@@ -8587,7 +8587,7 @@
     <t>VMC Company</t>
   </si>
   <si>
-    <t>23/16  Hïng V­¬ng, ViÖt Tr×, Phó Thä</t>
+    <t>23/16  Hùng Vương, Việt Trì, Phú Thọ</t>
   </si>
   <si>
     <t>2600305261</t>
@@ -8596,10 +8596,10 @@
     <t>VOICANGLONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Mét Thµnh Viªn V«i Cµng Long</t>
-  </si>
-  <si>
-    <t>2/27 §­êng §ç M­êi, Khu phè 6, Ph­êng HiÖp B×nh, Thµnh Phè Hå ChÝ MInh, ViÖt Nam</t>
+    <t>Công ty TNHH Một Thành Viên Vôi Càng Long</t>
+  </si>
+  <si>
+    <t>2/27 Đường Đỗ Mười, Khu phố 6, Phường Hiệp Bình, Thành Phố Hồ Chí MInh, Việt Nam</t>
   </si>
   <si>
     <t>0315458410</t>
@@ -8608,19 +8608,19 @@
     <t>VOISONHOA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH S¶n XuÊt Vµ Th­¬ng M¹i V«i S¬n Hoµ</t>
-  </si>
-  <si>
-    <t>10/1 Quèc Lé 1A, Khu phè 6, Ph­êng B×nh HiÖp, Thµnh Phè Hå ChÝ MInh</t>
+    <t>Công ty TNHH Sản Xuất Và Thương Mại Vôi Sơn Hoà</t>
+  </si>
+  <si>
+    <t>10/1 Quốc Lộ 1A, Khu phố 6, Phường Bình Hiệp, Thành Phố Hồ Chí MInh</t>
   </si>
   <si>
     <t>VOITANPHAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH S¶n XuÊt Th­¬ng m¹i DÞch Vô V«i TÊn Ph¸t</t>
-  </si>
-  <si>
-    <t>Sè 6 Quèc Lé 1A, KP3, Ph­êng HiÖp B×nh Ph­íc, QuËn Thue §øc, TP. HCM</t>
+    <t>Công ty TNHH Sản Xuất Thương mại Dịch Vụ Vôi Tấn Phát</t>
+  </si>
+  <si>
+    <t>Số 6 Quốc Lộ 1A, KP3, Phường Hiệp Bình Phước, Quận Thue Đức, TP. HCM</t>
   </si>
   <si>
     <t>0312621404</t>
@@ -8629,7 +8629,7 @@
     <t>VT2</t>
   </si>
   <si>
-    <t>Sè 04 L¹ch Tray - Ng« QuyÒn - H¶i Phßng</t>
+    <t>Số 04 Lạch Tray - Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0200287977-001</t>
@@ -8638,10 +8638,10 @@
     <t>VTB SHT</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn VËn T¶i BiÓn SHT</t>
-  </si>
-  <si>
-    <t>Sè 12/508 Lª Th¸nh T«ng, P. V¹n Mü, Q. Ng« QuyÒn, Tp. H¶i Phßng</t>
+    <t>Công ty cổ phần Vận Tải Biển SHT</t>
+  </si>
+  <si>
+    <t>Số 12/508 Lê Thánh Tông, P. Vạn Mỹ, Q. Ngô Quyền, Tp. Hải Phòng</t>
   </si>
   <si>
     <t>0201858969</t>
@@ -8650,10 +8650,10 @@
     <t>VTB&amp;TM3M</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i biÓn vµ th­¬ng m¹i 3M</t>
-  </si>
-  <si>
-    <t>Sè 3 Lª Th¸nh T«ng, Ph­êng M¸y T¬, QuËn Ng« QuyÒn, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần vận tải biển và thương mại 3M</t>
+  </si>
+  <si>
+    <t>Số 3 Lê Thánh Tông, Phường Máy Tơ, Quận Ngô Quyền, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201112225</t>
@@ -8662,10 +8662,10 @@
     <t>VTB&amp;XNK HTK</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i BiÓn vµ XuÊt NhËp KhÈu  HTK</t>
-  </si>
-  <si>
-    <t>Sè 341 §µ N½ng,Ph­êng V¹n Mý,QuËn Ng« QuyÒn, Thµnh Phè H¶i Phßng</t>
+    <t>Công ty TNHH Vận Tải Biển và Xuất Nhập Khẩu  HTK</t>
+  </si>
+  <si>
+    <t>Số 341 Đà Nẵng,Phường Vạn Mý,Quận Ngô Quyền, Thành Phố Hải Phòng</t>
   </si>
   <si>
     <t>0200458573</t>
@@ -8674,10 +8674,10 @@
     <t>VTB68</t>
   </si>
   <si>
-    <t>C«ng Ty Cæ PhÇn VËn T¶i BiÓn 68</t>
-  </si>
-  <si>
-    <t>Sè 132 khu 5, ThÞ trÊn Diªm §iÒn, huyÖn Th¸i Thuþ, TØnh th¸i B×nh</t>
+    <t>Công Ty Cổ Phần Vận Tải Biển 68</t>
+  </si>
+  <si>
+    <t>Số 132 khu 5, Thị trấn Diêm Điền, huyện Thái Thuỵ, Tỉnh thái Bình</t>
   </si>
   <si>
     <t>1001072094</t>
@@ -8686,10 +8686,10 @@
     <t>VTBANPHONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Du ThuyÒn VËn T¶i BiÓn An Phong</t>
-  </si>
-  <si>
-    <t>Sè 266, ®­êng P­¬ng L­u, Ph­êng §«ng h¶i 1, Q. H¶i An, TP. H¶i Phßng</t>
+    <t>Công ty TNHH Du Thuyền Vận Tải Biển An Phong</t>
+  </si>
+  <si>
+    <t>Số 266, đường Pương Lưu, Phường Đông hải 1, Q. Hải An, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201981352</t>
@@ -8698,10 +8698,10 @@
     <t>VTBB</t>
   </si>
   <si>
-    <t>C«ng ty Cæ phÇn vËn t¶i BiÓn B¾c</t>
-  </si>
-  <si>
-    <t>Sè 278 T«n §øc Th¾ng, P Hµng Bét, Q §èng §a, TP Hµ Néi</t>
+    <t>Công ty Cổ phần vận tải Biển Bắc</t>
+  </si>
+  <si>
+    <t>Số 278 Tôn Đức Thắng, P Hàng Bột, Q Đống Đa, TP Hà Nội</t>
   </si>
   <si>
     <t>0100105609</t>
@@ -8710,10 +8710,10 @@
     <t>VTBCHAUATBD</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i BiÓn Ch©u ¸ Th¸i B×nh D­¬ng</t>
-  </si>
-  <si>
-    <t>TÇng 7, Tßa nhµ 29 Huúnh Thóc Kh¸ng, Ph­êng L¸ng H¹, QuËn §èng §a, TP. Hµ Néi</t>
+    <t>Công ty TNHH Vận Tải Biển Châu á Thái Bình Dương</t>
+  </si>
+  <si>
+    <t>Tầng 7, Tòa nhà 29 Huỳnh Thúc Kháng, Phường Láng Hạ, Quận Đống Đa, TP. Hà Nội</t>
   </si>
   <si>
     <t>0109512704</t>
@@ -8722,19 +8722,19 @@
     <t>VTBDANANG</t>
   </si>
   <si>
-    <t>C«ng ty CP vËn t¶i biÓn §µ N½ng</t>
-  </si>
-  <si>
-    <t>156 B¹ch §»ng - §µ N½ng</t>
+    <t>Công ty CP vận tải biển Đà Nẵng</t>
+  </si>
+  <si>
+    <t>156 Bạch Đằng - Đà Nẵng</t>
   </si>
   <si>
     <t>VTBDOANKET</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i BiÓn §oµn KÕt</t>
-  </si>
-  <si>
-    <t>Thöa 12 l« 8A2, Khu ®« thÞ míi ng· 5 s©n bay C¸t Bi, ph­êng Gia Viªn, TP H¶i Phßng, VN</t>
+    <t>Công ty TNHH Vận Tải Biển Đoàn Kết</t>
+  </si>
+  <si>
+    <t>Thửa 12 lô 8A2, Khu đô thị mới ngã 5 sân bay Cát Bi, phường Gia Viên, TP Hải Phòng, VN</t>
   </si>
   <si>
     <t>0202189598</t>
@@ -8743,22 +8743,22 @@
     <t>VTBDONGLONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH vËn t¶i biÓn §«ng Long</t>
+    <t>Công ty TNHH vận tải biển Đông Long</t>
   </si>
   <si>
     <t>VTBDUCDAT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i vËn t¶i biÓn §øc §¹t</t>
+    <t>Công ty TNHH Thương Mại vận tải biển Đức Đạt</t>
   </si>
   <si>
     <t>VTBHA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH MTV vËn t¶i biÓn Hoµng Anh</t>
-  </si>
-  <si>
-    <t>LÇu 5 -11 A Hoµng DiÖu - QuËn 4 - HCM</t>
+    <t>Công ty TNHH MTV vận tải biển Hoàng Anh</t>
+  </si>
+  <si>
+    <t>Lầu 5 -11 A Hoàng Diệu - Quận 4 - HCM</t>
   </si>
   <si>
     <t>0304776411</t>
@@ -8767,10 +8767,10 @@
     <t>VTBHAIAU</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i biÓn H¶i ¢u</t>
-  </si>
-  <si>
-    <t>Sè 12 §oµn Nh­ Hµi - Ph­êng 12 - QuËn 4 - TP. HCM</t>
+    <t>Công ty cổ phần vận tải biển Hải Âu</t>
+  </si>
+  <si>
+    <t>Số 12 Đoàn Như Hài - Phường 12 - Quận 4 - TP. HCM</t>
   </si>
   <si>
     <t>0302020027</t>
@@ -8779,10 +8779,10 @@
     <t>VTBHAIDUONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i Vµ VËn T¶i BiÓn H¶i D­¬ng</t>
-  </si>
-  <si>
-    <t>Sè nhµ 22, ngâ 105 Do·n KÕ ThiÖn, Ph­êng Mai DÞch, QuËn CÇu GiÊy, TP. HN</t>
+    <t>Công ty TNHH Thương Mại Và Vận Tải Biển Hải Dương</t>
+  </si>
+  <si>
+    <t>Số nhà 22, ngõ 105 Doãn Kế Thiện, Phường Mai Dịch, Quận Cầu Giấy, TP. HN</t>
   </si>
   <si>
     <t>0108527899</t>
@@ -8791,10 +8791,10 @@
     <t>VTBHAIPHUONG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH vËn t¶i biÓn H¶i Ph­¬ng</t>
-  </si>
-  <si>
-    <t>TDP Phó Thä, thÞ trÊn C¸t Thµnh, huyÖn Trùc Ninh, tØnh Nam §Þnh</t>
+    <t>Công ty TNHH vận tải biển Hải Phương</t>
+  </si>
+  <si>
+    <t>TDP Phú Thọ, thị trấn Cát Thành, huyện Trực Ninh, tỉnh Nam Định</t>
   </si>
   <si>
     <t>0601159524</t>
@@ -8803,10 +8803,10 @@
     <t>VTBHOANGLOC</t>
   </si>
   <si>
-    <t>CN c«ng ty cæ phÇn vËn t¶i biÓn Hoµng Léc</t>
-  </si>
-  <si>
-    <t>Sè 292, Khu 5, TT. Diªm §iÒm, H. Th¸i Thôy, T. Th¸i B×nh, VN</t>
+    <t>CN công ty cổ phần vận tải biển Hoàng Lộc</t>
+  </si>
+  <si>
+    <t>Số 292, Khu 5, TT. Diêm Điềm, H. Thái Thụy, T. Thái Bình, VN</t>
   </si>
   <si>
     <t>1000333297001</t>
@@ -8815,10 +8815,10 @@
     <t>VTBHOANGLONG</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn ®¹i lý vËn t¶i biÓn Hoµng Long</t>
-  </si>
-  <si>
-    <t>Sè 93. l« 26D, Lª Hång Phong, Ph­êng §«ng Khª, QuËn Ng« QuyÒn, HP</t>
+    <t>Công ty Cổ Phần đại lý vận tải biển Hoàng Long</t>
+  </si>
+  <si>
+    <t>Số 93. lô 26D, Lê Hồng Phong, Phường Đông Khê, Quận Ngô Quyền, HP</t>
   </si>
   <si>
     <t>0201148937</t>
@@ -8827,10 +8827,10 @@
     <t>VTBHOAPHAT</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i biÓn Hßa Ph¸t</t>
-  </si>
-  <si>
-    <t>Khu d©n c­ HiÖp Th­îng, Ph­êng HiÖp S¬n, ThÞ X· Kinh M«n, TØnh H¶i D­¬ng, VN</t>
+    <t>Công ty cổ phần vận tải biển Hòa Phát</t>
+  </si>
+  <si>
+    <t>Khu dân cư Hiệp Thượng, Phường Hiệp Sơn, Thị Xã Kinh Môn, Tỉnh Hải Dương, VN</t>
   </si>
   <si>
     <t>0801300608</t>
@@ -8839,10 +8839,10 @@
     <t>VTBHOAPHUONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dÞch vô th­¬ng m¹i vµ vËn t¶i biÓn Hoa Ph­îng</t>
-  </si>
-  <si>
-    <t>32/B8 §iÖn Biªn Phñ, Ph­êng 25, QuËn B×nh Th¹nh, TP. Hå ChÝ Minh</t>
+    <t>Công ty cổ phần dịch vụ thương mại và vận tải biển Hoa Phượng</t>
+  </si>
+  <si>
+    <t>32/B8 Điện Biên Phủ, Phường 25, Quận Bình Thạnh, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0308597847</t>
@@ -8851,10 +8851,10 @@
     <t>VTBLEPHAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i vµ VËn T¶i Lª Ph¹m</t>
-  </si>
-  <si>
-    <t>TÇng 9 - Sè 508 Lª Th¸nh T«ng - Ph­êng v¹n Mü - QuËn Ng« QuyÒn -HP</t>
+    <t>Công ty TNHH Thương Mại và Vận Tải Lê Phạm</t>
+  </si>
+  <si>
+    <t>Tầng 9 - Số 508 Lê Thánh Tông - Phường vạn Mỹ - Quận Ngô Quyền -HP</t>
   </si>
   <si>
     <t>0200824011</t>
@@ -8863,10 +8863,10 @@
     <t>VTBLONGTAN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH vËn t¶i biÓn Long T©n</t>
-  </si>
-  <si>
-    <t>Sè 93 l« 26D, Lª Hång Phong, P §«ng Khª, Q Ng« QuyÒn, TP H¶i Phßng</t>
+    <t>Công ty TNHH vận tải biển Long Tân</t>
+  </si>
+  <si>
+    <t>Số 93 lô 26D, Lê Hồng Phong, P Đông Khê, Q Ngô Quyền, TP Hải Phòng</t>
   </si>
   <si>
     <t>0201649098</t>
@@ -8875,10 +8875,10 @@
     <t>VTBMINHDUONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i biÓn Minh D­¬ng</t>
-  </si>
-  <si>
-    <t>Sè 8/80 ®­êng H¹ Lý, Ph­êng H¹ Lý, QuËn Hång Bµng, TP. H¶i Phßng</t>
+    <t>Công ty cổ phần vận tải biển Minh Dương</t>
+  </si>
+  <si>
+    <t>Số 8/80 đường Hạ Lý, Phường Hạ Lý, Quận Hồng Bàng, TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201617699</t>
@@ -8887,10 +8887,10 @@
     <t>VTBNAMPHAT</t>
   </si>
   <si>
-    <t>C«ng ty Cæ PhÇn §ãng Tµu vµ VËn T¶i BiÓn Nam Ph¸t</t>
-  </si>
-  <si>
-    <t>Khu phè 12, Ph­êng Hµ An, ThÞ X· Qu¶ng Yªn, TØnh Qu¶ng Ninh, ViÖt Nam</t>
+    <t>Công ty Cổ Phần Đóng Tàu và Vận Tải Biển Nam Phát</t>
+  </si>
+  <si>
+    <t>Khu phố 12, Phường Hà An, Thị Xã Quảng Yên, Tỉnh Quảng Ninh, Việt Nam</t>
   </si>
   <si>
     <t>5701483604</t>
@@ -8899,10 +8899,10 @@
     <t>VTBNEWSUN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH vËn t¶i biÓn NEWSUN</t>
-  </si>
-  <si>
-    <t>TÇng 2, tßa nhµ 381 §éi CÊn, P LiÔu Giai, Q Ba §×nh, TP Hµ Néi, ViÖt Nam</t>
+    <t>Công ty TNHH vận tải biển NEWSUN</t>
+  </si>
+  <si>
+    <t>Tầng 2, tòa nhà 381 Đội Cấn, P Liễu Giai, Q Ba Đình, TP Hà Nội, Việt Nam</t>
   </si>
   <si>
     <t>0110276145</t>
@@ -8911,10 +8911,10 @@
     <t>VTBNGOISAO</t>
   </si>
   <si>
-    <t>C«ng ty TNHH vËn t¶i biÓn Ng«i Sao</t>
-  </si>
-  <si>
-    <t>Sè nhµ129, khu 6, ThÞ TrÊn Diªm §iÒn, HuyÖn Th¸i Thôy, TØnh Th¸i B×nh</t>
+    <t>Công ty TNHH vận tải biển Ngôi Sao</t>
+  </si>
+  <si>
+    <t>Số nhà129, khu 6, Thị Trấn Diêm Điền, Huyện Thái Thụy, Tỉnh Thái Bình</t>
   </si>
   <si>
     <t>1001095567</t>
@@ -8923,10 +8923,10 @@
     <t>VTBNT</t>
   </si>
   <si>
-    <t>C«ng ty TNHH MTV vËn t¶i biÓn Nam TriÖu</t>
-  </si>
-  <si>
-    <t>Km90 + 300 ®­êng 5 míi, Hïng V­¬ng, Hång Bµng, H¶i Phßng</t>
+    <t>Công ty TNHH MTV vận tải biển Nam Triệu</t>
+  </si>
+  <si>
+    <t>Km90 + 300 đường 5 mới, Hùng Vương, Hồng Bàng, Hải Phòng</t>
   </si>
   <si>
     <t>0200787320</t>
@@ -8935,10 +8935,10 @@
     <t>VTBPHC</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i BiÓn PHC</t>
-  </si>
-  <si>
-    <t>Sè 300 Thiªn L«i, Ph­êng VÜnh NiÖm, QuËn Lª Ch©n, Thµnh Phè H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Vận Tải Biển PHC</t>
+  </si>
+  <si>
+    <t>Số 300 Thiên Lôi, Phường Vĩnh Niệm, Quận Lê Chân, Thành Phố Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0202024973</t>
@@ -8947,19 +8947,19 @@
     <t>VTBPHUONGDONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i biÓn vµ th­¬ng m¹i Ph­¬ng §«ng</t>
-  </si>
-  <si>
-    <t>278 T«n §øc Th¾ng - P.Hµng Bét, QuËn §èng §a, Hµ Néi</t>
+    <t>Công ty cổ phần vận tải biển và thương mại Phương Đông</t>
+  </si>
+  <si>
+    <t>278 Tôn Đức Thắng - P.Hàng Bột, Quận Đống Đa, Hà Nội</t>
   </si>
   <si>
     <t>VTBQT</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i biÓn Quèc tÕ</t>
-  </si>
-  <si>
-    <t>Sè 229 §µ N½ng - Ng« QuyÒn - HP</t>
+    <t>Công ty cổ phần vận tải biển Quốc tế</t>
+  </si>
+  <si>
+    <t>Số 229 Đà Nẵng - Ngô Quyền - HP</t>
   </si>
   <si>
     <t>0200613451</t>
@@ -8968,10 +8968,10 @@
     <t>VTBQTBINHMINH</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i biÓn quèc tÕ B×nh Minh</t>
-  </si>
-  <si>
-    <t>Sè 9/9 Hoµng DiÖu, P. Minh Khai, Q. Hång Bµng, TP. H¶i PHßng</t>
+    <t>Công ty cổ phần vận tải biển quốc tế Bình Minh</t>
+  </si>
+  <si>
+    <t>Số 9/9 Hoàng Diệu, P. Minh Khai, Q. Hồng Bàng, TP. Hải PHòng</t>
   </si>
   <si>
     <t>0200663910</t>
@@ -8980,10 +8980,10 @@
     <t>VTBQUOCTE</t>
   </si>
   <si>
-    <t>C«ng ty TNHH §¹i Lý vµ M«i Giíi vËn t¶i biÓn Quèc TÕ</t>
-  </si>
-  <si>
-    <t>TÇng 1 sè 5A - Vâ ThÞ S¸u - Ng« QuyÒn - H¶i Phßng</t>
+    <t>Công ty TNHH Đại Lý và Môi Giới vận tải biển Quốc Tế</t>
+  </si>
+  <si>
+    <t>Tầng 1 số 5A - Võ Thị Sáu - Ngô Quyền - Hải Phòng</t>
   </si>
   <si>
     <t>0200785926</t>
@@ -8992,19 +8992,19 @@
     <t>VTBRANGDONG</t>
   </si>
   <si>
-    <t>C«ng Ty TNHH §¹i Lý VËn T¶i BiÓn R¹ng §«ng</t>
-  </si>
-  <si>
-    <t>46 TrÇn Xu©n So¹n, Thµnh Phè Thanh Hãa</t>
+    <t>Công Ty TNHH Đại Lý Vận Tải Biển Rạng Đông</t>
+  </si>
+  <si>
+    <t>46 Trần Xuân Soạn, Thành Phố Thanh Hóa</t>
   </si>
   <si>
     <t>VTBTANVIETPHUC</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn t¶i BiÓn T©n ViÖt Phóc</t>
-  </si>
-  <si>
-    <t>Sè 1E Lý Tù Träng - Ph­¬ng Minh Khai - QuËn Hång bµng - TP. H¶i Phßng</t>
+    <t>Công ty TNHH Vận tải Biển Tân Việt Phúc</t>
+  </si>
+  <si>
+    <t>Số 1E Lý Tự Trọng - Phương Minh Khai - Quận Hồng bàng - TP. Hải Phòng</t>
   </si>
   <si>
     <t>0201243958</t>
@@ -9013,10 +9013,10 @@
     <t>VTBTINNGHIA</t>
   </si>
   <si>
-    <t>C«ng ty TNHH VËn T¶i BiÓn TÝn NghÜa</t>
-  </si>
-  <si>
-    <t>Km7, Quèc Lé 18, Khu C«ng NghiÖp QuÕ Vâ, TØnh B¾c Ninh</t>
+    <t>Công ty TNHH Vận Tải Biển Tín Nghĩa</t>
+  </si>
+  <si>
+    <t>Km7, Quốc Lộ 18, Khu Công Nghiệp Quế Võ, Tỉnh Bắc Ninh</t>
   </si>
   <si>
     <t>0101860273</t>
@@ -9025,22 +9025,22 @@
     <t>VTBTRUNGKIEN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng m¹i dÞch vô vËn t¶i biÓn Trung Kiªn</t>
+    <t>Công ty TNHH Thương mại dịch vụ vận tải biển Trung Kiên</t>
   </si>
   <si>
     <t>VTD</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Khai Th¸c Vµ Qu¶n Lý Tµu VTD</t>
+    <t>Công ty TNHH Khai Thác Và Quản Lý Tàu VTD</t>
   </si>
   <si>
     <t>VTDAUKHI</t>
   </si>
   <si>
-    <t>C«ng ty CP vËn t¶i dÇu khÝ ViÖt Nam</t>
-  </si>
-  <si>
-    <t>Sè 172A - NguyÔn §×nh ChiÓu - QuËn 3 - TP. Hå ChÝ Minh</t>
+    <t>Công ty CP vận tải dầu khí Việt Nam</t>
+  </si>
+  <si>
+    <t>Số 172A - Nguyễn Đình Chiểu - Quận 3 - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0300447310</t>
@@ -9049,10 +9049,10 @@
     <t>VTHAIPHONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn dÞch vô Th­¬ng m¹i vµ vËn t¶i H¶i Phßng</t>
-  </si>
-  <si>
-    <t>Sè 55H/55C VÜnh Tieens1, Ph­êng VÜnh NiÖm, QuËn Lª Ch©n, Thµnh Phè H¶i Phßng, VN</t>
+    <t>Công ty cổ phần dịch vụ Thương mại và vận tải Hải Phòng</t>
+  </si>
+  <si>
+    <t>Số 55H/55C Vĩnh Tieens1, Phường Vĩnh Niệm, Quận Lê Chân, Thành Phố Hải Phòng, VN</t>
   </si>
   <si>
     <t>0201715720</t>
@@ -9061,10 +9061,10 @@
     <t>VTHTHANH</t>
   </si>
   <si>
-    <t>Cty TNHH MTV vËn t¶i biÓn Hoµng Thµnh</t>
-  </si>
-  <si>
-    <t>Sè 185-187 (lÇu7) NguyÔn Th¸i Häc, QuËn 1, HCM</t>
+    <t>Cty TNHH MTV vận tải biển Hoàng Thành</t>
+  </si>
+  <si>
+    <t>Số 185-187 (lầu7) Nguyễn Thái Học, Quận 1, HCM</t>
   </si>
   <si>
     <t>0309402025</t>
@@ -9073,10 +9073,10 @@
     <t>VTKVI</t>
   </si>
   <si>
-    <t>Trung t©n dÞch vô viÔn th«ng KVI</t>
-  </si>
-  <si>
-    <t>Sè 9 L¸ng H¹, Hµ Néi</t>
+    <t>Trung tân dịch vụ viễn thông KVI</t>
+  </si>
+  <si>
+    <t>Số 9 Láng Hạ, Hà Nội</t>
   </si>
   <si>
     <t>0100692876-006</t>
@@ -9085,7 +9085,7 @@
     <t>VTMINHPHU</t>
   </si>
   <si>
-    <t>Xãm 10 Liªn Minh, H¶i Minh, H¶i HËu, Nam §Þnh</t>
+    <t>Xóm 10 Liên Minh, Hải Minh, Hải Hậu, Nam Định</t>
   </si>
   <si>
     <t>0600817308</t>
@@ -9094,10 +9094,10 @@
     <t>VTQT360</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i quèc tÕ 360 ®é Logistics</t>
-  </si>
-  <si>
-    <t>¤ 119, l« A3 khu ®« thÞ §¹i Kim, Ph­êng §Þnh C«ng, TP Hµ Néi</t>
+    <t>Công ty cổ phần vận tải quốc tế 360 độ Logistics</t>
+  </si>
+  <si>
+    <t>Ô 119, lô A3 khu đô thị Đại Kim, Phường Định Công, TP Hà Nội</t>
   </si>
   <si>
     <t>0105161861</t>
@@ -9106,10 +9106,10 @@
     <t>VTSB QN</t>
   </si>
   <si>
-    <t>C«ng ty CP XNK vµ VTSB Qu¶ng Ninh</t>
-  </si>
-  <si>
-    <t>Sè 85 Lª Th¸nh T«ng - TP. H¹ Long - TØnh Qu¶ng Ninh</t>
+    <t>Công ty CP XNK và VTSB Quảng Ninh</t>
+  </si>
+  <si>
+    <t>Số 85 Lê Thánh Tông - TP. Hạ Long - Tỉnh Quảng Ninh</t>
   </si>
   <si>
     <t>5700567241</t>
@@ -9118,16 +9118,16 @@
     <t>VTSDD</t>
   </si>
   <si>
-    <t>C«ng ty TNHH DV giao nhËn vËn t¶i Sao §¹i D­¬ng</t>
+    <t>Công ty TNHH DV giao nhận vận tải Sao Đại Dương</t>
   </si>
   <si>
     <t>VTTHUETAU</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn vËn t¶i vµ thuª tµu</t>
-  </si>
-  <si>
-    <t>Sè 74, Phè NguyÔn Du, Ph­êng NguyÔn Du - QuËn Hai Bµ Tr­ng - TP. HN</t>
+    <t>Công ty cổ phần vận tải và thuê tàu</t>
+  </si>
+  <si>
+    <t>Số 74, Phố Nguyễn Du, Phường Nguyễn Du - Quận Hai Bà Trưng - TP. HN</t>
   </si>
   <si>
     <t>0100105937</t>
@@ -9136,10 +9136,10 @@
     <t>VTTRUONGTHANH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng m¹i vµ vËn t¶i Tr­êng Thµnh</t>
-  </si>
-  <si>
-    <t>khu ®« thÞ míi, ThÞ trÊn Minh T©n, HuyÖn Kinh M«n, TØnh H¶i D­¬ng</t>
+    <t>Công ty TNHH Thương mại và vận tải Trường Thành</t>
+  </si>
+  <si>
+    <t>khu đô thị mới, Thị trấn Minh Tân, Huyện Kinh Môn, Tỉnh Hải Dương</t>
   </si>
   <si>
     <t>0800289260</t>
@@ -9148,10 +9148,10 @@
     <t>VTTTHCM</t>
   </si>
   <si>
-    <t>CN C«ng ty CP vËn t¶i vµ thuª tµu ( Vietfracht Hå ChÝ Minh)</t>
-  </si>
-  <si>
-    <t>11 NguyÔn C«ng Trø - P. NguyÔn Th¸i B×nh - QuËn 1 - TP. Hå ChÝ Minh</t>
+    <t>CN Công ty CP vận tải và thuê tàu ( Vietfracht Hồ Chí Minh)</t>
+  </si>
+  <si>
+    <t>11 Nguyễn Công Trứ - P. Nguyễn Thái Bình - Quận 1 - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0100105937002</t>
@@ -9160,10 +9160,10 @@
     <t>VUDINHNINHBINH</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Vò §×nh Ninh B×nh</t>
-  </si>
-  <si>
-    <t>L« C12, KCN Kh¸nh Phu, x· Kh¸nh Phu, huyÖn Yªn Kh¸nh, TØnh Ninh B×nh</t>
+    <t>Công ty TNHH Vũ Đình Ninh Bình</t>
+  </si>
+  <si>
+    <t>Lô C12, KCN Khánh Phu, xã Khánh Phu, huyện Yên Khánh, Tỉnh Ninh Bình</t>
   </si>
   <si>
     <t>2700611569</t>
@@ -9172,10 +9172,10 @@
     <t>VUGIATAM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i vµ vËn t¶i Vò Gia Tam</t>
-  </si>
-  <si>
-    <t>Nhµ «ng Lª Ngäc Ngä, Xãm 3, Th«n Tam §ång, X· Th¸i Thuþ, TØnh H­ng Yªn, ViÖt Nam</t>
+    <t>Công ty TNHH Thương Mại và vận tải Vũ Gia Tam</t>
+  </si>
+  <si>
+    <t>Nhà ông Lê Ngọc Ngọ, Xóm 3, Thôn Tam Đồng, Xã Thái Thuỵ, Tỉnh Hưng Yên, Việt Nam</t>
   </si>
   <si>
     <t>1001011415</t>
@@ -9184,10 +9184,10 @@
     <t>WALLEM VN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Hµng H¶i Wallem ViÖt Nam</t>
-  </si>
-  <si>
-    <t>1489 NguyÔn V¨n Linh - Ph­êng T©n Phong - QuËn 7 - TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH Hàng Hải Wallem Việt Nam</t>
+  </si>
+  <si>
+    <t>1489 Nguyễn Văn Linh - Phường Tân Phong - Quận 7 - TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0309822284</t>
@@ -9265,10 +9265,10 @@
     <t>WOOSUNG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Woongsung Electronics ViÖt Nam</t>
-  </si>
-  <si>
-    <t>L« K2, KCN Trµng DuÖ, x· Hång Phong, huyÖn An D­¬ng, TP. H¶i Phßng,VN</t>
+    <t>Công ty TNHH Woongsung Electronics Việt Nam</t>
+  </si>
+  <si>
+    <t>Lô K2, KCN Tràng Duệ, xã Hồng Phong, huyện An Dương, TP. Hải Phòng,VN</t>
   </si>
   <si>
     <t>0201703482</t>
@@ -9283,10 +9283,10 @@
     <t>XAYDUNGTHANHAN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Kinh Doanh vµ X©y Dùng Thµnh An</t>
-  </si>
-  <si>
-    <t>Sè NT3.15A, khu ®« thÞ Vinhomes Maria, Ph­êng An Biªn, Thµnh Phè H¶i Phßng, VN</t>
+    <t>Công ty TNHH Kinh Doanh và Xây Dựng Thành An</t>
+  </si>
+  <si>
+    <t>Số NT3.15A, khu đô thị Vinhomes Maria, Phường An Biên, Thành Phố Hải Phòng, VN</t>
   </si>
   <si>
     <t>0202131090</t>
@@ -9295,10 +9295,10 @@
     <t>XDTHANGLONG</t>
   </si>
   <si>
-    <t>C«ng ty cæ phÇn xuÊt nhËp khÈu - ®Çu t­ - x©y dùng Th¨ng Long</t>
-  </si>
-  <si>
-    <t>Sè 35 NguyÔn V¨n trçi, P. Ph­¬ng LiÖt, Q. Thanh Xu©n - TP. Hµ Néi</t>
+    <t>Công ty cổ phần xuất nhập khẩu - đầu tư - xây dựng Thăng Long</t>
+  </si>
+  <si>
+    <t>Số 35 Nguyễn Văn trỗi, P. Phương Liệt, Q. Thanh Xuân - TP. Hà Nội</t>
   </si>
   <si>
     <t>0102703900</t>
@@ -9307,10 +9307,10 @@
     <t>XDTLOI</t>
   </si>
   <si>
-    <t>C«ng ty TNHH TM - DV x¨ng dÇu ThuËn Lîi</t>
-  </si>
-  <si>
-    <t>15B/26 Lª Th¸nh T«n - Ph­êng BÕn NghÐ - QuËn 1</t>
+    <t>Công ty TNHH TM - DV xăng dầu Thuận Lợi</t>
+  </si>
+  <si>
+    <t>15B/26 Lê Thánh Tôn - Phường Bến Nghé - Quận 1</t>
   </si>
   <si>
     <t>0309920073</t>
@@ -9325,10 +9325,10 @@
     <t>XINGFENG</t>
   </si>
   <si>
-    <t>C«ng ty TNHH C«ng NghÖ N¨ng L­îng Xing Feng</t>
-  </si>
-  <si>
-    <t>Sè 36 §­êng Néi Khu H­ng Gia 1, Ph­êng T©n Phong, QuËn 7, TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH Công Nghệ Năng Lượng Xing Feng</t>
+  </si>
+  <si>
+    <t>Số 36 Đường Nội Khu Hưng Gia 1, Phường Tân Phong, Quận 7, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0318582261</t>
@@ -9337,10 +9337,10 @@
     <t>XINSAN</t>
   </si>
   <si>
-    <t>C«ng ty TNHH XuÊt NhËp KhÈu Xinsan</t>
-  </si>
-  <si>
-    <t>Xãm Lòng - X· V¨n Lu«ng - HuyÖn T©n S¬n - TØnh Phó Thä</t>
+    <t>Công ty TNHH Xuất Nhập Khẩu Xinsan</t>
+  </si>
+  <si>
+    <t>Xóm Lũng - Xã Văn Luông - Huyện Tân Sơn - Tỉnh Phú Thọ</t>
   </si>
   <si>
     <t>2600876593</t>
@@ -9349,10 +9349,10 @@
     <t>XNK CCM</t>
   </si>
   <si>
-    <t>C«ng ty TNHH Th­¬ng M¹i DÞch Vô Vµ XuÊt NhËp KhÈu CCM</t>
-  </si>
-  <si>
-    <t>L« 33, tæ d©n phè 7, Ph­êng H¶i An, Thµnh Phè H¶i Phßng, ViÖt Nam</t>
+    <t>Công ty TNHH Thương Mại Dịch Vụ Và Xuất Nhập Khẩu CCM</t>
+  </si>
+  <si>
+    <t>Lô 33, tổ dân phố 7, Phường Hải An, Thành Phố Hải Phòng, Việt Nam</t>
   </si>
   <si>
     <t>0202133002</t>
@@ -9361,7 +9361,7 @@
     <t>XNKKH</t>
   </si>
   <si>
-    <t>40/115 §µo TÊn, Ba §×nh, HN</t>
+    <t>40/115 Đào Tấn, Ba Đình, HN</t>
   </si>
   <si>
     <t>0102631036</t>
@@ -9370,10 +9370,10 @@
     <t>XNKTBMCT</t>
   </si>
   <si>
-    <t>Cty TNHH XNK thiÕt bÞ m¸y c«ng tr×nh ViÖt Hµn</t>
-  </si>
-  <si>
-    <t>562 NguyÔn V¨n Cõ, Long Biªn, Hµ Néi</t>
+    <t>Cty TNHH XNK thiết bị máy công trình Việt Hàn</t>
+  </si>
+  <si>
+    <t>562 Nguyễn Văn Cừ, Long Biên, Hà Nội</t>
   </si>
   <si>
     <t>0101654030</t>
@@ -9382,10 +9382,10 @@
     <t>XNKVN</t>
   </si>
   <si>
-    <t>Cty CP TMDV &amp; XNK ViÖt Nam</t>
-  </si>
-  <si>
-    <t>P2206 Toµ nhµ 71 NguyÔn ChÝ Thanh, §èng §a, HN</t>
+    <t>Cty CP TMDV &amp; XNK Việt Nam</t>
+  </si>
+  <si>
+    <t>P2206 Toà nhà 71 Nguyễn Chí Thanh, Đống Đa, HN</t>
   </si>
   <si>
     <t>0101577202</t>
@@ -9412,7 +9412,7 @@
     <t>YEN</t>
   </si>
   <si>
-    <t>C«ng ty Yann Horng Enterprise</t>
+    <t>Công ty Yann Horng Enterprise</t>
   </si>
   <si>
     <t>198-10 Chung-Shan RD, Su-Ao Township, I-Lan county Taiwan</t>
@@ -9430,10 +9430,10 @@
     <t>YKHOA HEARLIFE</t>
   </si>
   <si>
-    <t>C«ng ty TNHH MTV ThiÕt BÞ Y Khoa Hearlife</t>
-  </si>
-  <si>
-    <t>180-182 Ng« Gia Tù, Ph­êng 9, QuËn 10, TP. Hå ChÝ Minh</t>
+    <t>Công ty TNHH MTV Thiết Bị Y Khoa Hearlife</t>
+  </si>
+  <si>
+    <t>180-182 Ngô Gia Tự, Phường 9, Quận 10, TP. Hồ Chí Minh</t>
   </si>
   <si>
     <t>0312146780</t>
@@ -9484,13 +9484,13 @@
     <t>2F, No.380, Sec.6, WunShan District, TaiPei City, Taiwan</t>
   </si>
   <si>
-    <t>§TP</t>
-  </si>
-  <si>
-    <t>C«ng ty CP §«ng Thiªn Phó MiÒn Nam</t>
-  </si>
-  <si>
-    <t>B21-K34 TrÇn ThiÖn Ch¸nh, P12, Q. 10, HCM</t>
+    <t>ĐTP</t>
+  </si>
+  <si>
+    <t>Công ty CP Đông Thiên Phú Miền Nam</t>
+  </si>
+  <si>
+    <t>B21-K34 Trần Thiện Chánh, P12, Q. 10, HCM</t>
   </si>
   <si>
     <t>0305700750</t>
@@ -9529,49 +9529,49 @@
     <t>[ 11 ]</t>
   </si>
   <si>
-    <t>M· §T</t>
-  </si>
-  <si>
-    <t>Tªn ®èi t­îng</t>
-  </si>
-  <si>
-    <t>Tªn nhãm</t>
-  </si>
-  <si>
-    <t>§Þa chØ</t>
-  </si>
-  <si>
-    <t>§iÖn tho¹i</t>
-  </si>
-  <si>
-    <t>Ms thuÕ</t>
-  </si>
-  <si>
-    <t>Ng­êi ®¹i diÖn</t>
-  </si>
-  <si>
-    <t>M· nhãm §T</t>
-  </si>
-  <si>
-    <t>DiÔn gi¶i</t>
-  </si>
-  <si>
-    <t>§¬n vÞ</t>
-  </si>
-  <si>
-    <t>Th«ng tin</t>
-  </si>
-  <si>
-    <t>Danh môc nhãm ®èi t­îng</t>
-  </si>
-  <si>
-    <t>§iÖn tho¹i: 0225 3750205</t>
-  </si>
-  <si>
-    <t>§Þa chØ: Sè 508 Lª Th¸nh T«ng, Ph­êng V¹n Mü, Ng« QuyÒn, H¶i Phßng</t>
-  </si>
-  <si>
-    <t>C«ng ty tr¸ch nhiÖm h÷u h¹n Lª Ph¹m</t>
+    <t>Mã ĐT</t>
+  </si>
+  <si>
+    <t>Tên đối tượng</t>
+  </si>
+  <si>
+    <t>Tên nhóm</t>
+  </si>
+  <si>
+    <t>Địa chỉ</t>
+  </si>
+  <si>
+    <t>Điện thoại</t>
+  </si>
+  <si>
+    <t>Ms thuế</t>
+  </si>
+  <si>
+    <t>Người đại diện</t>
+  </si>
+  <si>
+    <t>Mã nhóm ĐT</t>
+  </si>
+  <si>
+    <t>Diễn giải</t>
+  </si>
+  <si>
+    <t>Đơn vị</t>
+  </si>
+  <si>
+    <t>Thông tin</t>
+  </si>
+  <si>
+    <t>Danh mục nhóm đối tượng</t>
+  </si>
+  <si>
+    <t>Điện thoại: 0225 3750205</t>
+  </si>
+  <si>
+    <t>Địa chỉ: Số 508 Lê Thánh Tông, Phường Vạn Mỹ, Ngô Quyền, Hải Phòng</t>
+  </si>
+  <si>
+    <t>Công ty trách nhiệm hữu hạn Lê Phạm</t>
   </si>
 </sst>
 </file>
